--- a/Article_data/Step 3 results from Prodcom data manipulations.xlsx
+++ b/Article_data/Step 3 results from Prodcom data manipulations.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80881D6C-5C6C-437D-BBD0-A53F4B769057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1D2142-ADF2-42C6-95CD-FF979A6BD5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="3" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
     <sheet name="Filtered Prodcom data" sheetId="3" r:id="rId2"/>
     <sheet name="Calculations" sheetId="6" r:id="rId3"/>
-    <sheet name="Hotspots" sheetId="7" r:id="rId4"/>
+    <sheet name="Hotspot prodcom products" sheetId="7" r:id="rId4"/>
     <sheet name="References" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
@@ -9302,9 +9302,6 @@
     <t>Note:</t>
   </si>
   <si>
-    <t>When determining the Ecoinvent regions, if local availability of a product in Europe was 80% or more, we assumed 100% RER or RER w/o RU. See "Get product importers from BACI.ipynb" file in the SI for details on the calculation of import shares from the different regions and countries.</t>
-  </si>
-  <si>
     <t>Prodcom data obtained from "Extract Prodcom data.ipynb"</t>
   </si>
   <si>
@@ -9324,6 +9321,9 @@
   </si>
   <si>
     <t>Ecoinvent 3.12 activity region 5 share</t>
+  </si>
+  <si>
+    <t>When determining the Ecoinvent regions, if local availability of a product in Europe was 80% or more, we assumed 100% RER or RER w/o RU. See "Get product importers from BACI.ipynb" file in the SI for details on the calculation of import shares from the different regions and countries. The table should be exported as CSV and imported into the "Calculate product footprints and generate hotspot figure.ipynb" notebook.</t>
   </si>
 </sst>
 </file>
@@ -9680,7 +9680,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="9" applyBorder="1" applyAlignment="1">
@@ -9852,9 +9852,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="8" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="13" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -9865,6 +9862,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -10587,37 +10590,37 @@
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="86" t="s">
-        <v>3067</v>
-      </c>
-      <c r="C30" s="87" t="str">
+      <c r="B30" s="85" t="s">
+        <v>3066</v>
+      </c>
+      <c r="C30" s="86" t="str">
         <f>'Filtered Prodcom data'!$B$1</f>
         <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="86" t="s">
+      <c r="B31" s="85" t="s">
         <v>2729</v>
       </c>
-      <c r="C31" s="87" t="str">
+      <c r="C31" s="86" t="str">
         <f>Calculations!$B$1</f>
         <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B32" s="86" t="s">
+      <c r="B32" s="85" t="s">
         <v>2730</v>
       </c>
-      <c r="C32" s="87" t="str">
-        <f>Hotspots!$B$1</f>
+      <c r="C32" s="86" t="str">
+        <f>'Hotspot prodcom products'!$B$1</f>
         <v>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="88" t="s">
+      <c r="B33" s="87" t="s">
         <v>2731</v>
       </c>
-      <c r="C33" s="89" t="str">
+      <c r="C33" s="88" t="str">
         <f>References!$B$1</f>
         <v>Bibliography: list of references used thoughout the workbook</v>
       </c>
@@ -10893,7 +10896,7 @@
         <v>3061</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="AC1" s="44"/>
       <c r="AE1" s="44"/>
@@ -10906,7 +10909,7 @@
         <v>3063</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="AC2" s="44"/>
       <c r="AE2" s="44"/>
@@ -39911,7 +39914,7 @@
         <v>3061</v>
       </c>
       <c r="B1" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -40255,16 +40258,16 @@
       <c r="A2" t="s">
         <v>3063</v>
       </c>
-      <c r="B2" t="s">
-        <v>3064</v>
+      <c r="B2" s="91" t="s">
+        <v>3071</v>
       </c>
     </row>
     <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="F4" s="85" t="s">
+      <c r="F4" s="90" t="s">
         <v>705</v>
       </c>
-      <c r="G4" s="85"/>
+      <c r="G4" s="90"/>
       <c r="I4" s="47"/>
       <c r="J4" s="47"/>
     </row>
@@ -40357,10 +40360,10 @@
         <v>3056</v>
       </c>
       <c r="AD5" s="57" t="s">
+        <v>3069</v>
+      </c>
+      <c r="AE5" s="57" t="s">
         <v>3070</v>
-      </c>
-      <c r="AE5" s="57" t="s">
-        <v>3071</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
@@ -40670,8 +40673,8 @@
       <c r="B10" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="90" t="s">
-        <v>3069</v>
+      <c r="C10" s="89" t="s">
+        <v>3068</v>
       </c>
       <c r="D10" t="s">
         <v>112</v>

--- a/Article_data/Step 3 results from Prodcom data manipulations.xlsx
+++ b/Article_data/Step 3 results from Prodcom data manipulations.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF1D2142-ADF2-42C6-95CD-FF979A6BD5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457B40DD-F25B-427A-982C-22A54F724B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" activeTab="3" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
     <sheet name="Filtered Prodcom data" sheetId="3" r:id="rId2"/>
     <sheet name="Calculations" sheetId="6" r:id="rId3"/>
-    <sheet name="Hotspot prodcom products" sheetId="7" r:id="rId4"/>
+    <sheet name="Hotspot products export" sheetId="7" r:id="rId4"/>
     <sheet name="References" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7444" uniqueCount="3072">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7448" uniqueCount="3076">
   <si>
     <t>freq</t>
   </si>
@@ -7961,9 +7961,6 @@
     <t>In scope</t>
   </si>
   <si>
-    <t>Ecoinvent 3.11 activity name proxy</t>
-  </si>
-  <si>
     <t>Note and references</t>
   </si>
   <si>
@@ -8300,9 +8297,6 @@
     <t>Calculations</t>
   </si>
   <si>
-    <t>Hotspots</t>
-  </si>
-  <si>
     <t>References</t>
   </si>
   <si>
@@ -9324,6 +9318,24 @@
   </si>
   <si>
     <t>When determining the Ecoinvent regions, if local availability of a product in Europe was 80% or more, we assumed 100% RER or RER w/o RU. See "Get product importers from BACI.ipynb" file in the SI for details on the calculation of import shares from the different regions and countries. The table should be exported as CSV and imported into the "Calculate product footprints and generate hotspot figure.ipynb" notebook.</t>
+  </si>
+  <si>
+    <t>Ecoinvent activity name or proxy</t>
+  </si>
+  <si>
+    <t>Tested with Ecoinvent 3.11 and 3.12</t>
+  </si>
+  <si>
+    <t>Green columns:</t>
+  </si>
+  <si>
+    <t>Required in the CSV export used for listing available Ecoinvent geographies</t>
+  </si>
+  <si>
+    <t>Improved some descriptions. Renamed some column titles and sheet name in export sheet.</t>
+  </si>
+  <si>
+    <t>Hotspot products export</t>
   </si>
 </sst>
 </file>
@@ -9480,7 +9492,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9514,6 +9526,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -9680,7 +9698,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="9" applyBorder="1" applyAlignment="1">
@@ -9864,10 +9882,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -10436,7 +10457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0928EDD3-90ED-405A-8C35-7F6C77CACFAF}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:G47"/>
+  <dimension ref="B2:G48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.77734375" customWidth="1"/>
@@ -10447,100 +10468,100 @@
   <sheetData>
     <row r="2" spans="2:3" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="12" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B5" s="13" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>2703</v>
+      </c>
+      <c r="C7" t="s">
         <v>2704</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2705</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
+        <v>2705</v>
+      </c>
+      <c r="C8" t="s">
         <v>2706</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2707</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
+        <v>2707</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>2708</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>2709</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
+        <v>2709</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>2710</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>2711</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>2712</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>2713</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>2713</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>2714</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>2715</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>2716</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>2717</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>2718</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>2719</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>2720</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>2721</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="13" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="17" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
@@ -10548,7 +10569,7 @@
         <v>46146</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
@@ -10556,277 +10577,285 @@
         <v>46242</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>2808</v>
+        <v>2806</v>
       </c>
     </row>
-    <row r="23" spans="2:3" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="19">
+    <row r="23" spans="2:3" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="37">
         <v>46245</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>3060</v>
+      <c r="C23" s="29" t="s">
+        <v>3058</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="13" t="s">
+    <row r="24" spans="2:3" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="19">
+        <v>46247</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>3074</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="13" t="s">
+        <v>2724</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29" s="17" t="s">
         <v>2725</v>
       </c>
-    </row>
-    <row r="27" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" s="17" t="s">
-        <v>2726</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>2714</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="21" t="s">
-        <v>2727</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>2728</v>
+      <c r="C29" s="18" t="s">
+        <v>2713</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="85" t="s">
-        <v>3066</v>
-      </c>
-      <c r="C30" s="86" t="str">
-        <f>'Filtered Prodcom data'!$B$1</f>
-        <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
+      <c r="B30" s="21" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C30" s="22" t="s">
+        <v>2727</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="85" t="s">
-        <v>2729</v>
+        <v>3064</v>
       </c>
       <c r="C31" s="86" t="str">
-        <f>Calculations!$B$1</f>
-        <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
+        <f>'Filtered Prodcom data'!$B$1</f>
+        <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="85" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="C32" s="86" t="str">
-        <f>'Hotspot prodcom products'!$B$1</f>
+        <f>Calculations!$B$1</f>
+        <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B33" s="85" t="s">
+        <v>3075</v>
+      </c>
+      <c r="C33" s="86" t="str">
+        <f>'Hotspot products export'!$B$1</f>
         <v>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="87" t="s">
-        <v>2731</v>
-      </c>
-      <c r="C33" s="88" t="str">
+    <row r="34" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="87" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C34" s="88" t="str">
         <f>References!$B$1</f>
         <v>Bibliography: list of references used thoughout the workbook</v>
       </c>
     </row>
-    <row r="35" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="13" t="s">
+    <row r="36" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B37" s="13" t="s">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B39" s="17" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>2713</v>
+      </c>
+      <c r="D39" s="23" t="s">
         <v>2732</v>
       </c>
-    </row>
-    <row r="37" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="17" t="s">
+      <c r="E39" s="23" t="s">
         <v>2733</v>
       </c>
-      <c r="C38" s="23" t="s">
-        <v>2714</v>
-      </c>
-      <c r="D38" s="23" t="s">
+      <c r="F39" s="23" t="s">
         <v>2734</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="G39" s="24" t="s">
         <v>2735</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>2736</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>2737</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="21" t="s">
-        <v>2738</v>
-      </c>
-      <c r="C39" t="s">
-        <v>2739</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>2740</v>
-      </c>
-      <c r="E39" s="25">
-        <v>15</v>
-      </c>
-      <c r="F39" s="25">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G39" s="26">
-        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B40" s="21" t="s">
-        <v>2741</v>
+        <v>2736</v>
       </c>
       <c r="C40" t="s">
-        <v>2742</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>2743</v>
-      </c>
-      <c r="E40" s="3">
+        <v>2737</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E40" s="25">
         <v>15</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="25">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G40" s="76">
+      <c r="G40" s="26">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="21" t="s">
-        <v>2744</v>
+        <v>2739</v>
       </c>
       <c r="C41" t="s">
-        <v>2745</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>2746</v>
-      </c>
-      <c r="E41" s="4">
+        <v>2740</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="E41" s="3">
         <v>15</v>
       </c>
-      <c r="F41" s="68">
+      <c r="F41" s="3">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G41" s="69">
+      <c r="G41" s="76">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="21" t="s">
-        <v>2747</v>
+        <v>2742</v>
       </c>
       <c r="C42" t="s">
-        <v>2748</v>
-      </c>
-      <c r="D42" s="27" t="s">
-        <v>2749</v>
-      </c>
-      <c r="E42" s="27">
+        <v>2743</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>2744</v>
+      </c>
+      <c r="E42" s="4">
         <v>15</v>
       </c>
-      <c r="F42" s="27">
+      <c r="F42" s="68">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G42" s="28">
+      <c r="G42" s="69">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="21" t="s">
-        <v>2750</v>
+        <v>2745</v>
       </c>
       <c r="C43" t="s">
-        <v>2751</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>2752</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>2753</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>2754</v>
-      </c>
-      <c r="G43" s="81" t="s">
-        <v>2755</v>
+        <v>2746</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E43" s="27">
+        <v>15</v>
+      </c>
+      <c r="F43" s="27">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G43" s="28">
+        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="21" t="s">
-        <v>2756</v>
+        <v>2748</v>
       </c>
       <c r="C44" t="s">
-        <v>2757</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>2758</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>2759</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>2760</v>
-      </c>
-      <c r="G44" s="73" t="s">
-        <v>2761</v>
+        <v>2749</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>2750</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>2751</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>2752</v>
+      </c>
+      <c r="G44" s="81" t="s">
+        <v>2753</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="21" t="s">
-        <v>2762</v>
+        <v>2754</v>
       </c>
       <c r="C45" t="s">
-        <v>2763</v>
-      </c>
-      <c r="D45" s="66" t="s">
-        <v>2764</v>
-      </c>
-      <c r="E45" s="66" t="s">
-        <v>2765</v>
-      </c>
-      <c r="F45" s="66" t="s">
-        <v>2766</v>
-      </c>
-      <c r="G45" s="67"/>
+        <v>2755</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>2756</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>2757</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>2758</v>
+      </c>
+      <c r="G45" s="73" t="s">
+        <v>2759</v>
+      </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="30" t="s">
+      <c r="B46" s="21" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D46" s="66" t="s">
+        <v>2762</v>
+      </c>
+      <c r="E46" s="66" t="s">
+        <v>2763</v>
+      </c>
+      <c r="F46" s="66" t="s">
+        <v>2764</v>
+      </c>
+      <c r="G46" s="67"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B47" s="30" t="s">
+        <v>2765</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2766</v>
+      </c>
+      <c r="D47" s="31" t="s">
         <v>2767</v>
       </c>
-      <c r="C46" t="s">
+      <c r="E47" s="31">
+        <v>15</v>
+      </c>
+      <c r="F47" s="31">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G47" s="32">
+        <v>5.5855E-5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="33" t="s">
+        <v>2765</v>
+      </c>
+      <c r="C48" s="34" t="s">
         <v>2768</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D48" s="35" t="s">
         <v>2769</v>
       </c>
-      <c r="E46" s="31">
+      <c r="E48" s="70">
         <v>15</v>
       </c>
-      <c r="F46" s="31">
+      <c r="F48" s="36">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G46" s="32">
-        <v>5.5855E-5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="33" t="s">
-        <v>2767</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>2770</v>
-      </c>
-      <c r="D47" s="35" t="s">
-        <v>2771</v>
-      </c>
-      <c r="E47" s="70">
-        <v>15</v>
-      </c>
-      <c r="F47" s="36">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G47" s="77">
+      <c r="G48" s="77">
         <v>5.5855E-5</v>
       </c>
     </row>
@@ -10836,10 +10865,10 @@
     <hyperlink ref="C11" r:id="rId2" xr:uid="{41B7F739-267F-43D4-BA81-097B57D6E931}"/>
     <hyperlink ref="C15" r:id="rId3" xr:uid="{A231AF78-61FF-4A68-B4C3-3DDFEB4B0959}"/>
     <hyperlink ref="C14" r:id="rId4" xr:uid="{5739EB44-C6AF-4C59-923B-AEA8B4D6A45E}"/>
-    <hyperlink ref="B30" location="'Filtered Prodcom data'!A1" display="'Filtered Prodcom data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
-    <hyperlink ref="B31" location="'Calculations'!A1" display="'Calculations'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
-    <hyperlink ref="B32" location="'Hotspots'!A1" display="'Hotspots'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
-    <hyperlink ref="B33" location="'References'!A1" display="'References'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
+    <hyperlink ref="B31" location="'Filtered Prodcom data'!A1" display="'Filtered Prodcom data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
+    <hyperlink ref="B32" location="'Calculations'!A1" display="'Calculations'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
+    <hyperlink ref="B33" location="'Hotspot products export'!A1" display="'Hotspot products export'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
+    <hyperlink ref="B34" location="'References'!A1" display="'References'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10893,10 +10922,10 @@
   <sheetData>
     <row r="1" spans="1:37" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>3064</v>
+        <v>3062</v>
       </c>
       <c r="AC1" s="44"/>
       <c r="AE1" s="44"/>
@@ -10906,10 +10935,10 @@
     </row>
     <row r="2" spans="1:37" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
+        <v>3061</v>
+      </c>
+      <c r="B2" s="50" t="s">
         <v>3063</v>
-      </c>
-      <c r="B2" s="50" t="s">
-        <v>3065</v>
       </c>
       <c r="AC2" s="44"/>
       <c r="AE2" s="44"/>
@@ -11031,7 +11060,7 @@
         <v>2615</v>
       </c>
       <c r="AJ4" s="7" t="s">
-        <v>2809</v>
+        <v>2807</v>
       </c>
       <c r="AK4" s="7" t="s">
         <v>2616</v>
@@ -11156,7 +11185,7 @@
         <v>0.33934595780815596</v>
       </c>
       <c r="AK5" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.3">
@@ -11278,7 +11307,7 @@
         <v>0.86402104863567564</v>
       </c>
       <c r="AK6" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.3">
@@ -11400,7 +11429,7 @@
         <v>0.87904863332422545</v>
       </c>
       <c r="AK7" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.3">
@@ -11522,7 +11551,7 @@
         <v>0.94409418582769256</v>
       </c>
       <c r="AK8" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.3">
@@ -11644,7 +11673,7 @@
         <v>0.78369292184089345</v>
       </c>
       <c r="AK9" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.3">
@@ -11766,7 +11795,7 @@
         <v>0.14193164800139446</v>
       </c>
       <c r="AK10" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.3">
@@ -11888,7 +11917,7 @@
         <v>0.88287081478020857</v>
       </c>
       <c r="AK11" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="12" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -12010,7 +12039,7 @@
         <v>0.70164983556725846</v>
       </c>
       <c r="AK12" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="13" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -12024,73 +12053,73 @@
         <v>526</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>2618</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>2619</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>2620</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J13" s="5" t="s">
         <v>2621</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13" s="5" t="s">
+      <c r="K13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L13" s="5" t="s">
         <v>2622</v>
       </c>
-      <c r="K13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="L13" s="5" t="s">
+      <c r="M13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="N13" s="5" t="s">
         <v>2623</v>
       </c>
-      <c r="M13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="N13" s="5" t="s">
+      <c r="O13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="P13" s="5" t="s">
         <v>2624</v>
       </c>
-      <c r="O13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="P13" s="5" t="s">
+      <c r="Q13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="R13" s="5" t="s">
         <v>2625</v>
       </c>
-      <c r="Q13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="R13" s="5" t="s">
+      <c r="S13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="T13" s="5" t="s">
         <v>2626</v>
       </c>
-      <c r="S13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="T13" s="5" t="s">
+      <c r="U13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="V13" s="5" t="s">
         <v>2627</v>
       </c>
-      <c r="U13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="V13" s="5" t="s">
+      <c r="W13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="X13" s="5" t="s">
         <v>2628</v>
       </c>
-      <c r="W13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="X13" s="5" t="s">
+      <c r="Y13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="5" t="s">
         <v>2629</v>
-      </c>
-      <c r="Y13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z13" s="5" t="s">
-        <v>2630</v>
       </c>
       <c r="AA13" s="6" t="s">
         <v>7</v>
@@ -12132,7 +12161,7 @@
         <v>0.76664800793122878</v>
       </c>
       <c r="AK13" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.3">
@@ -12254,7 +12283,7 @@
         <v>0.89272188364169869</v>
       </c>
       <c r="AK14" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.3">
@@ -12376,7 +12405,7 @@
         <v>0.7961067883023123</v>
       </c>
       <c r="AK15" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="16" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -12498,7 +12527,7 @@
         <v>0.89458376512907545</v>
       </c>
       <c r="AK16" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.3">
@@ -12620,7 +12649,7 @@
         <v>0.8225375065540016</v>
       </c>
       <c r="AK17" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.3">
@@ -12742,7 +12771,7 @@
         <v>0.82690725513409014</v>
       </c>
       <c r="AK18" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.3">
@@ -12864,7 +12893,7 @@
         <v>0.80199726304971886</v>
       </c>
       <c r="AK19" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.3">
@@ -12986,7 +13015,7 @@
         <v>0.6568762309953875</v>
       </c>
       <c r="AK20" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="21" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -13108,7 +13137,7 @@
         <v>0.95198584959722587</v>
       </c>
       <c r="AK21" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="22" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -13230,7 +13259,7 @@
         <v>0.79176760421541659</v>
       </c>
       <c r="AK22" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.3">
@@ -13352,7 +13381,7 @@
         <v>0.9968172135460267</v>
       </c>
       <c r="AK23" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="24" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -13474,7 +13503,7 @@
         <v>0.35342298211170275</v>
       </c>
       <c r="AK24" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="25" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -13596,7 +13625,7 @@
         <v>0.71256887205279718</v>
       </c>
       <c r="AK25" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.3">
@@ -13718,7 +13747,7 @@
         <v>0.87748442629671652</v>
       </c>
       <c r="AK26" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="27" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -13840,7 +13869,7 @@
         <v>0.42567979681845169</v>
       </c>
       <c r="AK27" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="28" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -13962,7 +13991,7 @@
         <v>0.84732594279594586</v>
       </c>
       <c r="AK28" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="29" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -14084,7 +14113,7 @@
         <v>6.2771337325646187E-2</v>
       </c>
       <c r="AK29" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.3">
@@ -14206,7 +14235,7 @@
         <v>0.99997666754441616</v>
       </c>
       <c r="AK30" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="31" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -14328,7 +14357,7 @@
         <v>0.95900426816996931</v>
       </c>
       <c r="AK31" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.3">
@@ -14450,7 +14479,7 @@
         <v>0.88707249478326589</v>
       </c>
       <c r="AK32" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="33" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -14572,7 +14601,7 @@
         <v>0.84828638672183576</v>
       </c>
       <c r="AK33" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.3">
@@ -14694,7 +14723,7 @@
         <v>0.55687101886052137</v>
       </c>
       <c r="AK34" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="35" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -14816,7 +14845,7 @@
         <v>0.84592847893162759</v>
       </c>
       <c r="AK35" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="36" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -14938,7 +14967,7 @@
         <v>0.72633337392949582</v>
       </c>
       <c r="AK36" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="37" spans="1:37" x14ac:dyDescent="0.3">
@@ -15060,7 +15089,7 @@
         <v>0.98168669522505081</v>
       </c>
       <c r="AK37" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="38" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -15182,7 +15211,7 @@
         <v>0.83863209227625446</v>
       </c>
       <c r="AK38" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="39" spans="1:37" x14ac:dyDescent="0.3">
@@ -15304,7 +15333,7 @@
         <v>0.93163807390386044</v>
       </c>
       <c r="AK39" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="40" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -15426,7 +15455,7 @@
         <v>0.41122958882181987</v>
       </c>
       <c r="AK40" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="41" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -15440,55 +15469,55 @@
         <v>529</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>2630</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>2631</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>2632</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H41" s="5" t="s">
+      <c r="I41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J41" s="5" t="s">
         <v>2633</v>
       </c>
-      <c r="I41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J41" s="5" t="s">
+      <c r="K41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L41" s="5" t="s">
         <v>2634</v>
       </c>
-      <c r="K41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="L41" s="5" t="s">
+      <c r="M41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="N41" s="5" t="s">
         <v>2635</v>
       </c>
-      <c r="M41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="N41" s="5" t="s">
+      <c r="O41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="P41" s="5" t="s">
         <v>2636</v>
       </c>
-      <c r="O41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="P41" s="5" t="s">
+      <c r="Q41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="R41" s="5" t="s">
         <v>2637</v>
       </c>
-      <c r="Q41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="R41" s="5" t="s">
+      <c r="S41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="T41" s="5" t="s">
         <v>2638</v>
-      </c>
-      <c r="S41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="T41" s="5" t="s">
-        <v>2639</v>
       </c>
       <c r="U41" s="6" t="s">
         <v>7</v>
@@ -15500,13 +15529,13 @@
         <v>527</v>
       </c>
       <c r="X41" s="5" t="s">
+        <v>2639</v>
+      </c>
+      <c r="Y41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z41" s="5" t="s">
         <v>2640</v>
-      </c>
-      <c r="Y41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z41" s="5" t="s">
-        <v>2641</v>
       </c>
       <c r="AA41" s="6" t="s">
         <v>7</v>
@@ -15548,7 +15577,7 @@
         <v>0.64695136177420065</v>
       </c>
       <c r="AK41" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="42" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -15670,7 +15699,7 @@
         <v>0.658130403766089</v>
       </c>
       <c r="AK42" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="43" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -15792,7 +15821,7 @@
         <v>0.88711811424638753</v>
       </c>
       <c r="AK43" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="44" spans="1:37" x14ac:dyDescent="0.3">
@@ -15914,7 +15943,7 @@
         <v>0.7564803460728331</v>
       </c>
       <c r="AK44" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="45" spans="1:37" x14ac:dyDescent="0.3">
@@ -16036,7 +16065,7 @@
         <v>0.46597635861951109</v>
       </c>
       <c r="AK45" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="46" spans="1:37" x14ac:dyDescent="0.3">
@@ -16158,7 +16187,7 @@
         <v>0.97878773028598831</v>
       </c>
       <c r="AK46" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="47" spans="1:37" x14ac:dyDescent="0.3">
@@ -16280,7 +16309,7 @@
         <v>0.92846915963429333</v>
       </c>
       <c r="AK47" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="48" spans="1:37" x14ac:dyDescent="0.3">
@@ -16402,7 +16431,7 @@
         <v>0.88632047658515611</v>
       </c>
       <c r="AK48" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="49" spans="1:37" x14ac:dyDescent="0.3">
@@ -16524,7 +16553,7 @@
         <v>0.97723312392412343</v>
       </c>
       <c r="AK49" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="50" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -16646,7 +16675,7 @@
         <v>0.9480517247887339</v>
       </c>
       <c r="AK50" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="51" spans="1:37" x14ac:dyDescent="0.3">
@@ -16768,7 +16797,7 @@
         <v>0.98372184312642852</v>
       </c>
       <c r="AK51" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="52" spans="1:37" x14ac:dyDescent="0.3">
@@ -16890,7 +16919,7 @@
         <v>0.16881151544376369</v>
       </c>
       <c r="AK52" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="53" spans="1:37" x14ac:dyDescent="0.3">
@@ -17012,7 +17041,7 @@
         <v>0.9949802605865421</v>
       </c>
       <c r="AK53" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="54" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -17134,7 +17163,7 @@
         <v>0.33991591454699727</v>
       </c>
       <c r="AK54" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="55" spans="1:37" x14ac:dyDescent="0.3">
@@ -17256,7 +17285,7 @@
         <v>0.90674928778782138</v>
       </c>
       <c r="AK55" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="56" spans="1:37" x14ac:dyDescent="0.3">
@@ -17378,7 +17407,7 @@
         <v>0.54958148029233567</v>
       </c>
       <c r="AK56" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="57" spans="1:37" x14ac:dyDescent="0.3">
@@ -17500,7 +17529,7 @@
         <v>0.50439285712492499</v>
       </c>
       <c r="AK57" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="58" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -17622,7 +17651,7 @@
         <v>0.75003262250355462</v>
       </c>
       <c r="AK58" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="59" spans="1:37" x14ac:dyDescent="0.3">
@@ -17744,7 +17773,7 @@
         <v>0.94336652483154892</v>
       </c>
       <c r="AK59" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="60" spans="1:37" x14ac:dyDescent="0.3">
@@ -17866,7 +17895,7 @@
         <v>0.71535186139088358</v>
       </c>
       <c r="AK60" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="61" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -17988,7 +18017,7 @@
         <v>0.59724348457138576</v>
       </c>
       <c r="AK61" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="62" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -18110,7 +18139,7 @@
         <v>0.90180169843095415</v>
       </c>
       <c r="AK62" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="63" spans="1:37" x14ac:dyDescent="0.3">
@@ -18232,7 +18261,7 @@
         <v>0.97390715616715806</v>
       </c>
       <c r="AK63" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="64" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -18354,7 +18383,7 @@
         <v>0.90107686900967998</v>
       </c>
       <c r="AK64" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="65" spans="1:37" x14ac:dyDescent="0.3">
@@ -18476,7 +18505,7 @@
         <v>0.93548794446506622</v>
       </c>
       <c r="AK65" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="66" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -18598,7 +18627,7 @@
         <v>0.96173635728890372</v>
       </c>
       <c r="AK66" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="67" spans="1:37" x14ac:dyDescent="0.3">
@@ -18720,7 +18749,7 @@
         <v>0.9345821199560983</v>
       </c>
       <c r="AK67" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="68" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -18842,7 +18871,7 @@
         <v>0.79406464516903963</v>
       </c>
       <c r="AK68" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="69" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -18964,7 +18993,7 @@
         <v>0.72590541973084</v>
       </c>
       <c r="AK69" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="70" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -19086,7 +19115,7 @@
         <v>0.87301153280870381</v>
       </c>
       <c r="AK70" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="71" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -19208,7 +19237,7 @@
         <v>0.61212794489624245</v>
       </c>
       <c r="AK71" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="72" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -19330,7 +19359,7 @@
         <v>0.45202263595449155</v>
       </c>
       <c r="AK72" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="73" spans="1:37" x14ac:dyDescent="0.3">
@@ -19452,7 +19481,7 @@
         <v>0.85098041922137724</v>
       </c>
       <c r="AK73" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="74" spans="1:37" x14ac:dyDescent="0.3">
@@ -19574,7 +19603,7 @@
         <v>0.35122892718634474</v>
       </c>
       <c r="AK74" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="75" spans="1:37" x14ac:dyDescent="0.3">
@@ -19696,7 +19725,7 @@
         <v>0.85514301162071182</v>
       </c>
       <c r="AK75" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="76" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -19818,7 +19847,7 @@
         <v>0.83315163260239966</v>
       </c>
       <c r="AK76" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="77" spans="1:37" x14ac:dyDescent="0.3">
@@ -19940,7 +19969,7 @@
         <v>0.80917344833809868</v>
       </c>
       <c r="AK77" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="78" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -20062,7 +20091,7 @@
         <v>0.93588516459574056</v>
       </c>
       <c r="AK78" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="79" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -20184,7 +20213,7 @@
         <v>0.70017280887298816</v>
       </c>
       <c r="AK79" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="80" spans="1:37" x14ac:dyDescent="0.3">
@@ -20306,7 +20335,7 @@
         <v>0.93385612259264728</v>
       </c>
       <c r="AK80" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="81" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -20428,7 +20457,7 @@
         <v>0.7953139339510229</v>
       </c>
       <c r="AK81" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="82" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -20550,7 +20579,7 @@
         <v>0.57356531800796118</v>
       </c>
       <c r="AK82" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="83" spans="1:37" x14ac:dyDescent="0.3">
@@ -20672,7 +20701,7 @@
         <v>0.66130800742337414</v>
       </c>
       <c r="AK83" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="84" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -20794,7 +20823,7 @@
         <v>0.80492567424485906</v>
       </c>
       <c r="AK84" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="85" spans="1:37" x14ac:dyDescent="0.3">
@@ -20916,7 +20945,7 @@
         <v>0.84223339185782964</v>
       </c>
       <c r="AK85" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="86" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -21038,7 +21067,7 @@
         <v>0.61457642182308181</v>
       </c>
       <c r="AK86" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="87" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -21160,7 +21189,7 @@
         <v>0.80560138177575824</v>
       </c>
       <c r="AK87" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="88" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -21282,7 +21311,7 @@
         <v>0.54663577278738729</v>
       </c>
       <c r="AK88" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="89" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -21404,7 +21433,7 @@
         <v>0.69596387979478203</v>
       </c>
       <c r="AK89" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="90" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -21526,7 +21555,7 @@
         <v>0.80889517214691353</v>
       </c>
       <c r="AK90" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="91" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -21648,7 +21677,7 @@
         <v>1</v>
       </c>
       <c r="AK91" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="92" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -21770,7 +21799,7 @@
         <v>0.72584027281203278</v>
       </c>
       <c r="AK92" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="93" spans="1:37" x14ac:dyDescent="0.3">
@@ -21892,7 +21921,7 @@
         <v>0.78843905350643284</v>
       </c>
       <c r="AK93" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="94" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22014,7 +22043,7 @@
         <v>0.87304597202251155</v>
       </c>
       <c r="AK94" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="95" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22136,7 +22165,7 @@
         <v>0.74467671282929093</v>
       </c>
       <c r="AK95" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="96" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22258,7 +22287,7 @@
         <v>0.34004888919630283</v>
       </c>
       <c r="AK96" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="97" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22380,7 +22409,7 @@
         <v>0.85535390644234766</v>
       </c>
       <c r="AK97" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="98" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22502,7 +22531,7 @@
         <v>0.77668678646459133</v>
       </c>
       <c r="AK98" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="99" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22624,7 +22653,7 @@
         <v>0.98200279586540884</v>
       </c>
       <c r="AK99" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="100" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22746,7 +22775,7 @@
         <v>0.99140499756573175</v>
       </c>
       <c r="AK100" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="101" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22868,7 +22897,7 @@
         <v>0.89876701344048993</v>
       </c>
       <c r="AK101" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="102" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -22990,7 +23019,7 @@
         <v>0.73572325398675043</v>
       </c>
       <c r="AK102" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="103" spans="1:37" x14ac:dyDescent="0.3">
@@ -23112,7 +23141,7 @@
         <v>0.9014296604554024</v>
       </c>
       <c r="AK103" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="104" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -23234,7 +23263,7 @@
         <v>0.98994367940648209</v>
       </c>
       <c r="AK104" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="105" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -23356,7 +23385,7 @@
         <v>0.94288661816451902</v>
       </c>
       <c r="AK105" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="106" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -23478,7 +23507,7 @@
         <v>0.75600805841085594</v>
       </c>
       <c r="AK106" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="107" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -23600,7 +23629,7 @@
         <v>0.76414371365953782</v>
       </c>
       <c r="AK107" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="108" spans="1:37" x14ac:dyDescent="0.3">
@@ -23722,7 +23751,7 @@
         <v>0.11917329138193365</v>
       </c>
       <c r="AK108" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="109" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -23844,7 +23873,7 @@
         <v>0.77035394952188618</v>
       </c>
       <c r="AK109" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="110" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -23966,7 +23995,7 @@
         <v>1</v>
       </c>
       <c r="AK110" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="111" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -24088,7 +24117,7 @@
         <v>0.46992455690726237</v>
       </c>
       <c r="AK111" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="112" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -24210,7 +24239,7 @@
         <v>0.8661699742090343</v>
       </c>
       <c r="AK112" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="113" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -24332,7 +24361,7 @@
         <v>0.89033284305949667</v>
       </c>
       <c r="AK113" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="114" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -24454,7 +24483,7 @@
         <v>0.82938000240517451</v>
       </c>
       <c r="AK114" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="115" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -24576,7 +24605,7 @@
         <v>0.44819380139008802</v>
       </c>
       <c r="AK115" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="116" spans="1:37" x14ac:dyDescent="0.3">
@@ -24698,7 +24727,7 @@
         <v>0.59226283959165005</v>
       </c>
       <c r="AK116" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="117" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -24820,7 +24849,7 @@
         <v>0.72440349017239358</v>
       </c>
       <c r="AK117" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="118" spans="1:37" x14ac:dyDescent="0.3">
@@ -24942,7 +24971,7 @@
         <v>0.18642415725740188</v>
       </c>
       <c r="AK118" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="119" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -25064,7 +25093,7 @@
         <v>0.74589771408301653</v>
       </c>
       <c r="AK119" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="120" spans="1:37" x14ac:dyDescent="0.3">
@@ -25186,7 +25215,7 @@
         <v>0.27981747008972768</v>
       </c>
       <c r="AK120" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="121" spans="1:37" x14ac:dyDescent="0.3">
@@ -25308,7 +25337,7 @@
         <v>0.44804616680036363</v>
       </c>
       <c r="AK121" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="122" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -25430,7 +25459,7 @@
         <v>0.96758386349295888</v>
       </c>
       <c r="AK122" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="123" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -25552,7 +25581,7 @@
         <v>0.72843594676968892</v>
       </c>
       <c r="AK123" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="124" spans="1:37" x14ac:dyDescent="0.3">
@@ -25674,7 +25703,7 @@
         <v>0.99702850277831634</v>
       </c>
       <c r="AK124" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="125" spans="1:37" x14ac:dyDescent="0.3">
@@ -25796,7 +25825,7 @@
         <v>1</v>
       </c>
       <c r="AK125" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="126" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -25918,7 +25947,7 @@
         <v>0.66228584692790315</v>
       </c>
       <c r="AK126" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="127" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -26040,7 +26069,7 @@
         <v>0.76360573085382855</v>
       </c>
       <c r="AK127" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="128" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -26162,7 +26191,7 @@
         <v>0.74529257372965163</v>
       </c>
       <c r="AK128" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="129" spans="1:37" x14ac:dyDescent="0.3">
@@ -26284,7 +26313,7 @@
         <v>0.77509698342872879</v>
       </c>
       <c r="AK129" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="130" spans="1:37" x14ac:dyDescent="0.3">
@@ -26406,7 +26435,7 @@
         <v>0.79762913990660789</v>
       </c>
       <c r="AK130" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="131" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -26528,7 +26557,7 @@
         <v>0.87730649726841847</v>
       </c>
       <c r="AK131" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="132" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -26650,7 +26679,7 @@
         <v>0.74303894532695136</v>
       </c>
       <c r="AK132" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="133" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -26772,7 +26801,7 @@
         <v>0.55460697478630516</v>
       </c>
       <c r="AK133" s="11" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="134" spans="1:37" x14ac:dyDescent="0.3">
@@ -26894,7 +26923,7 @@
         <v>1.1148601794389756E-2</v>
       </c>
       <c r="AK134" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="135" spans="1:37" x14ac:dyDescent="0.3">
@@ -27016,7 +27045,7 @@
         <v>0.82989044529528611</v>
       </c>
       <c r="AK135" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="136" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -27138,7 +27167,7 @@
         <v>0.64650089722677051</v>
       </c>
       <c r="AK136" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="137" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -27260,7 +27289,7 @@
         <v>0.88308986235111508</v>
       </c>
       <c r="AK137" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="138" spans="1:37" x14ac:dyDescent="0.3">
@@ -27382,7 +27411,7 @@
         <v>0.90288375654538056</v>
       </c>
       <c r="AK138" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="139" spans="1:37" x14ac:dyDescent="0.3">
@@ -27504,7 +27533,7 @@
         <v>0.78425003774534707</v>
       </c>
       <c r="AK139" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="140" spans="1:37" x14ac:dyDescent="0.3">
@@ -27626,7 +27655,7 @@
         <v>0.94068840365698758</v>
       </c>
       <c r="AK140" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="141" spans="1:37" x14ac:dyDescent="0.3">
@@ -27748,7 +27777,7 @@
         <v>0.95264796437226296</v>
       </c>
       <c r="AK141" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="142" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -27870,7 +27899,7 @@
         <v>0.6857952178822132</v>
       </c>
       <c r="AK142" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="143" spans="1:37" x14ac:dyDescent="0.3">
@@ -27992,7 +28021,7 @@
         <v>0.89459879491727434</v>
       </c>
       <c r="AK143" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="144" spans="1:37" x14ac:dyDescent="0.3">
@@ -28114,7 +28143,7 @@
         <v>0.99129225346909133</v>
       </c>
       <c r="AK144" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="145" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -28236,7 +28265,7 @@
         <v>0.57120501580949157</v>
       </c>
       <c r="AK145" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="146" spans="1:37" x14ac:dyDescent="0.3">
@@ -28358,7 +28387,7 @@
         <v>0.95690379138433124</v>
       </c>
       <c r="AK146" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="147" spans="1:37" x14ac:dyDescent="0.3">
@@ -28480,7 +28509,7 @@
         <v>0.5992467135623597</v>
       </c>
       <c r="AK147" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="148" spans="1:37" x14ac:dyDescent="0.3">
@@ -28602,7 +28631,7 @@
         <v>0.96788625629390646</v>
       </c>
       <c r="AK148" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="149" spans="1:37" x14ac:dyDescent="0.3">
@@ -28724,7 +28753,7 @@
         <v>0.64725014717907636</v>
       </c>
       <c r="AK149" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="150" spans="1:37" x14ac:dyDescent="0.3">
@@ -28846,7 +28875,7 @@
         <v>0.97863441842570087</v>
       </c>
       <c r="AK150" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="151" spans="1:37" x14ac:dyDescent="0.3">
@@ -28968,7 +28997,7 @@
         <v>0.9141815219703836</v>
       </c>
       <c r="AK151" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="152" spans="1:37" x14ac:dyDescent="0.3">
@@ -29090,7 +29119,7 @@
         <v>0.69551360878634616</v>
       </c>
       <c r="AK152" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="153" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -29212,7 +29241,7 @@
         <v>0.63205684055564271</v>
       </c>
       <c r="AK153" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="154" spans="1:37" x14ac:dyDescent="0.3">
@@ -29334,7 +29363,7 @@
         <v>0.56258695032472161</v>
       </c>
       <c r="AK154" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="155" spans="1:37" x14ac:dyDescent="0.3">
@@ -29456,7 +29485,7 @@
         <v>0.60647770980031401</v>
       </c>
       <c r="AK155" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="156" spans="1:37" x14ac:dyDescent="0.3">
@@ -29578,7 +29607,7 @@
         <v>0.97590778881521356</v>
       </c>
       <c r="AK156" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="157" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -29700,7 +29729,7 @@
         <v>0.69404183018202681</v>
       </c>
       <c r="AK157" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="158" spans="1:37" x14ac:dyDescent="0.3">
@@ -29822,7 +29851,7 @@
         <v>0.94883006409739856</v>
       </c>
       <c r="AK158" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="159" spans="1:37" x14ac:dyDescent="0.3">
@@ -29944,7 +29973,7 @@
         <v>0.87715172017078769</v>
       </c>
       <c r="AK159" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="160" spans="1:37" x14ac:dyDescent="0.3">
@@ -30066,7 +30095,7 @@
         <v>0.41362973586744844</v>
       </c>
       <c r="AK160" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="161" spans="1:37" x14ac:dyDescent="0.3">
@@ -30188,7 +30217,7 @@
         <v>0.69138359325162047</v>
       </c>
       <c r="AK161" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="162" spans="1:37" x14ac:dyDescent="0.3">
@@ -30310,7 +30339,7 @@
         <v>0.83504039662567464</v>
       </c>
       <c r="AK162" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="163" spans="1:37" x14ac:dyDescent="0.3">
@@ -30432,7 +30461,7 @@
         <v>0.79855005393564804</v>
       </c>
       <c r="AK163" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="164" spans="1:37" x14ac:dyDescent="0.3">
@@ -30554,7 +30583,7 @@
         <v>0.99097887158722364</v>
       </c>
       <c r="AK164" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="165" spans="1:37" x14ac:dyDescent="0.3">
@@ -30676,7 +30705,7 @@
         <v>0.77618660764499126</v>
       </c>
       <c r="AK165" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="166" spans="1:37" x14ac:dyDescent="0.3">
@@ -30798,7 +30827,7 @@
         <v>0.40654615892077889</v>
       </c>
       <c r="AK166" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="167" spans="1:37" x14ac:dyDescent="0.3">
@@ -30920,7 +30949,7 @@
         <v>0.8630672187769437</v>
       </c>
       <c r="AK167" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="168" spans="1:37" x14ac:dyDescent="0.3">
@@ -31042,7 +31071,7 @@
         <v>0.81743256692218247</v>
       </c>
       <c r="AK168" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="169" spans="1:37" x14ac:dyDescent="0.3">
@@ -31164,7 +31193,7 @@
         <v>0.88810959402900624</v>
       </c>
       <c r="AK169" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="170" spans="1:37" x14ac:dyDescent="0.3">
@@ -31286,7 +31315,7 @@
         <v>0.88016999174842303</v>
       </c>
       <c r="AK170" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="171" spans="1:37" x14ac:dyDescent="0.3">
@@ -31408,7 +31437,7 @@
         <v>0.83438161214834594</v>
       </c>
       <c r="AK171" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="172" spans="1:37" x14ac:dyDescent="0.3">
@@ -31530,7 +31559,7 @@
         <v>0.94645483310893763</v>
       </c>
       <c r="AK172" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="173" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -31652,7 +31681,7 @@
         <v>0.90794088508830595</v>
       </c>
       <c r="AK173" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="174" spans="1:37" x14ac:dyDescent="0.3">
@@ -31774,7 +31803,7 @@
         <v>0.43106742597182102</v>
       </c>
       <c r="AK174" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="175" spans="1:37" x14ac:dyDescent="0.3">
@@ -31896,7 +31925,7 @@
         <v>0.27212069689283225</v>
       </c>
       <c r="AK175" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="176" spans="1:37" x14ac:dyDescent="0.3">
@@ -32018,7 +32047,7 @@
         <v>0.78023149312354678</v>
       </c>
       <c r="AK176" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="177" spans="1:37" x14ac:dyDescent="0.3">
@@ -32140,7 +32169,7 @@
         <v>0.99041437352725381</v>
       </c>
       <c r="AK177" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="178" spans="1:37" x14ac:dyDescent="0.3">
@@ -32262,7 +32291,7 @@
         <v>0.79063378265517725</v>
       </c>
       <c r="AK178" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="179" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -32384,7 +32413,7 @@
         <v>0.95277023221985879</v>
       </c>
       <c r="AK179" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="180" spans="1:37" x14ac:dyDescent="0.3">
@@ -32506,7 +32535,7 @@
         <v>0.83482550275591905</v>
       </c>
       <c r="AK180" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="181" spans="1:37" x14ac:dyDescent="0.3">
@@ -32628,7 +32657,7 @@
         <v>0.9038777122150079</v>
       </c>
       <c r="AK181" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="182" spans="1:37" x14ac:dyDescent="0.3">
@@ -32750,7 +32779,7 @@
         <v>0.91693580897647453</v>
       </c>
       <c r="AK182" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="183" spans="1:37" x14ac:dyDescent="0.3">
@@ -32872,7 +32901,7 @@
         <v>0.8576677944722485</v>
       </c>
       <c r="AK183" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="184" spans="1:37" x14ac:dyDescent="0.3">
@@ -32994,7 +33023,7 @@
         <v>0.4456159191830969</v>
       </c>
       <c r="AK184" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="185" spans="1:37" x14ac:dyDescent="0.3">
@@ -33116,7 +33145,7 @@
         <v>0.96858343139567948</v>
       </c>
       <c r="AK185" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="186" spans="1:37" x14ac:dyDescent="0.3">
@@ -33238,7 +33267,7 @@
         <v>0.9974800992745394</v>
       </c>
       <c r="AK186" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="187" spans="1:37" x14ac:dyDescent="0.3">
@@ -33360,7 +33389,7 @@
         <v>1</v>
       </c>
       <c r="AK187" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="188" spans="1:37" x14ac:dyDescent="0.3">
@@ -33482,7 +33511,7 @@
         <v>0.73188621905995144</v>
       </c>
       <c r="AK188" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="189" spans="1:37" x14ac:dyDescent="0.3">
@@ -33604,7 +33633,7 @@
         <v>0.73438428564287628</v>
       </c>
       <c r="AK189" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="190" spans="1:37" x14ac:dyDescent="0.3">
@@ -33726,7 +33755,7 @@
         <v>0.44325426569898102</v>
       </c>
       <c r="AK190" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="191" spans="1:37" x14ac:dyDescent="0.3">
@@ -33848,7 +33877,7 @@
         <v>0.73968703677099323</v>
       </c>
       <c r="AK191" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="192" spans="1:37" x14ac:dyDescent="0.3">
@@ -33970,7 +33999,7 @@
         <v>0.99025140633637521</v>
       </c>
       <c r="AK192" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="193" spans="1:37" x14ac:dyDescent="0.3">
@@ -34092,7 +34121,7 @@
         <v>0.69657998817120104</v>
       </c>
       <c r="AK193" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="194" spans="1:37" x14ac:dyDescent="0.3">
@@ -34214,7 +34243,7 @@
         <v>0.66879736590144656</v>
       </c>
       <c r="AK194" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="195" spans="1:37" x14ac:dyDescent="0.3">
@@ -34336,7 +34365,7 @@
         <v>0.27214615409631898</v>
       </c>
       <c r="AK195" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="196" spans="1:37" x14ac:dyDescent="0.3">
@@ -34458,7 +34487,7 @@
         <v>0.61875191456121259</v>
       </c>
       <c r="AK196" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="197" spans="1:37" x14ac:dyDescent="0.3">
@@ -34580,7 +34609,7 @@
         <v>0.66985413567345276</v>
       </c>
       <c r="AK197" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="198" spans="1:37" x14ac:dyDescent="0.3">
@@ -34702,7 +34731,7 @@
         <v>0.29695858971858091</v>
       </c>
       <c r="AK198" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="199" spans="1:37" x14ac:dyDescent="0.3">
@@ -34824,7 +34853,7 @@
         <v>0.99998687682999221</v>
       </c>
       <c r="AK199" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="200" spans="1:37" x14ac:dyDescent="0.3">
@@ -34946,7 +34975,7 @@
         <v>1</v>
       </c>
       <c r="AK200" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="201" spans="1:37" x14ac:dyDescent="0.3">
@@ -35068,7 +35097,7 @@
         <v>0.70789482111681767</v>
       </c>
       <c r="AK201" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="202" spans="1:37" x14ac:dyDescent="0.3">
@@ -35190,7 +35219,7 @@
         <v>0.4140183808428396</v>
       </c>
       <c r="AK202" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="203" spans="1:37" x14ac:dyDescent="0.3">
@@ -35312,7 +35341,7 @@
         <v>0.82408033142231429</v>
       </c>
       <c r="AK203" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="204" spans="1:37" x14ac:dyDescent="0.3">
@@ -35434,7 +35463,7 @@
         <v>0.27454081088373905</v>
       </c>
       <c r="AK204" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="205" spans="1:37" x14ac:dyDescent="0.3">
@@ -35556,7 +35585,7 @@
         <v>1</v>
       </c>
       <c r="AK205" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="206" spans="1:37" x14ac:dyDescent="0.3">
@@ -35678,7 +35707,7 @@
         <v>8.3721815991908408E-2</v>
       </c>
       <c r="AK206" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="207" spans="1:37" x14ac:dyDescent="0.3">
@@ -35800,7 +35829,7 @@
         <v>0.93951241602194369</v>
       </c>
       <c r="AK207" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="208" spans="1:37" x14ac:dyDescent="0.3">
@@ -35922,7 +35951,7 @@
         <v>0.48131339107073179</v>
       </c>
       <c r="AK208" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="209" spans="1:37" x14ac:dyDescent="0.3">
@@ -36044,7 +36073,7 @@
         <v>0.66426360696024267</v>
       </c>
       <c r="AK209" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="210" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -36166,7 +36195,7 @@
         <v>0.53913788228157977</v>
       </c>
       <c r="AK210" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="211" spans="1:37" x14ac:dyDescent="0.3">
@@ -36288,7 +36317,7 @@
         <v>0.26697880939131335</v>
       </c>
       <c r="AK211" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="212" spans="1:37" x14ac:dyDescent="0.3">
@@ -36410,7 +36439,7 @@
         <v>0.91290180199163007</v>
       </c>
       <c r="AK212" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="213" spans="1:37" x14ac:dyDescent="0.3">
@@ -36532,7 +36561,7 @@
         <v>0.89116434230644492</v>
       </c>
       <c r="AK213" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="214" spans="1:37" x14ac:dyDescent="0.3">
@@ -36654,7 +36683,7 @@
         <v>0.82534841936255054</v>
       </c>
       <c r="AK214" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="215" spans="1:37" x14ac:dyDescent="0.3">
@@ -36776,7 +36805,7 @@
         <v>0.52783322999639759</v>
       </c>
       <c r="AK215" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="216" spans="1:37" x14ac:dyDescent="0.3">
@@ -36898,7 +36927,7 @@
         <v>0.75362836563829017</v>
       </c>
       <c r="AK216" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="217" spans="1:37" x14ac:dyDescent="0.3">
@@ -37020,7 +37049,7 @@
         <v>0.64135166145354661</v>
       </c>
       <c r="AK217" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="218" spans="1:37" x14ac:dyDescent="0.3">
@@ -37142,7 +37171,7 @@
         <v>0.54546892599895813</v>
       </c>
       <c r="AK218" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="219" spans="1:37" x14ac:dyDescent="0.3">
@@ -37264,7 +37293,7 @@
         <v>0.70063201640157213</v>
       </c>
       <c r="AK219" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="220" spans="1:37" x14ac:dyDescent="0.3">
@@ -37386,7 +37415,7 @@
         <v>0.1704418198179628</v>
       </c>
       <c r="AK220" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="221" spans="1:37" x14ac:dyDescent="0.3">
@@ -37508,7 +37537,7 @@
         <v>0.83238626274105909</v>
       </c>
       <c r="AK221" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="222" spans="1:37" x14ac:dyDescent="0.3">
@@ -37630,7 +37659,7 @@
         <v>0.43344106149715961</v>
       </c>
       <c r="AK222" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="223" spans="1:37" x14ac:dyDescent="0.3">
@@ -37752,7 +37781,7 @@
         <v>0.29633536866342375</v>
       </c>
       <c r="AK223" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="224" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -37874,7 +37903,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK224" s="11" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="225" spans="1:37" x14ac:dyDescent="0.3">
@@ -37996,7 +38025,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK225" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="226" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -38118,7 +38147,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK226" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="227" spans="1:37" x14ac:dyDescent="0.3">
@@ -38240,7 +38269,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK227" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="228" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -38362,7 +38391,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK228" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="229" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -38484,7 +38513,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK229" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="230" spans="1:37" x14ac:dyDescent="0.3">
@@ -38606,7 +38635,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK230" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="231" spans="1:37" x14ac:dyDescent="0.3">
@@ -38728,7 +38757,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK231" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="232" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -38850,7 +38879,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK232" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="233" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -38972,7 +39001,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK233" s="11" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="234" spans="1:37" x14ac:dyDescent="0.3">
@@ -39094,7 +39123,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK234" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="235" spans="1:37" x14ac:dyDescent="0.3">
@@ -39216,7 +39245,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK235" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="236" spans="1:37" x14ac:dyDescent="0.3">
@@ -39338,7 +39367,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK236" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="237" spans="1:37" x14ac:dyDescent="0.3">
@@ -39460,7 +39489,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK237" s="11" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="238" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -39582,7 +39611,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK238" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="239" spans="1:37" hidden="1" x14ac:dyDescent="0.3">
@@ -39704,7 +39733,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="AK239" s="11" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
   </sheetData>
@@ -39911,16 +39940,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="B1" t="s">
-        <v>3067</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="13" t="s">
-        <v>2858</v>
+        <v>2856</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -39939,7 +39968,7 @@
         <v>2370412440</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -39947,7 +39976,7 @@
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="45" t="s">
-        <v>2859</v>
+        <v>2857</v>
       </c>
       <c r="D8" s="10"/>
     </row>
@@ -39956,28 +39985,28 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10" s="43" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="C10" s="78">
         <v>1009</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>2861</v>
+        <v>2859</v>
       </c>
       <c r="E10" s="82" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11" s="43" t="s">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="C11" s="71">
         <f>C10/1000</f>
         <v>1.0089999999999999</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -39988,10 +40017,10 @@
         <v>0.95</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>2864</v>
+        <v>2862</v>
       </c>
       <c r="E12" s="82" t="s">
-        <v>2865</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -40003,7 +40032,7 @@
         <v>0.9585499999999999</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>2863</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -40011,16 +40040,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="43" t="s">
-        <v>2866</v>
+        <v>2864</v>
       </c>
       <c r="C15" s="79">
         <v>4</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="E15" s="82" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -40028,7 +40057,7 @@
     </row>
     <row r="17" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="45" t="s">
-        <v>2868</v>
+        <v>2866</v>
       </c>
       <c r="D17" s="10"/>
     </row>
@@ -40037,54 +40066,54 @@
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="43" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="C19" s="78">
         <v>646</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="E19" s="82" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="43" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
       <c r="C20" s="78">
         <v>513</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>2870</v>
+        <v>2868</v>
       </c>
       <c r="E20" s="82" t="s">
-        <v>2862</v>
+        <v>2860</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="43" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="C21" s="71">
         <f>C19/1000</f>
         <v>0.64600000000000002</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="43" t="s">
-        <v>2871</v>
+        <v>2869</v>
       </c>
       <c r="C22" s="71">
         <f>C20/1000</f>
         <v>0.51300000000000001</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>2872</v>
+        <v>2870</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
@@ -40092,16 +40121,16 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="43" t="s">
-        <v>2873</v>
+        <v>2871</v>
       </c>
       <c r="C24" s="79">
         <v>3.4</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="E24" s="82" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
@@ -40119,30 +40148,30 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="43" t="s">
-        <v>2874</v>
+        <v>2872</v>
       </c>
       <c r="C28" s="79">
         <v>10</v>
       </c>
       <c r="D28" s="74" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="E28" s="82" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="43" t="s">
-        <v>2875</v>
+        <v>2873</v>
       </c>
       <c r="C29" s="79">
         <v>3</v>
       </c>
       <c r="D29" s="74" t="s">
-        <v>2867</v>
+        <v>2865</v>
       </c>
       <c r="E29" s="82" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
@@ -40163,61 +40192,61 @@
         <v>1049281862</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>3034</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="46" t="s">
-        <v>2876</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>2877</v>
+        <v>2875</v>
       </c>
       <c r="D36" s="75"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="43" t="s">
-        <v>2878</v>
+        <v>2876</v>
       </c>
       <c r="C37" s="79">
         <v>12.010999999999999</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="E37" s="82" t="s">
-        <v>2880</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="43" t="s">
-        <v>2881</v>
+        <v>2879</v>
       </c>
       <c r="C38" s="79">
         <v>15.999000000000001</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="E38" s="82" t="s">
-        <v>2880</v>
+        <v>2878</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="43" t="s">
-        <v>2882</v>
+        <v>2880</v>
       </c>
       <c r="C39" s="79">
         <v>1.008</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="E39" s="82" t="s">
-        <v>2883</v>
+        <v>2881</v>
       </c>
     </row>
   </sheetData>
@@ -40231,7 +40260,7 @@
   <dimension ref="A1:AF107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
     <col min="2" max="2" width="16.88671875" customWidth="1"/>
     <col min="3" max="3" width="9.21875" customWidth="1"/>
     <col min="4" max="4" width="40.5546875" customWidth="1"/>
@@ -40248,122 +40277,131 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="B1" t="s">
-        <v>2884</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3063</v>
-      </c>
-      <c r="B2" s="91" t="s">
+        <v>3061</v>
+      </c>
+      <c r="B2" s="90" t="s">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="50" t="s">
+        <v>3072</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="F4" s="92" t="s">
+        <v>705</v>
+      </c>
+      <c r="G4" s="92"/>
+      <c r="I4" s="47" t="s">
         <v>3071</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="F4" s="90" t="s">
-        <v>705</v>
-      </c>
-      <c r="G4" s="90"/>
-      <c r="I4" s="47"/>
       <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:31" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="57" t="s">
-        <v>3058</v>
+      <c r="A5" s="91" t="s">
+        <v>3056</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>2883</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>2884</v>
+      </c>
+      <c r="E5" s="57" t="s">
         <v>2885</v>
       </c>
-      <c r="C5" s="57" t="s">
-        <v>2810</v>
-      </c>
-      <c r="D5" s="57" t="s">
+      <c r="F5" s="57" t="s">
+        <v>3033</v>
+      </c>
+      <c r="G5" s="57" t="s">
+        <v>3034</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>3057</v>
+      </c>
+      <c r="I5" s="91" t="s">
+        <v>3070</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>2617</v>
+      </c>
+      <c r="K5" s="57" t="s">
         <v>2886</v>
       </c>
-      <c r="E5" s="57" t="s">
+      <c r="L5" s="57" t="s">
         <v>2887</v>
       </c>
-      <c r="F5" s="57" t="s">
+      <c r="M5" s="57" t="s">
+        <v>2888</v>
+      </c>
+      <c r="N5" s="57" t="s">
+        <v>2889</v>
+      </c>
+      <c r="O5" s="62" t="s">
+        <v>2890</v>
+      </c>
+      <c r="P5" s="57" t="s">
         <v>3035</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="Q5" s="57" t="s">
         <v>3036</v>
       </c>
-      <c r="H5" s="57" t="s">
-        <v>3059</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>2617</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>2618</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>2888</v>
-      </c>
-      <c r="L5" s="57" t="s">
-        <v>2889</v>
-      </c>
-      <c r="M5" s="57" t="s">
-        <v>2890</v>
-      </c>
-      <c r="N5" s="57" t="s">
-        <v>2891</v>
-      </c>
-      <c r="O5" s="57" t="s">
-        <v>2892</v>
-      </c>
-      <c r="P5" s="57" t="s">
-        <v>3037</v>
-      </c>
-      <c r="Q5" s="57" t="s">
+      <c r="R5" s="57" t="s">
         <v>3038</v>
       </c>
-      <c r="R5" s="57" t="s">
+      <c r="S5" s="57" t="s">
+        <v>3039</v>
+      </c>
+      <c r="T5" s="57" t="s">
+        <v>3048</v>
+      </c>
+      <c r="U5" s="62" t="s">
+        <v>3049</v>
+      </c>
+      <c r="V5" s="57" t="s">
+        <v>3041</v>
+      </c>
+      <c r="W5" s="57" t="s">
+        <v>3042</v>
+      </c>
+      <c r="X5" s="57" t="s">
         <v>3040</v>
       </c>
-      <c r="S5" s="57" t="s">
-        <v>3041</v>
-      </c>
-      <c r="T5" s="57" t="s">
+      <c r="Y5" s="57" t="s">
+        <v>3046</v>
+      </c>
+      <c r="Z5" s="57" t="s">
         <v>3050</v>
       </c>
-      <c r="U5" s="62" t="s">
+      <c r="AA5" s="57" t="s">
         <v>3051</v>
       </c>
-      <c r="V5" s="57" t="s">
-        <v>3043</v>
-      </c>
-      <c r="W5" s="57" t="s">
-        <v>3044</v>
-      </c>
-      <c r="X5" s="57" t="s">
-        <v>3042</v>
-      </c>
-      <c r="Y5" s="57" t="s">
-        <v>3048</v>
-      </c>
-      <c r="Z5" s="57" t="s">
-        <v>3052</v>
-      </c>
-      <c r="AA5" s="57" t="s">
+      <c r="AB5" s="57" t="s">
         <v>3053</v>
       </c>
-      <c r="AB5" s="57" t="s">
-        <v>3055</v>
-      </c>
       <c r="AC5" s="57" t="s">
-        <v>3056</v>
+        <v>3054</v>
       </c>
       <c r="AD5" s="57" t="s">
-        <v>3069</v>
+        <v>3067</v>
       </c>
       <c r="AE5" s="57" t="s">
-        <v>3070</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
@@ -40374,13 +40412,13 @@
         <v>614</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>2811</v>
+        <v>2809</v>
       </c>
       <c r="D6" t="s">
         <v>615</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>2893</v>
+        <v>2891</v>
       </c>
       <c r="F6" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B6, prodcom_data[product], 0))</f>
@@ -40395,29 +40433,29 @@
         <v>0.86402104863567564</v>
       </c>
       <c r="I6" s="49" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K6" s="79" t="s">
-        <v>2894</v>
+        <v>2892</v>
       </c>
       <c r="L6" s="79">
         <v>42.081000000000003</v>
       </c>
       <c r="M6" s="80" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="N6" s="72">
         <f>M6*Calculations!$C$37/L6</f>
         <v>0.85627717972481643</v>
       </c>
-      <c r="O6" s="82" t="s">
-        <v>2896</v>
+      <c r="O6" s="81" t="s">
+        <v>2894</v>
       </c>
       <c r="P6" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q6" s="58">
         <v>1</v>
@@ -40427,7 +40465,7 @@
       <c r="T6" s="59"/>
       <c r="U6" s="63"/>
       <c r="V6" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W6" s="58">
         <v>1</v>
@@ -40449,7 +40487,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>2812</v>
+        <v>2810</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -40470,29 +40508,29 @@
         <v>0.87904863332422545</v>
       </c>
       <c r="I7" s="49" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K7" s="79" t="s">
-        <v>2900</v>
+        <v>2898</v>
       </c>
       <c r="L7" s="79">
         <v>28.05</v>
       </c>
       <c r="M7" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N7" s="72">
         <f>M7*Calculations!$C$37/L7</f>
         <v>0.85639928698752221</v>
       </c>
-      <c r="O7" s="82" t="s">
-        <v>2902</v>
+      <c r="O7" s="81" t="s">
+        <v>2900</v>
       </c>
       <c r="P7" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q7" s="58">
         <v>1</v>
@@ -40502,7 +40540,7 @@
       <c r="T7" s="59"/>
       <c r="U7" s="63"/>
       <c r="V7" s="59" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="W7" s="58">
         <v>1</v>
@@ -40524,13 +40562,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>2812</v>
+        <v>2810</v>
       </c>
       <c r="D8" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>2897</v>
+        <v>2895</v>
       </c>
       <c r="F8" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B8, prodcom_data[product], 0))</f>
@@ -40545,29 +40583,29 @@
         <v>0.94409418582769256</v>
       </c>
       <c r="I8" s="49" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K8" s="79" t="s">
-        <v>2898</v>
+        <v>2896</v>
       </c>
       <c r="L8" s="79">
         <v>42.08</v>
       </c>
       <c r="M8" s="80" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="N8" s="72">
         <f>M8*Calculations!$C$37/L8</f>
         <v>0.85629752851711038</v>
       </c>
-      <c r="O8" s="82" t="s">
-        <v>2899</v>
+      <c r="O8" s="81" t="s">
+        <v>2897</v>
       </c>
       <c r="P8" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q8" s="58">
         <v>1</v>
@@ -40577,7 +40615,7 @@
       <c r="T8" s="59"/>
       <c r="U8" s="63"/>
       <c r="V8" s="59" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="W8" s="58">
         <v>1</v>
@@ -40599,13 +40637,13 @@
         <v>539</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>2813</v>
+        <v>2811</v>
       </c>
       <c r="D9" t="s">
         <v>540</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="F9" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B9, prodcom_data[product], 0))</f>
@@ -40620,29 +40658,29 @@
         <v>0.78369292184089345</v>
       </c>
       <c r="I9" s="49" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K9" s="79" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="L9" s="79">
         <v>28.053999999999998</v>
       </c>
       <c r="M9" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N9" s="72">
         <f>M9*Calculations!$C$37/L9</f>
         <v>0.85627717972481643</v>
       </c>
-      <c r="O9" s="82" t="s">
-        <v>2905</v>
+      <c r="O9" s="81" t="s">
+        <v>2903</v>
       </c>
       <c r="P9" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q9" s="58">
         <v>1</v>
@@ -40652,7 +40690,7 @@
       <c r="T9" s="59"/>
       <c r="U9" s="63"/>
       <c r="V9" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W9" s="58">
         <v>1</v>
@@ -40674,13 +40712,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="89" t="s">
-        <v>3068</v>
+        <v>3066</v>
       </c>
       <c r="D10" t="s">
         <v>112</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>2906</v>
+        <v>2904</v>
       </c>
       <c r="F10" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B10, prodcom_data[product], 0))</f>
@@ -40695,54 +40733,54 @@
         <v>0.14193164800139446</v>
       </c>
       <c r="I10" s="49" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K10" s="79" t="s">
-        <v>2907</v>
+        <v>2905</v>
       </c>
       <c r="L10" s="79">
         <v>32.042000000000002</v>
       </c>
       <c r="M10" s="80" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="N10" s="72">
         <f>M10*Calculations!$C$37/L10</f>
         <v>0.3748517570688471</v>
       </c>
-      <c r="O10" s="82" t="s">
-        <v>2909</v>
+      <c r="O10" s="81" t="s">
+        <v>2907</v>
       </c>
       <c r="P10" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q10" s="58">
         <v>0.35</v>
       </c>
       <c r="R10" s="59" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
       <c r="S10" s="58">
         <v>0.23</v>
       </c>
       <c r="T10" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="U10" s="61">
         <f>1-Q10-S10</f>
         <v>0.42000000000000004</v>
       </c>
       <c r="V10" s="59" t="s">
-        <v>3049</v>
+        <v>3045</v>
       </c>
       <c r="W10" s="58">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="X10" s="59" t="s">
-        <v>3054</v>
+        <v>3052</v>
       </c>
       <c r="Y10" s="58">
         <v>0.21</v>
@@ -40751,16 +40789,16 @@
         <v>3047</v>
       </c>
       <c r="AA10" s="58">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="AB10" s="59" t="s">
-        <v>3057</v>
+        <v>3055</v>
       </c>
       <c r="AC10" s="60">
         <v>0.16</v>
       </c>
       <c r="AD10" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="AE10" s="61" cm="1">
         <f t="array" ref="AE10">1-SUM(IF(ISNUMBER(V10:AC10), V10:AC10, 0))</f>
@@ -40775,7 +40813,7 @@
         <v>34</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>2815</v>
+        <v>2813</v>
       </c>
       <c r="D11" t="s">
         <v>35</v>
@@ -40796,29 +40834,29 @@
         <v>0.88287081478020857</v>
       </c>
       <c r="I11" s="49" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="J11" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K11" s="79" t="s">
-        <v>2910</v>
+        <v>2908</v>
       </c>
       <c r="L11" s="79">
         <v>78.11</v>
       </c>
       <c r="M11" s="80" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="N11" s="72">
         <f>M11*Calculations!$C$37/L11</f>
         <v>0.92262194341313541</v>
       </c>
-      <c r="O11" s="82" t="s">
-        <v>2912</v>
+      <c r="O11" s="81" t="s">
+        <v>2910</v>
       </c>
       <c r="P11" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q11" s="58">
         <v>1</v>
@@ -40828,7 +40866,7 @@
       <c r="T11" s="59"/>
       <c r="U11" s="63"/>
       <c r="V11" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W11" s="58">
         <v>1</v>
@@ -40850,13 +40888,13 @@
         <v>563</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>2816</v>
+        <v>2814</v>
       </c>
       <c r="D12" t="s">
         <v>564</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="F12" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B12, prodcom_data[product], 0))</f>
@@ -40871,29 +40909,29 @@
         <v>0.89272188364169869</v>
       </c>
       <c r="I12" s="49" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K12" s="79" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="L12" s="79">
         <v>62.5</v>
       </c>
       <c r="M12" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N12" s="72">
         <f>M12*Calculations!$C$37/L12</f>
         <v>0.38435199999999997</v>
       </c>
-      <c r="O12" s="82" t="s">
-        <v>2915</v>
+      <c r="O12" s="81" t="s">
+        <v>2913</v>
       </c>
       <c r="P12" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q12" s="58">
         <v>1</v>
@@ -40903,7 +40941,7 @@
       <c r="T12" s="59"/>
       <c r="U12" s="63"/>
       <c r="V12" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W12" s="58">
         <v>1</v>
@@ -40925,13 +40963,13 @@
         <v>536</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>2814</v>
+        <v>2812</v>
       </c>
       <c r="D13" t="s">
         <v>537</v>
       </c>
       <c r="E13" s="48" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="F13" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B13, prodcom_data[product], 0))</f>
@@ -40946,29 +40984,29 @@
         <v>0.7961067883023123</v>
       </c>
       <c r="I13" s="49" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K13" s="79" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="L13" s="79">
         <v>28.053999999999998</v>
       </c>
       <c r="M13" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N13" s="72">
         <f>M13*Calculations!$C$37/L13</f>
         <v>0.85627717972481643</v>
       </c>
-      <c r="O13" s="82" t="s">
-        <v>2905</v>
+      <c r="O13" s="81" t="s">
+        <v>2903</v>
       </c>
       <c r="P13" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q13" s="58">
         <v>1</v>
@@ -40978,7 +41016,7 @@
       <c r="T13" s="59"/>
       <c r="U13" s="63"/>
       <c r="V13" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W13" s="58">
         <v>1</v>
@@ -41000,13 +41038,13 @@
         <v>533</v>
       </c>
       <c r="C14" s="64" t="s">
-        <v>2814</v>
+        <v>2812</v>
       </c>
       <c r="D14" t="s">
         <v>534</v>
       </c>
       <c r="E14" s="48" t="s">
-        <v>2903</v>
+        <v>2901</v>
       </c>
       <c r="F14" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B14, prodcom_data[product], 0))</f>
@@ -41021,29 +41059,29 @@
         <v>0.8225375065540016</v>
       </c>
       <c r="I14" s="49" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K14" s="79" t="s">
-        <v>2904</v>
+        <v>2902</v>
       </c>
       <c r="L14" s="79">
         <v>28.053999999999998</v>
       </c>
       <c r="M14" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N14" s="72">
         <f>M14*Calculations!$C$37/L14</f>
         <v>0.85627717972481643</v>
       </c>
-      <c r="O14" s="82" t="s">
-        <v>2905</v>
+      <c r="O14" s="81" t="s">
+        <v>2903</v>
       </c>
       <c r="P14" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q14" s="58">
         <v>1</v>
@@ -41053,7 +41091,7 @@
       <c r="T14" s="59"/>
       <c r="U14" s="63"/>
       <c r="V14" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W14" s="58">
         <v>1</v>
@@ -41075,7 +41113,7 @@
         <v>49</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>2817</v>
+        <v>2815</v>
       </c>
       <c r="D15" t="s">
         <v>50</v>
@@ -41096,29 +41134,29 @@
         <v>0.82690725513409014</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K15" s="79" t="s">
-        <v>2924</v>
+        <v>2922</v>
       </c>
       <c r="L15" s="79">
         <v>104.15</v>
       </c>
       <c r="M15" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N15" s="72">
         <f>M15*Calculations!$C$37/L15</f>
         <v>0.92259241478636567</v>
       </c>
-      <c r="O15" s="82" t="s">
-        <v>2925</v>
+      <c r="O15" s="81" t="s">
+        <v>2923</v>
       </c>
       <c r="P15" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q15" s="58">
         <v>1</v>
@@ -41128,7 +41166,7 @@
       <c r="T15" s="59"/>
       <c r="U15" s="63"/>
       <c r="V15" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W15" s="58">
         <v>1</v>
@@ -41150,13 +41188,13 @@
         <v>263</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>2818</v>
+        <v>2816</v>
       </c>
       <c r="D16" t="s">
         <v>264</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>2916</v>
+        <v>2914</v>
       </c>
       <c r="F16" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B16, prodcom_data[product], 0))</f>
@@ -41171,29 +41209,29 @@
         <v>0.80199726304971886</v>
       </c>
       <c r="I16" s="49" t="s">
+        <v>2655</v>
+      </c>
+      <c r="J16" s="49" t="s">
         <v>2656</v>
       </c>
-      <c r="J16" s="49" t="s">
-        <v>2657</v>
-      </c>
       <c r="K16" s="79" t="s">
-        <v>2917</v>
+        <v>2915</v>
       </c>
       <c r="L16" s="79">
         <v>166.13</v>
       </c>
       <c r="M16" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N16" s="72">
         <f>M16*Calculations!$C$37/L16</f>
         <v>0.57839041714320105</v>
       </c>
-      <c r="O16" s="82" t="s">
-        <v>2919</v>
+      <c r="O16" s="81" t="s">
+        <v>2917</v>
       </c>
       <c r="P16" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q16" s="58">
         <v>1</v>
@@ -41203,7 +41241,7 @@
       <c r="T16" s="59"/>
       <c r="U16" s="63"/>
       <c r="V16" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W16" s="58">
         <v>1</v>
@@ -41225,13 +41263,13 @@
         <v>599</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>2819</v>
+        <v>2817</v>
       </c>
       <c r="D17" t="s">
         <v>600</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="F17" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B17, prodcom_data[product], 0))</f>
@@ -41246,29 +41284,29 @@
         <v>0.6568762309953875</v>
       </c>
       <c r="I17" s="49" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K17" s="79" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="L17" s="79">
         <v>222.24</v>
       </c>
       <c r="M17" s="80" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="N17" s="72">
         <f>M17*Calculations!$C$37/L17</f>
         <v>0.64854211663066952</v>
       </c>
-      <c r="O17" s="82" t="s">
-        <v>2923</v>
+      <c r="O17" s="81" t="s">
+        <v>2921</v>
       </c>
       <c r="P17" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q17" s="58">
         <v>1</v>
@@ -41278,7 +41316,7 @@
       <c r="T17" s="59"/>
       <c r="U17" s="63"/>
       <c r="V17" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W17" s="58">
         <v>1</v>
@@ -41300,13 +41338,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>2820</v>
+        <v>2818</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>2926</v>
+        <v>2924</v>
       </c>
       <c r="F18" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B18, prodcom_data[product], 0))</f>
@@ -41321,29 +41359,29 @@
         <v>0.9968172135460267</v>
       </c>
       <c r="I18" s="49" t="s">
+        <v>2659</v>
+      </c>
+      <c r="J18" s="49" t="s">
         <v>2660</v>
       </c>
-      <c r="J18" s="49" t="s">
-        <v>2661</v>
-      </c>
       <c r="K18" s="79" t="s">
-        <v>2927</v>
+        <v>2925</v>
       </c>
       <c r="L18" s="79">
         <v>54.09</v>
       </c>
       <c r="M18" s="80" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="N18" s="72">
         <f>M18*Calculations!$C$37/L18</f>
         <v>0.88822333148456267</v>
       </c>
-      <c r="O18" s="82" t="s">
-        <v>2929</v>
+      <c r="O18" s="81" t="s">
+        <v>2927</v>
       </c>
       <c r="P18" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q18" s="58">
         <v>1</v>
@@ -41353,7 +41391,7 @@
       <c r="T18" s="59"/>
       <c r="U18" s="63"/>
       <c r="V18" s="59" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="W18" s="58">
         <v>1</v>
@@ -41375,13 +41413,13 @@
         <v>14</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>2822</v>
+        <v>2820</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
       </c>
       <c r="E19" s="48" t="s">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="F19" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B19, prodcom_data[product], 0))</f>
@@ -41396,29 +41434,29 @@
         <v>0.99997666754441616</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K19" s="79" t="s">
-        <v>2931</v>
+        <v>2929</v>
       </c>
       <c r="L19" s="79">
         <v>112.21</v>
       </c>
       <c r="M19" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N19" s="72">
         <f>M19*Calculations!$C$37/L19</f>
         <v>0.85632296586756973</v>
       </c>
-      <c r="O19" s="82" t="s">
-        <v>2932</v>
+      <c r="O19" s="81" t="s">
+        <v>2930</v>
       </c>
       <c r="P19" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q19" s="58">
         <v>1</v>
@@ -41428,7 +41466,7 @@
       <c r="T19" s="59"/>
       <c r="U19" s="63"/>
       <c r="V19" s="59" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="W19" s="58">
         <v>1</v>
@@ -41450,13 +41488,13 @@
         <v>548</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>2823</v>
+        <v>2821</v>
       </c>
       <c r="D20" t="s">
         <v>549</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="F20" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B20, prodcom_data[product], 0))</f>
@@ -41471,29 +41509,29 @@
         <v>0.88707249478326589</v>
       </c>
       <c r="I20" s="49" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="J20" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K20" s="79" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="L20" s="79">
         <v>104.15199999999999</v>
       </c>
       <c r="M20" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N20" s="72">
         <f>M20*Calculations!$C$37/L20</f>
         <v>0.92257469851755136</v>
       </c>
-      <c r="O20" s="82" t="s">
-        <v>2935</v>
+      <c r="O20" s="81" t="s">
+        <v>2933</v>
       </c>
       <c r="P20" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q20" s="58">
         <v>1</v>
@@ -41503,7 +41541,7 @@
       <c r="T20" s="59"/>
       <c r="U20" s="63"/>
       <c r="V20" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W20" s="58">
         <v>1</v>
@@ -41525,13 +41563,13 @@
         <v>132</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>2824</v>
+        <v>2822</v>
       </c>
       <c r="D21" t="s">
         <v>133</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>2939</v>
+        <v>2937</v>
       </c>
       <c r="F21" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B21, prodcom_data[product], 0))</f>
@@ -41546,35 +41584,35 @@
         <v>0.55687101886052137</v>
       </c>
       <c r="I21" s="49" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="J21" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K21" s="79" t="s">
-        <v>2940</v>
+        <v>2938</v>
       </c>
       <c r="L21" s="79">
         <v>62.07</v>
       </c>
       <c r="M21" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N21" s="72">
         <f>M21*Calculations!$C$37/L21</f>
         <v>0.38701466086676328</v>
       </c>
-      <c r="O21" s="82" t="s">
-        <v>2941</v>
+      <c r="O21" s="81" t="s">
+        <v>2939</v>
       </c>
       <c r="P21" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q21" s="60">
         <v>0.56000000000000005</v>
       </c>
       <c r="R21" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S21" s="61" cm="1">
         <f t="array" ref="S21">1-SUM(IF(ISNUMBER(P21:Q21), P21:Q21, 0))</f>
@@ -41583,13 +41621,13 @@
       <c r="T21" s="59"/>
       <c r="U21" s="63"/>
       <c r="V21" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W21" s="60">
         <v>0.56000000000000005</v>
       </c>
       <c r="X21" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y21" s="61" cm="1">
         <f t="array" ref="Y21">1-SUM(IF(ISNUMBER(V21:W21), V21:W21, 0))</f>
@@ -41610,13 +41648,13 @@
         <v>476</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>2825</v>
+        <v>2823</v>
       </c>
       <c r="D22" t="s">
         <v>477</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>2936</v>
+        <v>2934</v>
       </c>
       <c r="F22" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B22, prodcom_data[product], 0))</f>
@@ -41631,29 +41669,29 @@
         <v>0.98168669522505081</v>
       </c>
       <c r="I22" s="49" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="J22" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K22" s="79" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="L22" s="79">
         <v>58.08</v>
       </c>
       <c r="M22" s="80" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="N22" s="72">
         <f>M22*Calculations!$C$37/L22</f>
         <v>0.62040289256198355</v>
       </c>
-      <c r="O22" s="82" t="s">
-        <v>2938</v>
+      <c r="O22" s="81" t="s">
+        <v>2936</v>
       </c>
       <c r="P22" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q22" s="58">
         <v>1</v>
@@ -41663,7 +41701,7 @@
       <c r="T22" s="59"/>
       <c r="U22" s="63"/>
       <c r="V22" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W22" s="58">
         <v>1</v>
@@ -41685,13 +41723,13 @@
         <v>551</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>2826</v>
+        <v>2824</v>
       </c>
       <c r="D23" t="s">
         <v>552</v>
       </c>
       <c r="E23" s="48" t="s">
-        <v>2933</v>
+        <v>2931</v>
       </c>
       <c r="F23" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B23, prodcom_data[product], 0))</f>
@@ -41706,29 +41744,29 @@
         <v>0.93163807390386044</v>
       </c>
       <c r="I23" s="49" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="J23" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K23" s="79" t="s">
-        <v>2934</v>
+        <v>2932</v>
       </c>
       <c r="L23" s="79">
         <v>104.15199999999999</v>
       </c>
       <c r="M23" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N23" s="72">
         <f>M23*Calculations!$C$37/L23</f>
         <v>0.92257469851755136</v>
       </c>
-      <c r="O23" s="82" t="s">
-        <v>2935</v>
+      <c r="O23" s="81" t="s">
+        <v>2933</v>
       </c>
       <c r="P23" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q23" s="58">
         <v>1</v>
@@ -41738,7 +41776,7 @@
       <c r="T23" s="59"/>
       <c r="U23" s="63"/>
       <c r="V23" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W23" s="58">
         <v>1</v>
@@ -41760,13 +41798,13 @@
         <v>72</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>2827</v>
+        <v>2825</v>
       </c>
       <c r="D24" t="s">
         <v>73</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>2946</v>
+        <v>2944</v>
       </c>
       <c r="F24" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B24, prodcom_data[product], 0))</f>
@@ -41781,35 +41819,35 @@
         <v>0.7564803460728331</v>
       </c>
       <c r="I24" s="49" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="J24" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K24" s="79" t="s">
-        <v>2947</v>
+        <v>2945</v>
       </c>
       <c r="L24" s="79">
         <v>98.96</v>
       </c>
       <c r="M24" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N24" s="72">
         <f>M24*Calculations!$C$37/L24</f>
         <v>0.24274454324979791</v>
       </c>
-      <c r="O24" s="82" t="s">
-        <v>2948</v>
+      <c r="O24" s="81" t="s">
+        <v>2946</v>
       </c>
       <c r="P24" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q24" s="58">
         <v>0.86</v>
       </c>
       <c r="R24" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S24" s="61" cm="1">
         <f t="array" ref="S24">1-SUM(IF(ISNUMBER(P24:Q24), P24:Q24, 0))</f>
@@ -41818,13 +41856,13 @@
       <c r="T24" s="59"/>
       <c r="U24" s="63"/>
       <c r="V24" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W24" s="58">
         <v>0.86</v>
       </c>
       <c r="X24" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y24" s="61" cm="1">
         <f t="array" ref="Y24">1-SUM(IF(ISNUMBER(V24:W24), V24:W24, 0))</f>
@@ -41845,7 +41883,7 @@
         <v>43</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>2828</v>
+        <v>2826</v>
       </c>
       <c r="D25" t="s">
         <v>44</v>
@@ -41866,35 +41904,35 @@
         <v>0.46597635861951109</v>
       </c>
       <c r="I25" s="49" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="J25" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K25" s="79" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L25" s="79">
         <v>106.16</v>
       </c>
       <c r="M25" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N25" s="72">
         <f>M25*Calculations!$C$37/L25</f>
         <v>0.90512434061793512</v>
       </c>
-      <c r="O25" s="82" t="s">
-        <v>2984</v>
+      <c r="O25" s="81" t="s">
+        <v>2982</v>
       </c>
       <c r="P25" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q25" s="58">
         <v>0.48</v>
       </c>
       <c r="R25" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S25" s="61" cm="1">
         <f t="array" ref="S25">1-SUM(IF(ISNUMBER(P25:Q25), P25:Q25, 0))</f>
@@ -41903,13 +41941,13 @@
       <c r="T25" s="59"/>
       <c r="U25" s="63"/>
       <c r="V25" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W25" s="58">
         <v>0.48</v>
       </c>
       <c r="X25" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y25" s="61" cm="1">
         <f t="array" ref="Y25">1-SUM(IF(ISNUMBER(V25:W25), V25:W25, 0))</f>
@@ -41930,7 +41968,7 @@
         <v>37</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>2829</v>
+        <v>2827</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
@@ -41951,29 +41989,29 @@
         <v>0.97878773028598831</v>
       </c>
       <c r="I26" s="49" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="J26" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K26" s="79" t="s">
-        <v>2949</v>
+        <v>2947</v>
       </c>
       <c r="L26" s="79">
         <v>92.14</v>
       </c>
       <c r="M26" s="80" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="N26" s="72">
         <f>M26*Calculations!$C$37/L26</f>
         <v>0.91249186021271977</v>
       </c>
-      <c r="O26" s="82" t="s">
-        <v>2951</v>
+      <c r="O26" s="81" t="s">
+        <v>2949</v>
       </c>
       <c r="P26" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q26" s="58">
         <v>1</v>
@@ -41983,7 +42021,7 @@
       <c r="T26" s="59"/>
       <c r="U26" s="63"/>
       <c r="V26" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W26" s="58">
         <v>1</v>
@@ -42005,7 +42043,7 @@
         <v>420</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>2830</v>
+        <v>2828</v>
       </c>
       <c r="D27" t="s">
         <v>421</v>
@@ -42026,35 +42064,35 @@
         <v>0.92846915963429333</v>
       </c>
       <c r="I27" s="49" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="J27" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K27" s="79" t="s">
-        <v>2937</v>
+        <v>2935</v>
       </c>
       <c r="L27" s="79">
         <v>58.08</v>
       </c>
       <c r="M27" s="80" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="N27" s="72">
         <f>M27*Calculations!$C$37/L27</f>
         <v>0.62040289256198355</v>
       </c>
-      <c r="O27" s="82" t="s">
-        <v>2945</v>
+      <c r="O27" s="81" t="s">
+        <v>2943</v>
       </c>
       <c r="P27" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q27" s="58">
         <v>0.93</v>
       </c>
       <c r="R27" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S27" s="61" cm="1">
         <f t="array" ref="S27">1-SUM(IF(ISNUMBER(P27:Q27), P27:Q27, 0))</f>
@@ -42063,13 +42101,13 @@
       <c r="T27" s="59"/>
       <c r="U27" s="63"/>
       <c r="V27" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W27" s="58">
         <v>0.93</v>
       </c>
       <c r="X27" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y27" s="61" cm="1">
         <f t="array" ref="Y27">1-SUM(IF(ISNUMBER(V27:W27), V27:W27, 0))</f>
@@ -42090,13 +42128,13 @@
         <v>387</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>2832</v>
+        <v>2830</v>
       </c>
       <c r="D28" t="s">
         <v>388</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>2955</v>
+        <v>2953</v>
       </c>
       <c r="F28" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B28, prodcom_data[product], 0))</f>
@@ -42111,29 +42149,29 @@
         <v>0.97723312392412343</v>
       </c>
       <c r="I28" s="49" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="J28" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K28" s="79" t="s">
-        <v>2956</v>
+        <v>2954</v>
       </c>
       <c r="L28" s="79">
         <v>30.026</v>
       </c>
       <c r="M28" s="80" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="N28" s="72">
         <f>M28*Calculations!$C$37/L28</f>
         <v>0.40001998268167588</v>
       </c>
-      <c r="O28" s="82" t="s">
-        <v>2957</v>
+      <c r="O28" s="81" t="s">
+        <v>2955</v>
       </c>
       <c r="P28" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q28" s="58">
         <v>1</v>
@@ -42143,7 +42181,7 @@
       <c r="T28" s="59"/>
       <c r="U28" s="63"/>
       <c r="V28" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W28" s="58">
         <v>1</v>
@@ -42165,13 +42203,13 @@
         <v>620</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>2833</v>
+        <v>2831</v>
       </c>
       <c r="D29" t="s">
         <v>621</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>2942</v>
+        <v>2940</v>
       </c>
       <c r="F29" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B29, prodcom_data[product], 0))</f>
@@ -42186,29 +42224,29 @@
         <v>0.98372184312642852</v>
       </c>
       <c r="I29" s="49" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="J29" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K29" s="79" t="s">
-        <v>2943</v>
+        <v>2941</v>
       </c>
       <c r="L29" s="79">
         <v>86.09</v>
       </c>
       <c r="M29" s="80" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="N29" s="72">
         <f>M29*Calculations!$C$37/L29</f>
         <v>0.55806713904053895</v>
       </c>
-      <c r="O29" s="82" t="s">
-        <v>2944</v>
+      <c r="O29" s="81" t="s">
+        <v>2942</v>
       </c>
       <c r="P29" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q29" s="58">
         <v>1</v>
@@ -42218,7 +42256,7 @@
       <c r="T29" s="59"/>
       <c r="U29" s="63"/>
       <c r="V29" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W29" s="58">
         <v>1</v>
@@ -42240,7 +42278,7 @@
         <v>205</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>2834</v>
+        <v>2832</v>
       </c>
       <c r="D30" t="s">
         <v>206</v>
@@ -42261,29 +42299,29 @@
         <v>0.16881151544376369</v>
       </c>
       <c r="I30" s="49" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="J30" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K30" s="79" t="s">
-        <v>2958</v>
+        <v>2956</v>
       </c>
       <c r="L30" s="79">
         <v>60.05</v>
       </c>
       <c r="M30" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N30" s="72">
         <f>M30*Calculations!$C$37/L30</f>
         <v>0.40003330557868444</v>
       </c>
-      <c r="O30" s="82" t="s">
-        <v>2959</v>
+      <c r="O30" s="81" t="s">
+        <v>2957</v>
       </c>
       <c r="P30" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q30" s="58">
         <v>1</v>
@@ -42293,7 +42331,7 @@
       <c r="T30" s="59"/>
       <c r="U30" s="63"/>
       <c r="V30" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W30" s="58">
         <v>1</v>
@@ -42315,13 +42353,13 @@
         <v>473</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>2835</v>
+        <v>2833</v>
       </c>
       <c r="D31" t="s">
         <v>474</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>2965</v>
+        <v>2963</v>
       </c>
       <c r="F31" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B31, prodcom_data[product], 0))</f>
@@ -42336,29 +42374,29 @@
         <v>0.9949802605865421</v>
       </c>
       <c r="I31" s="49" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="J31" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K31" s="79" t="s">
-        <v>2966</v>
+        <v>2964</v>
       </c>
       <c r="L31" s="79">
         <v>44.05</v>
       </c>
       <c r="M31" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N31" s="72">
         <f>M31*Calculations!$C$37/L31</f>
         <v>0.54533484676503974</v>
       </c>
-      <c r="O31" s="82" t="s">
-        <v>2967</v>
+      <c r="O31" s="81" t="s">
+        <v>2965</v>
       </c>
       <c r="P31" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q31" s="58">
         <v>1</v>
@@ -42368,7 +42406,7 @@
       <c r="T31" s="59"/>
       <c r="U31" s="63"/>
       <c r="V31" s="59" t="s">
-        <v>3047</v>
+        <v>3045</v>
       </c>
       <c r="W31" s="58">
         <v>1</v>
@@ -42390,13 +42428,13 @@
         <v>78</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>2836</v>
+        <v>2834</v>
       </c>
       <c r="D32" t="s">
         <v>79</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="F32" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B32, prodcom_data[product], 0))</f>
@@ -42411,29 +42449,29 @@
         <v>0.90674928778782138</v>
       </c>
       <c r="I32" s="49" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="J32" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K32" s="79" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="L32" s="79">
         <v>62.5</v>
       </c>
       <c r="M32" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N32" s="72">
         <f>M32*Calculations!$C$37/L32</f>
         <v>0.38435199999999997</v>
       </c>
-      <c r="O32" s="82" t="s">
-        <v>2915</v>
+      <c r="O32" s="81" t="s">
+        <v>2913</v>
       </c>
       <c r="P32" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q32" s="58">
         <v>1</v>
@@ -42443,7 +42481,7 @@
       <c r="T32" s="59"/>
       <c r="U32" s="63"/>
       <c r="V32" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W32" s="58">
         <v>1</v>
@@ -42465,13 +42503,13 @@
         <v>293</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>2837</v>
+        <v>2835</v>
       </c>
       <c r="D33" t="s">
         <v>294</v>
       </c>
       <c r="E33" s="48" t="s">
-        <v>2952</v>
+        <v>2950</v>
       </c>
       <c r="F33" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B33, prodcom_data[product], 0))</f>
@@ -42486,35 +42524,35 @@
         <v>0.54958148029233567</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="J33" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K33" s="79" t="s">
-        <v>2953</v>
+        <v>2951</v>
       </c>
       <c r="L33" s="79">
         <v>93.13</v>
       </c>
       <c r="M33" s="80" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="N33" s="72">
         <f>M33*Calculations!$C$37/L33</f>
         <v>0.77382153978309898</v>
       </c>
-      <c r="O33" s="82" t="s">
-        <v>2954</v>
+      <c r="O33" s="81" t="s">
+        <v>2952</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q33" s="58">
         <v>0.8</v>
       </c>
       <c r="R33" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S33" s="61" cm="1">
         <f t="array" ref="S33">1-SUM(IF(ISNUMBER(P33:Q33), P33:Q33, 0))</f>
@@ -42523,13 +42561,13 @@
       <c r="T33" s="59"/>
       <c r="U33" s="63"/>
       <c r="V33" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W33" s="58">
         <v>0.8</v>
       </c>
       <c r="X33" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y33" s="61" cm="1">
         <f t="array" ref="Y33">1-SUM(IF(ISNUMBER(V33:W33), V33:W33, 0))</f>
@@ -42550,13 +42588,13 @@
         <v>602</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>2838</v>
+        <v>2836</v>
       </c>
       <c r="D34" t="s">
         <v>603</v>
       </c>
       <c r="E34" s="48" t="s">
-        <v>2920</v>
+        <v>2918</v>
       </c>
       <c r="F34" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B34, prodcom_data[product], 0))</f>
@@ -42571,29 +42609,29 @@
         <v>0.50439285712492499</v>
       </c>
       <c r="I34" s="49" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="J34" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K34" s="79" t="s">
-        <v>2921</v>
+        <v>2919</v>
       </c>
       <c r="L34" s="79">
         <v>222.24</v>
       </c>
       <c r="M34" s="80" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="N34" s="72">
         <f>M34*Calculations!$C$37/L34</f>
         <v>0.64854211663066952</v>
       </c>
-      <c r="O34" s="82" t="s">
-        <v>2923</v>
+      <c r="O34" s="81" t="s">
+        <v>2921</v>
       </c>
       <c r="P34" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q34" s="58">
         <v>1</v>
@@ -42603,7 +42641,7 @@
       <c r="T34" s="59"/>
       <c r="U34" s="63"/>
       <c r="V34" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W34" s="58">
         <v>1</v>
@@ -42625,13 +42663,13 @@
         <v>135</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>2839</v>
+        <v>2837</v>
       </c>
       <c r="D35" t="s">
         <v>136</v>
       </c>
       <c r="E35" s="48" t="s">
-        <v>2986</v>
+        <v>2984</v>
       </c>
       <c r="F35" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B35, prodcom_data[product], 0))</f>
@@ -42646,35 +42684,35 @@
         <v>0.94336652483154892</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="J35" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K35" s="79" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="L35" s="79">
         <v>76.09</v>
       </c>
       <c r="M35" s="80" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="N35" s="72">
         <f>M35*Calculations!$C$37/L35</f>
         <v>0.47355762912340649</v>
       </c>
-      <c r="O35" s="82" t="s">
-        <v>2988</v>
+      <c r="O35" s="81" t="s">
+        <v>2986</v>
       </c>
       <c r="P35" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q35" s="58">
         <v>0.95</v>
       </c>
       <c r="R35" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S35" s="61" cm="1">
         <f t="array" ref="S35">1-SUM(IF(ISNUMBER(P35:Q35), P35:Q35, 0))</f>
@@ -42683,13 +42721,13 @@
       <c r="T35" s="59"/>
       <c r="U35" s="63"/>
       <c r="V35" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W35" s="58">
         <v>0.95</v>
       </c>
       <c r="X35" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y35" s="61" cm="1">
         <f t="array" ref="Y35">1-SUM(IF(ISNUMBER(V35:W35), V35:W35, 0))</f>
@@ -42710,13 +42748,13 @@
         <v>557</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>2840</v>
+        <v>2838</v>
       </c>
       <c r="D36" t="s">
         <v>558</v>
       </c>
       <c r="E36" s="48" t="s">
-        <v>2960</v>
+        <v>2958</v>
       </c>
       <c r="F36" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B36, prodcom_data[product], 0))</f>
@@ -42731,29 +42769,29 @@
         <v>0.71535186139088358</v>
       </c>
       <c r="I36" s="49" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="J36" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K36" s="79" t="s">
-        <v>2961</v>
+        <v>2959</v>
       </c>
       <c r="L36" s="79">
         <v>211.3</v>
       </c>
       <c r="M36" s="80" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="N36" s="72">
         <f>M36*Calculations!$C$37/L36</f>
         <v>0.85265026029342161</v>
       </c>
-      <c r="O36" s="82" t="s">
-        <v>2963</v>
+      <c r="O36" s="81" t="s">
+        <v>2961</v>
       </c>
       <c r="P36" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q36" s="58">
         <v>1</v>
@@ -42763,7 +42801,7 @@
       <c r="T36" s="59"/>
       <c r="U36" s="63"/>
       <c r="V36" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W36" s="58">
         <v>1</v>
@@ -42785,13 +42823,13 @@
         <v>46</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>2841</v>
+        <v>2839</v>
       </c>
       <c r="D37" t="s">
         <v>47</v>
       </c>
       <c r="E37" s="48" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="F37" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B37, prodcom_data[product], 0))</f>
@@ -42806,35 +42844,35 @@
         <v>0.97390715616715806</v>
       </c>
       <c r="I37" s="49" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="J37" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K37" s="79" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L37" s="79">
         <v>106.16</v>
       </c>
       <c r="M37" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N37" s="72">
         <f>M37*Calculations!$C$37/L37</f>
         <v>0.90512434061793512</v>
       </c>
-      <c r="O37" s="82" t="s">
-        <v>2996</v>
+      <c r="O37" s="81" t="s">
+        <v>2994</v>
       </c>
       <c r="P37" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q37" s="58">
         <v>0.97</v>
       </c>
       <c r="R37" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S37" s="61" cm="1">
         <f t="array" ref="S37">1-SUM(IF(ISNUMBER(P37:Q37), P37:Q37, 0))</f>
@@ -42843,13 +42881,13 @@
       <c r="T37" s="59"/>
       <c r="U37" s="63"/>
       <c r="V37" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W37" s="58">
         <v>0.97</v>
       </c>
       <c r="X37" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y37" s="61" cm="1">
         <f t="array" ref="Y37">1-SUM(IF(ISNUMBER(V37:W37), V37:W37, 0))</f>
@@ -42870,13 +42908,13 @@
         <v>569</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>2842</v>
+        <v>2840</v>
       </c>
       <c r="D38" t="s">
         <v>570</v>
       </c>
       <c r="E38" s="48" t="s">
-        <v>2913</v>
+        <v>2911</v>
       </c>
       <c r="F38" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B38, prodcom_data[product], 0))</f>
@@ -42891,35 +42929,35 @@
         <v>0.93548794446506622</v>
       </c>
       <c r="I38" s="49" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="J38" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K38" s="79" t="s">
-        <v>2914</v>
+        <v>2912</v>
       </c>
       <c r="L38" s="79">
         <v>62.5</v>
       </c>
       <c r="M38" s="80" t="s">
-        <v>2901</v>
+        <v>2899</v>
       </c>
       <c r="N38" s="72">
         <f>M38*Calculations!$C$37/L38</f>
         <v>0.38435199999999997</v>
       </c>
-      <c r="O38" s="82" t="s">
-        <v>2915</v>
+      <c r="O38" s="81" t="s">
+        <v>2913</v>
       </c>
       <c r="P38" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q38" s="58">
         <v>0.98</v>
       </c>
       <c r="R38" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S38" s="61" cm="1">
         <f t="array" ref="S38">1-SUM(IF(ISNUMBER(P38:Q38), P38:Q38, 0))</f>
@@ -42928,13 +42966,13 @@
       <c r="T38" s="59"/>
       <c r="U38" s="63"/>
       <c r="V38" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W38" s="58">
         <v>0.98</v>
       </c>
       <c r="X38" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y38" s="61" cm="1">
         <f t="array" ref="Y38">1-SUM(IF(ISNUMBER(V38:W38), V38:W38, 0))</f>
@@ -42955,7 +42993,7 @@
         <v>55</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>2843</v>
+        <v>2841</v>
       </c>
       <c r="D39" t="s">
         <v>56</v>
@@ -42976,35 +43014,35 @@
         <v>0.9345821199560983</v>
       </c>
       <c r="I39" s="49" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="J39" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K39" s="79" t="s">
-        <v>2976</v>
+        <v>2974</v>
       </c>
       <c r="L39" s="79">
         <v>120.19</v>
       </c>
       <c r="M39" s="80" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="N39" s="72">
         <f>M39*Calculations!$C$37/L39</f>
         <v>0.89940094849821106</v>
       </c>
-      <c r="O39" s="82" t="s">
-        <v>2978</v>
+      <c r="O39" s="81" t="s">
+        <v>2976</v>
       </c>
       <c r="P39" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q39" s="58">
         <v>0.94</v>
       </c>
       <c r="R39" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S39" s="61" cm="1">
         <f t="array" ref="S39">1-SUM(IF(ISNUMBER(P39:Q39), P39:Q39, 0))</f>
@@ -43013,13 +43051,13 @@
       <c r="T39" s="59"/>
       <c r="U39" s="63"/>
       <c r="V39" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W39" s="58">
         <v>0.94</v>
       </c>
       <c r="X39" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y39" s="61" cm="1">
         <f t="array" ref="Y39">1-SUM(IF(ISNUMBER(V39:W39), V39:W39, 0))</f>
@@ -43040,7 +43078,7 @@
         <v>332</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>2844</v>
+        <v>2842</v>
       </c>
       <c r="D40" t="s">
         <v>333</v>
@@ -43061,29 +43099,29 @@
         <v>0.85098041922137724</v>
       </c>
       <c r="I40" s="49" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="J40" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K40" s="79" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="L40" s="79">
         <v>53.06</v>
       </c>
       <c r="M40" s="80" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="N40" s="72">
         <f>M40*Calculations!$C$37/L40</f>
         <v>0.67909913305691672</v>
       </c>
-      <c r="O40" s="82" t="s">
-        <v>3002</v>
+      <c r="O40" s="81" t="s">
+        <v>3000</v>
       </c>
       <c r="P40" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q40" s="58">
         <v>1</v>
@@ -43093,7 +43131,7 @@
       <c r="T40" s="59"/>
       <c r="U40" s="63"/>
       <c r="V40" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W40" s="58">
         <v>1</v>
@@ -43115,7 +43153,7 @@
         <v>28</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>2845</v>
+        <v>2843</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
@@ -43136,29 +43174,29 @@
         <v>0.35122892718634474</v>
       </c>
       <c r="I41" s="49" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="J41" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K41" s="79" t="s">
-        <v>2979</v>
+        <v>2977</v>
       </c>
       <c r="L41" s="79">
         <v>84.16</v>
       </c>
       <c r="M41" s="80" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="N41" s="72">
         <f>M41*Calculations!$C$37/L41</f>
         <v>0.85629752851711038</v>
       </c>
-      <c r="O41" s="82" t="s">
-        <v>2980</v>
+      <c r="O41" s="81" t="s">
+        <v>2978</v>
       </c>
       <c r="P41" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q41" s="58">
         <v>1</v>
@@ -43168,7 +43206,7 @@
       <c r="T41" s="59"/>
       <c r="U41" s="63"/>
       <c r="V41" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W41" s="58">
         <v>1</v>
@@ -43190,13 +43228,13 @@
         <v>252</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>2846</v>
+        <v>2844</v>
       </c>
       <c r="D42" t="s">
         <v>253</v>
       </c>
       <c r="E42" s="48" t="s">
-        <v>2869</v>
+        <v>2867</v>
       </c>
       <c r="F42" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B42, prodcom_data[product], 0))</f>
@@ -43211,29 +43249,29 @@
         <v>0.85514301162071182</v>
       </c>
       <c r="I42" s="49" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="J42" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K42" s="79" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="L42" s="79">
         <v>146.13999999999999</v>
       </c>
       <c r="M42" s="80" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="N42" s="72">
         <f>M42*Calculations!$C$37/L42</f>
         <v>0.49312987546188591</v>
       </c>
-      <c r="O42" s="82" t="s">
-        <v>2982</v>
+      <c r="O42" s="81" t="s">
+        <v>2980</v>
       </c>
       <c r="P42" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q42" s="58">
         <v>1</v>
@@ -43243,7 +43281,7 @@
       <c r="T42" s="59"/>
       <c r="U42" s="63"/>
       <c r="V42" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W42" s="58">
         <v>1</v>
@@ -43265,13 +43303,13 @@
         <v>114</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>2847</v>
+        <v>2845</v>
       </c>
       <c r="D43" t="s">
         <v>115</v>
       </c>
       <c r="E43" s="48" t="s">
-        <v>2973</v>
+        <v>2971</v>
       </c>
       <c r="F43" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B43, prodcom_data[product], 0))</f>
@@ -43286,35 +43324,35 @@
         <v>0.80917344833809868</v>
       </c>
       <c r="I43" s="49" t="s">
+        <v>2686</v>
+      </c>
+      <c r="J43" s="49" t="s">
         <v>2687</v>
       </c>
-      <c r="J43" s="49" t="s">
-        <v>2688</v>
-      </c>
       <c r="K43" s="79" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
       <c r="L43" s="79">
         <v>60.1</v>
       </c>
       <c r="M43" s="80" t="s">
-        <v>2895</v>
+        <v>2893</v>
       </c>
       <c r="N43" s="72">
         <f>M43*Calculations!$C$37/L43</f>
         <v>0.59955074875207992</v>
       </c>
-      <c r="O43" s="82" t="s">
-        <v>2975</v>
+      <c r="O43" s="81" t="s">
+        <v>2973</v>
       </c>
       <c r="P43" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q43" s="58">
         <v>0.82</v>
       </c>
       <c r="R43" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S43" s="61" cm="1">
         <f t="array" ref="S43">1-SUM(IF(ISNUMBER(P43:Q43), P43:Q43, 0))</f>
@@ -43323,13 +43361,13 @@
       <c r="T43" s="59"/>
       <c r="U43" s="63"/>
       <c r="V43" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W43" s="58">
         <v>0.82</v>
       </c>
       <c r="X43" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y43" s="61" cm="1">
         <f t="array" ref="Y43">1-SUM(IF(ISNUMBER(V43:W43), V43:W43, 0))</f>
@@ -43350,7 +43388,7 @@
         <v>52</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>2848</v>
+        <v>2846</v>
       </c>
       <c r="D44" t="s">
         <v>53</v>
@@ -43371,29 +43409,29 @@
         <v>0.93385612259264728</v>
       </c>
       <c r="I44" s="49" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="J44" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K44" s="79" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L44" s="79">
         <v>106.16</v>
       </c>
       <c r="M44" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N44" s="72">
         <f>M44*Calculations!$C$37/L44</f>
         <v>0.90512434061793512</v>
       </c>
-      <c r="O44" s="82" t="s">
-        <v>2985</v>
+      <c r="O44" s="81" t="s">
+        <v>2983</v>
       </c>
       <c r="P44" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q44" s="58">
         <v>1</v>
@@ -43403,7 +43441,7 @@
       <c r="T44" s="59"/>
       <c r="U44" s="63"/>
       <c r="V44" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W44" s="58">
         <v>1</v>
@@ -43425,7 +43463,7 @@
         <v>220</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>2849</v>
+        <v>2847</v>
       </c>
       <c r="D45" t="s">
         <v>221</v>
@@ -43446,35 +43484,35 @@
         <v>0.66130800742337414</v>
       </c>
       <c r="I45" s="49" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="J45" s="49" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="K45" s="79" t="s">
-        <v>2971</v>
+        <v>2969</v>
       </c>
       <c r="L45" s="79">
         <v>128.16900000000001</v>
       </c>
       <c r="M45" s="80" t="s">
-        <v>2950</v>
+        <v>2948</v>
       </c>
       <c r="N45" s="72">
         <f>M45*Calculations!$C$37/L45</f>
         <v>0.6559854567016985</v>
       </c>
-      <c r="O45" s="82" t="s">
-        <v>2972</v>
+      <c r="O45" s="81" t="s">
+        <v>2970</v>
       </c>
       <c r="P45" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q45" s="58">
         <v>0.72</v>
       </c>
       <c r="R45" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S45" s="61" cm="1">
         <f t="array" ref="S45">1-SUM(IF(ISNUMBER(P45:Q45), P45:Q45, 0))</f>
@@ -43483,13 +43521,13 @@
       <c r="T45" s="59"/>
       <c r="U45" s="63"/>
       <c r="V45" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W45" s="58">
         <v>0.72</v>
       </c>
       <c r="X45" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y45" s="61" cm="1">
         <f t="array" ref="Y45">1-SUM(IF(ISNUMBER(V45:W45), V45:W45, 0))</f>
@@ -43510,13 +43548,13 @@
         <v>542</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>2850</v>
+        <v>2848</v>
       </c>
       <c r="D46" t="s">
         <v>543</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>2968</v>
+        <v>2966</v>
       </c>
       <c r="F46" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B46, prodcom_data[product], 0))</f>
@@ -43531,35 +43569,35 @@
         <v>0.84223339185782964</v>
       </c>
       <c r="I46" s="49" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="J46" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K46" s="79" t="s">
-        <v>2969</v>
+        <v>2967</v>
       </c>
       <c r="L46" s="79">
         <v>114.14</v>
       </c>
       <c r="M46" s="80" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="N46" s="72">
         <f>M46*Calculations!$C$37/L46</f>
         <v>0.63138251270369727</v>
       </c>
-      <c r="O46" s="82" t="s">
-        <v>2970</v>
+      <c r="O46" s="81" t="s">
+        <v>2968</v>
       </c>
       <c r="P46" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q46" s="58">
         <v>0.87</v>
       </c>
       <c r="R46" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S46" s="61" cm="1">
         <f t="array" ref="S46">1-SUM(IF(ISNUMBER(P46:Q46), P46:Q46, 0))</f>
@@ -43568,13 +43606,13 @@
       <c r="T46" s="59"/>
       <c r="U46" s="63"/>
       <c r="V46" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W46" s="58">
         <v>0.87</v>
       </c>
       <c r="X46" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y46" s="61" cm="1">
         <f t="array" ref="Y46">1-SUM(IF(ISNUMBER(V46:W46), V46:W46, 0))</f>
@@ -43595,13 +43633,13 @@
         <v>117</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>2851</v>
+        <v>2849</v>
       </c>
       <c r="D47" t="s">
         <v>118</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>2989</v>
+        <v>2987</v>
       </c>
       <c r="F47" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B47, prodcom_data[product], 0))</f>
@@ -43616,29 +43654,29 @@
         <v>0.78843905350643284</v>
       </c>
       <c r="I47" s="49" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="J47" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K47" s="79" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="L47" s="79">
         <v>74.12</v>
       </c>
       <c r="M47" s="80" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="N47" s="72">
         <f>M47*Calculations!$C$37/L47</f>
         <v>0.64819212088505118</v>
       </c>
-      <c r="O47" s="82" t="s">
-        <v>2991</v>
+      <c r="O47" s="81" t="s">
+        <v>2989</v>
       </c>
       <c r="P47" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q47" s="58">
         <v>1</v>
@@ -43648,7 +43686,7 @@
       <c r="T47" s="59"/>
       <c r="U47" s="63"/>
       <c r="V47" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W47" s="58">
         <v>1</v>
@@ -43670,13 +43708,13 @@
         <v>284</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>2852</v>
+        <v>2850</v>
       </c>
       <c r="D48" t="s">
         <v>285</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
       <c r="F48" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B48, prodcom_data[product], 0))</f>
@@ -43691,35 +43729,35 @@
         <v>0.9014296604554024</v>
       </c>
       <c r="I48" s="49" t="s">
+        <v>2692</v>
+      </c>
+      <c r="J48" s="49" t="s">
         <v>2693</v>
       </c>
-      <c r="J48" s="49" t="s">
-        <v>2694</v>
-      </c>
       <c r="K48" s="79" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
       <c r="L48" s="79">
         <v>116.2</v>
       </c>
       <c r="M48" s="80" t="s">
-        <v>2911</v>
+        <v>2909</v>
       </c>
       <c r="N48" s="72">
         <f>M48*Calculations!$C$37/L48</f>
         <v>0.6201893287435456</v>
       </c>
-      <c r="O48" s="82" t="s">
-        <v>2994</v>
+      <c r="O48" s="81" t="s">
+        <v>2992</v>
       </c>
       <c r="P48" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q48" s="58">
         <v>0.91</v>
       </c>
       <c r="R48" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S48" s="61" cm="1">
         <f t="array" ref="S48">1-SUM(IF(ISNUMBER(P48:Q48), P48:Q48, 0))</f>
@@ -43728,13 +43766,13 @@
       <c r="T48" s="59"/>
       <c r="U48" s="63"/>
       <c r="V48" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W48" s="58">
         <v>0.91</v>
       </c>
       <c r="X48" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y48" s="61" cm="1">
         <f t="array" ref="Y48">1-SUM(IF(ISNUMBER(V48:W48), V48:W48, 0))</f>
@@ -43755,7 +43793,7 @@
         <v>186</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>2853</v>
+        <v>2851</v>
       </c>
       <c r="D49" t="s">
         <v>187</v>
@@ -43776,29 +43814,29 @@
         <v>0.11917329138193365</v>
       </c>
       <c r="I49" s="49" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
       <c r="J49" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K49" s="79" t="s">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="L49" s="79">
         <v>88.11</v>
       </c>
       <c r="M49" s="80" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="N49" s="72">
         <f>M49*Calculations!$C$37/L49</f>
         <v>0.54527295426171829</v>
       </c>
-      <c r="O49" s="82" t="s">
-        <v>3008</v>
+      <c r="O49" s="81" t="s">
+        <v>3006</v>
       </c>
       <c r="P49" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="Q49" s="58">
         <v>1</v>
@@ -43808,7 +43846,7 @@
       <c r="T49" s="59"/>
       <c r="U49" s="63"/>
       <c r="V49" s="59" t="s">
-        <v>3045</v>
+        <v>3043</v>
       </c>
       <c r="W49" s="58">
         <v>1</v>
@@ -43830,13 +43868,13 @@
         <v>581</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>2854</v>
+        <v>2852</v>
       </c>
       <c r="D50" t="s">
         <v>582</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="F50" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B50, prodcom_data[product], 0))</f>
@@ -43851,26 +43889,26 @@
         <v>0.59226283959165005</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="J50" s="49" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="K50" s="79" t="s">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="L50" s="79">
         <v>30.026</v>
       </c>
       <c r="M50" s="80" t="s">
-        <v>2908</v>
+        <v>2906</v>
       </c>
       <c r="N50" s="72">
         <f>M50*Calculations!$C$37/L50</f>
         <v>0.40001998268167588</v>
       </c>
-      <c r="O50" s="82" t="s">
-        <v>3006</v>
+      <c r="O50" s="81" t="s">
+        <v>3004</v>
       </c>
       <c r="P50" s="59"/>
       <c r="Q50" s="60"/>
@@ -43897,13 +43935,13 @@
         <v>459</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>2855</v>
+        <v>2853</v>
       </c>
       <c r="D51" t="s">
         <v>460</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="F51" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B51, prodcom_data[product], 0))</f>
@@ -43918,35 +43956,35 @@
         <v>0.18642415725740188</v>
       </c>
       <c r="I51" s="49" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="J51" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K51" s="79" t="s">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="L51" s="79">
         <v>106.12</v>
       </c>
       <c r="M51" s="80" t="s">
-        <v>2928</v>
+        <v>2926</v>
       </c>
       <c r="N51" s="72">
         <f>M51*Calculations!$C$37/L51</f>
         <v>0.45273275537127777</v>
       </c>
-      <c r="O51" s="82" t="s">
-        <v>3011</v>
+      <c r="O51" s="81" t="s">
+        <v>3009</v>
       </c>
       <c r="P51" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q51" s="58">
         <v>0.21</v>
       </c>
       <c r="R51" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S51" s="61" cm="1">
         <f t="array" ref="S51">1-SUM(IF(ISNUMBER(P51:Q51), P51:Q51, 0))</f>
@@ -43955,13 +43993,13 @@
       <c r="T51" s="59"/>
       <c r="U51" s="63"/>
       <c r="V51" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W51" s="58">
         <v>0.21</v>
       </c>
       <c r="X51" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y51" s="61" cm="1">
         <f t="array" ref="Y51">1-SUM(IF(ISNUMBER(V51:W51), V51:W51, 0))</f>
@@ -43982,13 +44020,13 @@
         <v>226</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>2856</v>
+        <v>2854</v>
       </c>
       <c r="D52" t="s">
         <v>227</v>
       </c>
       <c r="E52" s="48" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="F52" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B52, prodcom_data[product], 0))</f>
@@ -44003,35 +44041,35 @@
         <v>0.27981747008972768</v>
       </c>
       <c r="I52" s="49" t="s">
+        <v>2697</v>
+      </c>
+      <c r="J52" s="49" t="s">
         <v>2698</v>
       </c>
-      <c r="J52" s="49" t="s">
-        <v>2699</v>
-      </c>
       <c r="K52" s="79" t="s">
-        <v>2998</v>
+        <v>2996</v>
       </c>
       <c r="L52" s="79">
         <v>100.12</v>
       </c>
       <c r="M52" s="80" t="s">
-        <v>2999</v>
+        <v>2997</v>
       </c>
       <c r="N52" s="72">
         <f>M52*Calculations!$C$37/L52</f>
         <v>0.59983020375549334</v>
       </c>
-      <c r="O52" s="82" t="s">
-        <v>3000</v>
+      <c r="O52" s="81" t="s">
+        <v>2998</v>
       </c>
       <c r="P52" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q52" s="58">
         <v>0.35</v>
       </c>
       <c r="R52" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S52" s="61" cm="1">
         <f t="array" ref="S52">1-SUM(IF(ISNUMBER(P52:Q52), P52:Q52, 0))</f>
@@ -44040,13 +44078,13 @@
       <c r="T52" s="59"/>
       <c r="U52" s="63"/>
       <c r="V52" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W52" s="58">
         <v>0.35</v>
       </c>
       <c r="X52" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y52" s="61" cm="1">
         <f t="array" ref="Y52">1-SUM(IF(ISNUMBER(V52:W52), V52:W52, 0))</f>
@@ -44067,7 +44105,7 @@
         <v>40</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>2857</v>
+        <v>2855</v>
       </c>
       <c r="D53" t="s">
         <v>41</v>
@@ -44088,35 +44126,35 @@
         <v>0.44804616680036363</v>
       </c>
       <c r="I53" s="49" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="J53" s="49" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="K53" s="79" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L53" s="79">
         <v>106.16</v>
       </c>
       <c r="M53" s="80" t="s">
-        <v>2918</v>
+        <v>2916</v>
       </c>
       <c r="N53" s="72">
         <f>M53*Calculations!$C$37/L53</f>
         <v>0.90512434061793512</v>
       </c>
-      <c r="O53" s="82" t="s">
-        <v>3012</v>
+      <c r="O53" s="81" t="s">
+        <v>3010</v>
       </c>
       <c r="P53" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q53" s="58">
         <v>0.51</v>
       </c>
       <c r="R53" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S53" s="61" cm="1">
         <f t="array" ref="S53">1-SUM(IF(ISNUMBER(P53:Q53), P53:Q53, 0))</f>
@@ -44125,13 +44163,13 @@
       <c r="T53" s="59"/>
       <c r="U53" s="63"/>
       <c r="V53" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W53" s="58">
         <v>0.51</v>
       </c>
       <c r="X53" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y53" s="61" cm="1">
         <f t="array" ref="Y53">1-SUM(IF(ISNUMBER(V53:W53), V53:W53, 0))</f>
@@ -44152,13 +44190,13 @@
         <v>345</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>2831</v>
+        <v>2829</v>
       </c>
       <c r="D54" s="52" t="s">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>3014</v>
+        <v>3012</v>
       </c>
       <c r="F54" s="56">
         <f>Calculations!C32*(Calculations!C29/SUM(Calculations!$C$28:$C$29))</f>
@@ -44173,35 +44211,35 @@
         <v>0.88632047658515611</v>
       </c>
       <c r="I54" s="48" t="s">
-        <v>3015</v>
+        <v>3013</v>
       </c>
       <c r="J54" s="49" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="K54" s="79" t="s">
-        <v>3016</v>
+        <v>3014</v>
       </c>
       <c r="L54" s="79">
         <v>174.16</v>
       </c>
       <c r="M54" s="80" t="s">
-        <v>2977</v>
+        <v>2975</v>
       </c>
       <c r="N54" s="72">
         <f>M54*Calculations!$C$37/L54</f>
         <v>0.6206878732200275</v>
       </c>
-      <c r="O54" s="82" t="s">
-        <v>3017</v>
+      <c r="O54" s="81" t="s">
+        <v>3015</v>
       </c>
       <c r="P54" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q54" s="58">
         <v>0.88</v>
       </c>
       <c r="R54" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S54" s="61" cm="1">
         <f t="array" ref="S54">1-SUM(IF(ISNUMBER(P54:Q54), P54:Q54, 0))</f>
@@ -44210,13 +44248,13 @@
       <c r="T54" s="59"/>
       <c r="U54" s="63"/>
       <c r="V54" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W54" s="58">
         <v>0.88</v>
       </c>
       <c r="X54" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y54" s="61" cm="1">
         <f t="array" ref="Y54">1-SUM(IF(ISNUMBER(V54:W54), V54:W54, 0))</f>
@@ -44237,13 +44275,13 @@
         <v>345</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>2831</v>
+        <v>2829</v>
       </c>
       <c r="D55" s="52" t="s">
-        <v>3018</v>
+        <v>3016</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>3019</v>
+        <v>3017</v>
       </c>
       <c r="F55" s="56">
         <f>Calculations!C32*(Calculations!C28/SUM(Calculations!$C$28:$C$29))</f>
@@ -44258,35 +44296,35 @@
         <v>0.88632047658515611</v>
       </c>
       <c r="I55" s="48" t="s">
-        <v>3020</v>
+        <v>3018</v>
       </c>
       <c r="J55" s="49" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="K55" s="79" t="s">
-        <v>3021</v>
+        <v>3019</v>
       </c>
       <c r="L55" s="79">
         <v>250.25</v>
       </c>
       <c r="M55" s="80" t="s">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="N55" s="72">
         <f>M55*Calculations!$C$37/L55</f>
         <v>0.71994005994005994</v>
       </c>
-      <c r="O55" s="82" t="s">
-        <v>3022</v>
+      <c r="O55" s="81" t="s">
+        <v>3020</v>
       </c>
       <c r="P55" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q55" s="58">
         <v>0.88</v>
       </c>
       <c r="R55" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S55" s="61" cm="1">
         <f t="array" ref="S55">1-SUM(IF(ISNUMBER(P55:Q55), P55:Q55, 0))</f>
@@ -44295,13 +44333,13 @@
       <c r="T55" s="59"/>
       <c r="U55" s="63"/>
       <c r="V55" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W55" s="58">
         <v>0.88</v>
       </c>
       <c r="X55" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y55" s="61" cm="1">
         <f t="array" ref="Y55">1-SUM(IF(ISNUMBER(V55:W55), V55:W55, 0))</f>
@@ -44322,56 +44360,56 @@
         <v>634</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>2821</v>
+        <v>2819</v>
       </c>
       <c r="D56" s="52" t="s">
-        <v>3023</v>
+        <v>3021</v>
       </c>
       <c r="E56" s="48" t="s">
-        <v>3024</v>
+        <v>3022</v>
       </c>
       <c r="F56" s="56">
-        <f>Calculations!C6*(Calculations!C24/SUM(Calculations!$C$15:$C$25))</f>
-        <v>6902779.4706734307</v>
+        <f>Calculations!C6*(Calculations!C24/(Calculations!C15+Calculations!C24))</f>
+        <v>1089108418.3783784</v>
       </c>
       <c r="G56" s="54">
         <f t="shared" si="0"/>
-        <v>6.9027794706734303E-3</v>
+        <v>1.0891084183783784</v>
       </c>
       <c r="H56" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B56, prodcom_data[product], 0))</f>
         <v>0.87748442629671652</v>
       </c>
       <c r="I56" s="48" t="s">
-        <v>3025</v>
+        <v>3023</v>
       </c>
       <c r="J56" s="49" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="K56" s="79" t="s">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="L56" s="79">
         <v>224.3</v>
       </c>
       <c r="M56" s="80" t="s">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="N56" s="72">
         <f>M56*Calculations!$C$37/L56</f>
         <v>0.64258582255907271</v>
       </c>
-      <c r="O56" s="82" t="s">
-        <v>3027</v>
+      <c r="O56" s="81" t="s">
+        <v>3025</v>
       </c>
       <c r="P56" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q56" s="58">
         <v>0.91</v>
       </c>
       <c r="R56" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S56" s="61" cm="1">
         <f t="array" ref="S56">1-SUM(IF(ISNUMBER(P56:Q56), P56:Q56, 0))</f>
@@ -44380,13 +44418,13 @@
       <c r="T56" s="59"/>
       <c r="U56" s="63"/>
       <c r="V56" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W56" s="58">
         <v>0.91</v>
       </c>
       <c r="X56" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y56" s="61" cm="1">
         <f t="array" ref="Y56">1-SUM(IF(ISNUMBER(V56:W56), V56:W56, 0))</f>
@@ -44407,56 +44445,56 @@
         <v>634</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>2821</v>
+        <v>2819</v>
       </c>
       <c r="D57" s="52" t="s">
-        <v>3028</v>
+        <v>3026</v>
       </c>
       <c r="E57" s="48" t="s">
-        <v>3029</v>
+        <v>3027</v>
       </c>
       <c r="F57" s="56">
-        <f>Calculations!C6*(Calculations!C15/SUM(Calculations!$C$15:$C$25))</f>
-        <v>8120917.0243216828</v>
+        <f>Calculations!C6*(Calculations!C15/(Calculations!C15+Calculations!C24))</f>
+        <v>1281304021.6216214</v>
       </c>
       <c r="G57" s="54">
         <f t="shared" si="0"/>
-        <v>8.1209170243216819E-3</v>
+        <v>1.2813040216216214</v>
       </c>
       <c r="H57" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B57, prodcom_data[product], 0))</f>
         <v>0.87748442629671652</v>
       </c>
       <c r="I57" s="48" t="s">
-        <v>3030</v>
+        <v>3028</v>
       </c>
       <c r="J57" s="49" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="K57" s="79" t="s">
-        <v>3031</v>
+        <v>3029</v>
       </c>
       <c r="L57" s="79">
         <v>582.79999999999995</v>
       </c>
       <c r="M57" s="80" t="s">
-        <v>3032</v>
+        <v>3030</v>
       </c>
       <c r="N57" s="72">
         <f>M57*Calculations!$C$37/L57</f>
         <v>0.61827385037748805</v>
       </c>
-      <c r="O57" s="82" t="s">
-        <v>3033</v>
+      <c r="O57" s="81" t="s">
+        <v>3031</v>
       </c>
       <c r="P57" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="Q57" s="58">
         <v>0.91</v>
       </c>
       <c r="R57" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="S57" s="61" cm="1">
         <f t="array" ref="S57">1-SUM(IF(ISNUMBER(P57:Q57), P57:Q57, 0))</f>
@@ -44465,13 +44503,13 @@
       <c r="T57" s="59"/>
       <c r="U57" s="63"/>
       <c r="V57" s="59" t="s">
-        <v>3039</v>
+        <v>3037</v>
       </c>
       <c r="W57" s="58">
         <v>0.91</v>
       </c>
       <c r="X57" s="59" t="s">
-        <v>3046</v>
+        <v>3044</v>
       </c>
       <c r="Y57" s="61" cm="1">
         <f t="array" ref="Y57">1-SUM(IF(ISNUMBER(V57:W57), V57:W57, 0))</f>
@@ -44486,7 +44524,7 @@
     </row>
     <row r="107" spans="32:32" x14ac:dyDescent="0.3">
       <c r="AF107" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
   </sheetData>
@@ -44512,155 +44550,155 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
-        <v>3061</v>
+        <v>3059</v>
       </c>
       <c r="B1" t="s">
-        <v>3062</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="38" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B4" s="83" t="s">
-        <v>2774</v>
+        <v>2772</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>2775</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="83" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="83" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="83" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>2781</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B8" s="83" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>2783</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B9" s="83" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="83" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B11" s="83" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>2789</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="83" t="s">
-        <v>2790</v>
+        <v>2788</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B13" s="83" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B14" s="83" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="83" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="83" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="83" t="s">
-        <v>2800</v>
+        <v>2798</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>2801</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" s="83" t="s">
-        <v>2802</v>
+        <v>2800</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>2803</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" s="83" t="s">
-        <v>2804</v>
+        <v>2802</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>2805</v>
+        <v>2803</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="84" t="s">
-        <v>2806</v>
+        <v>2804</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>2807</v>
+        <v>2805</v>
       </c>
     </row>
   </sheetData>

--- a/Article_data/Step 3 results from Prodcom data manipulations.xlsx
+++ b/Article_data/Step 3 results from Prodcom data manipulations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457B40DD-F25B-427A-982C-22A54F724B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3D65E2-710E-4C0C-B3E1-BDBBEB851D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" activeTab="2" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>

--- a/Article_data/Step 3 results from Prodcom data manipulations.xlsx
+++ b/Article_data/Step 3 results from Prodcom data manipulations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3D65E2-710E-4C0C-B3E1-BDBBEB851D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6E6228-23B6-4D98-B031-21ED139D87E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" activeTab="2" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -8756,9 +8756,6 @@
     <t>(Prohaska et al., 2022, p. 581)</t>
   </si>
   <si>
-    <t>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below</t>
-  </si>
-  <si>
     <t>PRODCOM code</t>
   </si>
   <si>
@@ -9336,6 +9333,9 @@
   </si>
   <si>
     <t>Hotspot products export</t>
+  </si>
+  <si>
+    <t>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.</t>
   </si>
 </sst>
 </file>
@@ -10585,7 +10585,7 @@
         <v>46245</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10593,7 +10593,7 @@
         <v>46247</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
@@ -10620,7 +10620,7 @@
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" s="85" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="C31" s="86" t="str">
         <f>'Filtered Prodcom data'!$B$1</f>
@@ -10638,11 +10638,11 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="85" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="C33" s="86" t="str">
         <f>'Hotspot products export'!$B$1</f>
-        <v>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below</v>
+        <v>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10922,10 +10922,10 @@
   <sheetData>
     <row r="1" spans="1:37" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="AC1" s="44"/>
       <c r="AE1" s="44"/>
@@ -10935,10 +10935,10 @@
     </row>
     <row r="2" spans="1:37" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="AC2" s="44"/>
       <c r="AE2" s="44"/>
@@ -39940,10 +39940,10 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B1" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -39968,7 +39968,7 @@
         <v>2370412440</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -40192,7 +40192,7 @@
         <v>1049281862</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="18" thickBot="1" x14ac:dyDescent="0.4">
@@ -40277,26 +40277,26 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B1" t="s">
-        <v>2882</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50" t="s">
+        <v>3071</v>
+      </c>
+      <c r="B3" s="50" t="s">
         <v>3072</v>
-      </c>
-      <c r="B3" s="50" t="s">
-        <v>3073</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
@@ -40305,103 +40305,103 @@
       </c>
       <c r="G4" s="92"/>
       <c r="I4" s="47" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="J4" s="47"/>
     </row>
     <row r="5" spans="1:31" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="91" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="C5" s="57" t="s">
         <v>2808</v>
       </c>
       <c r="D5" s="57" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E5" s="57" t="s">
         <v>2884</v>
       </c>
-      <c r="E5" s="57" t="s">
-        <v>2885</v>
-      </c>
       <c r="F5" s="57" t="s">
+        <v>3032</v>
+      </c>
+      <c r="G5" s="57" t="s">
         <v>3033</v>
       </c>
-      <c r="G5" s="57" t="s">
-        <v>3034</v>
-      </c>
       <c r="H5" s="57" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="I5" s="91" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="J5" s="57" t="s">
         <v>2617</v>
       </c>
       <c r="K5" s="57" t="s">
+        <v>2885</v>
+      </c>
+      <c r="L5" s="57" t="s">
         <v>2886</v>
       </c>
-      <c r="L5" s="57" t="s">
+      <c r="M5" s="57" t="s">
         <v>2887</v>
       </c>
-      <c r="M5" s="57" t="s">
+      <c r="N5" s="57" t="s">
         <v>2888</v>
       </c>
-      <c r="N5" s="57" t="s">
+      <c r="O5" s="62" t="s">
         <v>2889</v>
       </c>
-      <c r="O5" s="62" t="s">
-        <v>2890</v>
-      </c>
       <c r="P5" s="57" t="s">
+        <v>3034</v>
+      </c>
+      <c r="Q5" s="57" t="s">
         <v>3035</v>
       </c>
-      <c r="Q5" s="57" t="s">
-        <v>3036</v>
-      </c>
       <c r="R5" s="57" t="s">
+        <v>3037</v>
+      </c>
+      <c r="S5" s="57" t="s">
         <v>3038</v>
       </c>
-      <c r="S5" s="57" t="s">
+      <c r="T5" s="57" t="s">
+        <v>3047</v>
+      </c>
+      <c r="U5" s="62" t="s">
+        <v>3048</v>
+      </c>
+      <c r="V5" s="57" t="s">
+        <v>3040</v>
+      </c>
+      <c r="W5" s="57" t="s">
+        <v>3041</v>
+      </c>
+      <c r="X5" s="57" t="s">
         <v>3039</v>
       </c>
-      <c r="T5" s="57" t="s">
-        <v>3048</v>
-      </c>
-      <c r="U5" s="62" t="s">
+      <c r="Y5" s="57" t="s">
+        <v>3045</v>
+      </c>
+      <c r="Z5" s="57" t="s">
         <v>3049</v>
       </c>
-      <c r="V5" s="57" t="s">
-        <v>3041</v>
-      </c>
-      <c r="W5" s="57" t="s">
-        <v>3042</v>
-      </c>
-      <c r="X5" s="57" t="s">
-        <v>3040</v>
-      </c>
-      <c r="Y5" s="57" t="s">
-        <v>3046</v>
-      </c>
-      <c r="Z5" s="57" t="s">
+      <c r="AA5" s="57" t="s">
         <v>3050</v>
       </c>
-      <c r="AA5" s="57" t="s">
-        <v>3051</v>
-      </c>
       <c r="AB5" s="57" t="s">
+        <v>3052</v>
+      </c>
+      <c r="AC5" s="57" t="s">
         <v>3053</v>
       </c>
-      <c r="AC5" s="57" t="s">
-        <v>3054</v>
-      </c>
       <c r="AD5" s="57" t="s">
+        <v>3066</v>
+      </c>
+      <c r="AE5" s="57" t="s">
         <v>3067</v>
-      </c>
-      <c r="AE5" s="57" t="s">
-        <v>3068</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
@@ -40418,7 +40418,7 @@
         <v>615</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="F6" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B6, prodcom_data[product], 0))</f>
@@ -40439,23 +40439,23 @@
         <v>2642</v>
       </c>
       <c r="K6" s="79" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="L6" s="79">
         <v>42.081000000000003</v>
       </c>
       <c r="M6" s="80" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N6" s="72">
         <f>M6*Calculations!$C$37/L6</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O6" s="81" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="P6" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q6" s="58">
         <v>1</v>
@@ -40465,7 +40465,7 @@
       <c r="T6" s="59"/>
       <c r="U6" s="63"/>
       <c r="V6" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W6" s="58">
         <v>1</v>
@@ -40514,23 +40514,23 @@
         <v>2642</v>
       </c>
       <c r="K7" s="79" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="L7" s="79">
         <v>28.05</v>
       </c>
       <c r="M7" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N7" s="72">
         <f>M7*Calculations!$C$37/L7</f>
         <v>0.85639928698752221</v>
       </c>
       <c r="O7" s="81" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="P7" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q7" s="58">
         <v>1</v>
@@ -40540,7 +40540,7 @@
       <c r="T7" s="59"/>
       <c r="U7" s="63"/>
       <c r="V7" s="59" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="W7" s="58">
         <v>1</v>
@@ -40568,7 +40568,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="F8" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B8, prodcom_data[product], 0))</f>
@@ -40589,23 +40589,23 @@
         <v>2642</v>
       </c>
       <c r="K8" s="79" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="L8" s="79">
         <v>42.08</v>
       </c>
       <c r="M8" s="80" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N8" s="72">
         <f>M8*Calculations!$C$37/L8</f>
         <v>0.85629752851711038</v>
       </c>
       <c r="O8" s="81" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="P8" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q8" s="58">
         <v>1</v>
@@ -40615,7 +40615,7 @@
       <c r="T8" s="59"/>
       <c r="U8" s="63"/>
       <c r="V8" s="59" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="W8" s="58">
         <v>1</v>
@@ -40643,7 +40643,7 @@
         <v>540</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="F9" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B9, prodcom_data[product], 0))</f>
@@ -40664,23 +40664,23 @@
         <v>2642</v>
       </c>
       <c r="K9" s="79" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="L9" s="79">
         <v>28.053999999999998</v>
       </c>
       <c r="M9" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N9" s="72">
         <f>M9*Calculations!$C$37/L9</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O9" s="81" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="P9" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q9" s="58">
         <v>1</v>
@@ -40690,7 +40690,7 @@
       <c r="T9" s="59"/>
       <c r="U9" s="63"/>
       <c r="V9" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W9" s="58">
         <v>1</v>
@@ -40712,13 +40712,13 @@
         <v>111</v>
       </c>
       <c r="C10" s="89" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="D10" t="s">
         <v>112</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="F10" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B10, prodcom_data[product], 0))</f>
@@ -40739,66 +40739,66 @@
         <v>2642</v>
       </c>
       <c r="K10" s="79" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="L10" s="79">
         <v>32.042000000000002</v>
       </c>
       <c r="M10" s="80" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="N10" s="72">
         <f>M10*Calculations!$C$37/L10</f>
         <v>0.3748517570688471</v>
       </c>
       <c r="O10" s="81" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="P10" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q10" s="58">
         <v>0.35</v>
       </c>
       <c r="R10" s="59" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="S10" s="58">
         <v>0.23</v>
       </c>
       <c r="T10" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="U10" s="61">
         <f>1-Q10-S10</f>
         <v>0.42000000000000004</v>
       </c>
       <c r="V10" s="59" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="W10" s="58">
         <v>0.18</v>
       </c>
       <c r="X10" s="59" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="Y10" s="58">
         <v>0.21</v>
       </c>
       <c r="Z10" s="59" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="AA10" s="58">
         <v>0.23</v>
       </c>
       <c r="AB10" s="59" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="AC10" s="60">
         <v>0.16</v>
       </c>
       <c r="AD10" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="AE10" s="61" cm="1">
         <f t="array" ref="AE10">1-SUM(IF(ISNUMBER(V10:AC10), V10:AC10, 0))</f>
@@ -40840,23 +40840,23 @@
         <v>2642</v>
       </c>
       <c r="K11" s="79" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="L11" s="79">
         <v>78.11</v>
       </c>
       <c r="M11" s="80" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="N11" s="72">
         <f>M11*Calculations!$C$37/L11</f>
         <v>0.92262194341313541</v>
       </c>
       <c r="O11" s="81" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="P11" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q11" s="58">
         <v>1</v>
@@ -40866,7 +40866,7 @@
       <c r="T11" s="59"/>
       <c r="U11" s="63"/>
       <c r="V11" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W11" s="58">
         <v>1</v>
@@ -40894,7 +40894,7 @@
         <v>564</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="F12" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B12, prodcom_data[product], 0))</f>
@@ -40915,23 +40915,23 @@
         <v>2642</v>
       </c>
       <c r="K12" s="79" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="L12" s="79">
         <v>62.5</v>
       </c>
       <c r="M12" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N12" s="72">
         <f>M12*Calculations!$C$37/L12</f>
         <v>0.38435199999999997</v>
       </c>
       <c r="O12" s="81" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="P12" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q12" s="58">
         <v>1</v>
@@ -40941,7 +40941,7 @@
       <c r="T12" s="59"/>
       <c r="U12" s="63"/>
       <c r="V12" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W12" s="58">
         <v>1</v>
@@ -40969,7 +40969,7 @@
         <v>537</v>
       </c>
       <c r="E13" s="48" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="F13" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B13, prodcom_data[product], 0))</f>
@@ -40990,23 +40990,23 @@
         <v>2642</v>
       </c>
       <c r="K13" s="79" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="L13" s="79">
         <v>28.053999999999998</v>
       </c>
       <c r="M13" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N13" s="72">
         <f>M13*Calculations!$C$37/L13</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O13" s="81" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="P13" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q13" s="58">
         <v>1</v>
@@ -41016,7 +41016,7 @@
       <c r="T13" s="59"/>
       <c r="U13" s="63"/>
       <c r="V13" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W13" s="58">
         <v>1</v>
@@ -41044,7 +41044,7 @@
         <v>534</v>
       </c>
       <c r="E14" s="48" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="F14" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B14, prodcom_data[product], 0))</f>
@@ -41065,23 +41065,23 @@
         <v>2642</v>
       </c>
       <c r="K14" s="79" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="L14" s="79">
         <v>28.053999999999998</v>
       </c>
       <c r="M14" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N14" s="72">
         <f>M14*Calculations!$C$37/L14</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O14" s="81" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="P14" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q14" s="58">
         <v>1</v>
@@ -41091,7 +41091,7 @@
       <c r="T14" s="59"/>
       <c r="U14" s="63"/>
       <c r="V14" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W14" s="58">
         <v>1</v>
@@ -41140,23 +41140,23 @@
         <v>2642</v>
       </c>
       <c r="K15" s="79" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="L15" s="79">
         <v>104.15</v>
       </c>
       <c r="M15" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N15" s="72">
         <f>M15*Calculations!$C$37/L15</f>
         <v>0.92259241478636567</v>
       </c>
       <c r="O15" s="81" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="P15" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q15" s="58">
         <v>1</v>
@@ -41166,7 +41166,7 @@
       <c r="T15" s="59"/>
       <c r="U15" s="63"/>
       <c r="V15" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W15" s="58">
         <v>1</v>
@@ -41194,7 +41194,7 @@
         <v>264</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="F16" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B16, prodcom_data[product], 0))</f>
@@ -41215,23 +41215,23 @@
         <v>2656</v>
       </c>
       <c r="K16" s="79" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="L16" s="79">
         <v>166.13</v>
       </c>
       <c r="M16" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N16" s="72">
         <f>M16*Calculations!$C$37/L16</f>
         <v>0.57839041714320105</v>
       </c>
       <c r="O16" s="81" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="P16" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q16" s="58">
         <v>1</v>
@@ -41241,7 +41241,7 @@
       <c r="T16" s="59"/>
       <c r="U16" s="63"/>
       <c r="V16" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W16" s="58">
         <v>1</v>
@@ -41269,7 +41269,7 @@
         <v>600</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="F17" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B17, prodcom_data[product], 0))</f>
@@ -41290,23 +41290,23 @@
         <v>2642</v>
       </c>
       <c r="K17" s="79" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="L17" s="79">
         <v>222.24</v>
       </c>
       <c r="M17" s="80" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="N17" s="72">
         <f>M17*Calculations!$C$37/L17</f>
         <v>0.64854211663066952</v>
       </c>
       <c r="O17" s="81" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="P17" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q17" s="58">
         <v>1</v>
@@ -41316,7 +41316,7 @@
       <c r="T17" s="59"/>
       <c r="U17" s="63"/>
       <c r="V17" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W17" s="58">
         <v>1</v>
@@ -41344,7 +41344,7 @@
         <v>18</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="F18" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B18, prodcom_data[product], 0))</f>
@@ -41365,23 +41365,23 @@
         <v>2660</v>
       </c>
       <c r="K18" s="79" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="L18" s="79">
         <v>54.09</v>
       </c>
       <c r="M18" s="80" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="N18" s="72">
         <f>M18*Calculations!$C$37/L18</f>
         <v>0.88822333148456267</v>
       </c>
       <c r="O18" s="81" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="P18" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q18" s="58">
         <v>1</v>
@@ -41391,7 +41391,7 @@
       <c r="T18" s="59"/>
       <c r="U18" s="63"/>
       <c r="V18" s="59" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="W18" s="58">
         <v>1</v>
@@ -41419,7 +41419,7 @@
         <v>15</v>
       </c>
       <c r="E19" s="48" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="F19" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B19, prodcom_data[product], 0))</f>
@@ -41440,23 +41440,23 @@
         <v>2642</v>
       </c>
       <c r="K19" s="79" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="L19" s="79">
         <v>112.21</v>
       </c>
       <c r="M19" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N19" s="72">
         <f>M19*Calculations!$C$37/L19</f>
         <v>0.85632296586756973</v>
       </c>
       <c r="O19" s="81" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="P19" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q19" s="58">
         <v>1</v>
@@ -41466,7 +41466,7 @@
       <c r="T19" s="59"/>
       <c r="U19" s="63"/>
       <c r="V19" s="59" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="W19" s="58">
         <v>1</v>
@@ -41494,7 +41494,7 @@
         <v>549</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="F20" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B20, prodcom_data[product], 0))</f>
@@ -41515,23 +41515,23 @@
         <v>2642</v>
       </c>
       <c r="K20" s="79" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="L20" s="79">
         <v>104.15199999999999</v>
       </c>
       <c r="M20" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N20" s="72">
         <f>M20*Calculations!$C$37/L20</f>
         <v>0.92257469851755136</v>
       </c>
       <c r="O20" s="81" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="P20" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q20" s="58">
         <v>1</v>
@@ -41541,7 +41541,7 @@
       <c r="T20" s="59"/>
       <c r="U20" s="63"/>
       <c r="V20" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W20" s="58">
         <v>1</v>
@@ -41569,7 +41569,7 @@
         <v>133</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="F21" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B21, prodcom_data[product], 0))</f>
@@ -41590,29 +41590,29 @@
         <v>2642</v>
       </c>
       <c r="K21" s="79" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="L21" s="79">
         <v>62.07</v>
       </c>
       <c r="M21" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N21" s="72">
         <f>M21*Calculations!$C$37/L21</f>
         <v>0.38701466086676328</v>
       </c>
       <c r="O21" s="81" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="P21" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q21" s="60">
         <v>0.56000000000000005</v>
       </c>
       <c r="R21" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S21" s="61" cm="1">
         <f t="array" ref="S21">1-SUM(IF(ISNUMBER(P21:Q21), P21:Q21, 0))</f>
@@ -41621,13 +41621,13 @@
       <c r="T21" s="59"/>
       <c r="U21" s="63"/>
       <c r="V21" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W21" s="60">
         <v>0.56000000000000005</v>
       </c>
       <c r="X21" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y21" s="61" cm="1">
         <f t="array" ref="Y21">1-SUM(IF(ISNUMBER(V21:W21), V21:W21, 0))</f>
@@ -41654,7 +41654,7 @@
         <v>477</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="F22" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B22, prodcom_data[product], 0))</f>
@@ -41675,23 +41675,23 @@
         <v>2642</v>
       </c>
       <c r="K22" s="79" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="L22" s="79">
         <v>58.08</v>
       </c>
       <c r="M22" s="80" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N22" s="72">
         <f>M22*Calculations!$C$37/L22</f>
         <v>0.62040289256198355</v>
       </c>
       <c r="O22" s="81" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="P22" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q22" s="58">
         <v>1</v>
@@ -41701,7 +41701,7 @@
       <c r="T22" s="59"/>
       <c r="U22" s="63"/>
       <c r="V22" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W22" s="58">
         <v>1</v>
@@ -41729,7 +41729,7 @@
         <v>552</v>
       </c>
       <c r="E23" s="48" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="F23" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B23, prodcom_data[product], 0))</f>
@@ -41750,23 +41750,23 @@
         <v>2642</v>
       </c>
       <c r="K23" s="79" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="L23" s="79">
         <v>104.15199999999999</v>
       </c>
       <c r="M23" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N23" s="72">
         <f>M23*Calculations!$C$37/L23</f>
         <v>0.92257469851755136</v>
       </c>
       <c r="O23" s="81" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="P23" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q23" s="58">
         <v>1</v>
@@ -41776,7 +41776,7 @@
       <c r="T23" s="59"/>
       <c r="U23" s="63"/>
       <c r="V23" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W23" s="58">
         <v>1</v>
@@ -41804,7 +41804,7 @@
         <v>73</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="F24" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B24, prodcom_data[product], 0))</f>
@@ -41825,29 +41825,29 @@
         <v>2642</v>
       </c>
       <c r="K24" s="79" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="L24" s="79">
         <v>98.96</v>
       </c>
       <c r="M24" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N24" s="72">
         <f>M24*Calculations!$C$37/L24</f>
         <v>0.24274454324979791</v>
       </c>
       <c r="O24" s="81" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="P24" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q24" s="58">
         <v>0.86</v>
       </c>
       <c r="R24" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S24" s="61" cm="1">
         <f t="array" ref="S24">1-SUM(IF(ISNUMBER(P24:Q24), P24:Q24, 0))</f>
@@ -41856,13 +41856,13 @@
       <c r="T24" s="59"/>
       <c r="U24" s="63"/>
       <c r="V24" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W24" s="58">
         <v>0.86</v>
       </c>
       <c r="X24" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y24" s="61" cm="1">
         <f t="array" ref="Y24">1-SUM(IF(ISNUMBER(V24:W24), V24:W24, 0))</f>
@@ -41910,29 +41910,29 @@
         <v>2642</v>
       </c>
       <c r="K25" s="79" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="L25" s="79">
         <v>106.16</v>
       </c>
       <c r="M25" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N25" s="72">
         <f>M25*Calculations!$C$37/L25</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O25" s="81" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="P25" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q25" s="58">
         <v>0.48</v>
       </c>
       <c r="R25" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S25" s="61" cm="1">
         <f t="array" ref="S25">1-SUM(IF(ISNUMBER(P25:Q25), P25:Q25, 0))</f>
@@ -41941,13 +41941,13 @@
       <c r="T25" s="59"/>
       <c r="U25" s="63"/>
       <c r="V25" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W25" s="58">
         <v>0.48</v>
       </c>
       <c r="X25" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y25" s="61" cm="1">
         <f t="array" ref="Y25">1-SUM(IF(ISNUMBER(V25:W25), V25:W25, 0))</f>
@@ -41995,23 +41995,23 @@
         <v>2642</v>
       </c>
       <c r="K26" s="79" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="L26" s="79">
         <v>92.14</v>
       </c>
       <c r="M26" s="80" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N26" s="72">
         <f>M26*Calculations!$C$37/L26</f>
         <v>0.91249186021271977</v>
       </c>
       <c r="O26" s="81" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="P26" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q26" s="58">
         <v>1</v>
@@ -42021,7 +42021,7 @@
       <c r="T26" s="59"/>
       <c r="U26" s="63"/>
       <c r="V26" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W26" s="58">
         <v>1</v>
@@ -42070,29 +42070,29 @@
         <v>2642</v>
       </c>
       <c r="K27" s="79" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="L27" s="79">
         <v>58.08</v>
       </c>
       <c r="M27" s="80" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N27" s="72">
         <f>M27*Calculations!$C$37/L27</f>
         <v>0.62040289256198355</v>
       </c>
       <c r="O27" s="81" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="P27" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q27" s="58">
         <v>0.93</v>
       </c>
       <c r="R27" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S27" s="61" cm="1">
         <f t="array" ref="S27">1-SUM(IF(ISNUMBER(P27:Q27), P27:Q27, 0))</f>
@@ -42101,13 +42101,13 @@
       <c r="T27" s="59"/>
       <c r="U27" s="63"/>
       <c r="V27" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W27" s="58">
         <v>0.93</v>
       </c>
       <c r="X27" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y27" s="61" cm="1">
         <f t="array" ref="Y27">1-SUM(IF(ISNUMBER(V27:W27), V27:W27, 0))</f>
@@ -42134,7 +42134,7 @@
         <v>388</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="F28" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B28, prodcom_data[product], 0))</f>
@@ -42155,23 +42155,23 @@
         <v>2642</v>
       </c>
       <c r="K28" s="79" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="L28" s="79">
         <v>30.026</v>
       </c>
       <c r="M28" s="80" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="N28" s="72">
         <f>M28*Calculations!$C$37/L28</f>
         <v>0.40001998268167588</v>
       </c>
       <c r="O28" s="81" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="P28" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q28" s="58">
         <v>1</v>
@@ -42181,7 +42181,7 @@
       <c r="T28" s="59"/>
       <c r="U28" s="63"/>
       <c r="V28" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W28" s="58">
         <v>1</v>
@@ -42209,7 +42209,7 @@
         <v>621</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="F29" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B29, prodcom_data[product], 0))</f>
@@ -42230,23 +42230,23 @@
         <v>2642</v>
       </c>
       <c r="K29" s="79" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="L29" s="79">
         <v>86.09</v>
       </c>
       <c r="M29" s="80" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="N29" s="72">
         <f>M29*Calculations!$C$37/L29</f>
         <v>0.55806713904053895</v>
       </c>
       <c r="O29" s="81" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="P29" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q29" s="58">
         <v>1</v>
@@ -42256,7 +42256,7 @@
       <c r="T29" s="59"/>
       <c r="U29" s="63"/>
       <c r="V29" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W29" s="58">
         <v>1</v>
@@ -42305,23 +42305,23 @@
         <v>2642</v>
       </c>
       <c r="K30" s="79" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="L30" s="79">
         <v>60.05</v>
       </c>
       <c r="M30" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N30" s="72">
         <f>M30*Calculations!$C$37/L30</f>
         <v>0.40003330557868444</v>
       </c>
       <c r="O30" s="81" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="P30" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q30" s="58">
         <v>1</v>
@@ -42331,7 +42331,7 @@
       <c r="T30" s="59"/>
       <c r="U30" s="63"/>
       <c r="V30" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W30" s="58">
         <v>1</v>
@@ -42359,7 +42359,7 @@
         <v>474</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="F31" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B31, prodcom_data[product], 0))</f>
@@ -42380,23 +42380,23 @@
         <v>2642</v>
       </c>
       <c r="K31" s="79" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="L31" s="79">
         <v>44.05</v>
       </c>
       <c r="M31" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N31" s="72">
         <f>M31*Calculations!$C$37/L31</f>
         <v>0.54533484676503974</v>
       </c>
       <c r="O31" s="81" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="P31" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q31" s="58">
         <v>1</v>
@@ -42406,7 +42406,7 @@
       <c r="T31" s="59"/>
       <c r="U31" s="63"/>
       <c r="V31" s="59" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="W31" s="58">
         <v>1</v>
@@ -42434,7 +42434,7 @@
         <v>79</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="F32" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B32, prodcom_data[product], 0))</f>
@@ -42455,23 +42455,23 @@
         <v>2642</v>
       </c>
       <c r="K32" s="79" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="L32" s="79">
         <v>62.5</v>
       </c>
       <c r="M32" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N32" s="72">
         <f>M32*Calculations!$C$37/L32</f>
         <v>0.38435199999999997</v>
       </c>
       <c r="O32" s="81" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="P32" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q32" s="58">
         <v>1</v>
@@ -42481,7 +42481,7 @@
       <c r="T32" s="59"/>
       <c r="U32" s="63"/>
       <c r="V32" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W32" s="58">
         <v>1</v>
@@ -42509,7 +42509,7 @@
         <v>294</v>
       </c>
       <c r="E33" s="48" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="F33" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B33, prodcom_data[product], 0))</f>
@@ -42530,29 +42530,29 @@
         <v>2642</v>
       </c>
       <c r="K33" s="79" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="L33" s="79">
         <v>93.13</v>
       </c>
       <c r="M33" s="80" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="N33" s="72">
         <f>M33*Calculations!$C$37/L33</f>
         <v>0.77382153978309898</v>
       </c>
       <c r="O33" s="81" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q33" s="58">
         <v>0.8</v>
       </c>
       <c r="R33" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S33" s="61" cm="1">
         <f t="array" ref="S33">1-SUM(IF(ISNUMBER(P33:Q33), P33:Q33, 0))</f>
@@ -42561,13 +42561,13 @@
       <c r="T33" s="59"/>
       <c r="U33" s="63"/>
       <c r="V33" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W33" s="58">
         <v>0.8</v>
       </c>
       <c r="X33" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y33" s="61" cm="1">
         <f t="array" ref="Y33">1-SUM(IF(ISNUMBER(V33:W33), V33:W33, 0))</f>
@@ -42594,7 +42594,7 @@
         <v>603</v>
       </c>
       <c r="E34" s="48" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="F34" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B34, prodcom_data[product], 0))</f>
@@ -42615,23 +42615,23 @@
         <v>2642</v>
       </c>
       <c r="K34" s="79" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="L34" s="79">
         <v>222.24</v>
       </c>
       <c r="M34" s="80" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="N34" s="72">
         <f>M34*Calculations!$C$37/L34</f>
         <v>0.64854211663066952</v>
       </c>
       <c r="O34" s="81" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="P34" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q34" s="58">
         <v>1</v>
@@ -42641,7 +42641,7 @@
       <c r="T34" s="59"/>
       <c r="U34" s="63"/>
       <c r="V34" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W34" s="58">
         <v>1</v>
@@ -42669,7 +42669,7 @@
         <v>136</v>
       </c>
       <c r="E35" s="48" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="F35" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B35, prodcom_data[product], 0))</f>
@@ -42690,29 +42690,29 @@
         <v>2642</v>
       </c>
       <c r="K35" s="79" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="L35" s="79">
         <v>76.09</v>
       </c>
       <c r="M35" s="80" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N35" s="72">
         <f>M35*Calculations!$C$37/L35</f>
         <v>0.47355762912340649</v>
       </c>
       <c r="O35" s="81" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="P35" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q35" s="58">
         <v>0.95</v>
       </c>
       <c r="R35" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S35" s="61" cm="1">
         <f t="array" ref="S35">1-SUM(IF(ISNUMBER(P35:Q35), P35:Q35, 0))</f>
@@ -42721,13 +42721,13 @@
       <c r="T35" s="59"/>
       <c r="U35" s="63"/>
       <c r="V35" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W35" s="58">
         <v>0.95</v>
       </c>
       <c r="X35" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y35" s="61" cm="1">
         <f t="array" ref="Y35">1-SUM(IF(ISNUMBER(V35:W35), V35:W35, 0))</f>
@@ -42754,7 +42754,7 @@
         <v>558</v>
       </c>
       <c r="E36" s="48" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="F36" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B36, prodcom_data[product], 0))</f>
@@ -42775,23 +42775,23 @@
         <v>2642</v>
       </c>
       <c r="K36" s="79" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="L36" s="79">
         <v>211.3</v>
       </c>
       <c r="M36" s="80" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="N36" s="72">
         <f>M36*Calculations!$C$37/L36</f>
         <v>0.85265026029342161</v>
       </c>
       <c r="O36" s="81" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="P36" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q36" s="58">
         <v>1</v>
@@ -42801,7 +42801,7 @@
       <c r="T36" s="59"/>
       <c r="U36" s="63"/>
       <c r="V36" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W36" s="58">
         <v>1</v>
@@ -42829,7 +42829,7 @@
         <v>47</v>
       </c>
       <c r="E37" s="48" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="F37" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B37, prodcom_data[product], 0))</f>
@@ -42850,29 +42850,29 @@
         <v>2642</v>
       </c>
       <c r="K37" s="79" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="L37" s="79">
         <v>106.16</v>
       </c>
       <c r="M37" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N37" s="72">
         <f>M37*Calculations!$C$37/L37</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O37" s="81" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="P37" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q37" s="58">
         <v>0.97</v>
       </c>
       <c r="R37" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S37" s="61" cm="1">
         <f t="array" ref="S37">1-SUM(IF(ISNUMBER(P37:Q37), P37:Q37, 0))</f>
@@ -42881,13 +42881,13 @@
       <c r="T37" s="59"/>
       <c r="U37" s="63"/>
       <c r="V37" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W37" s="58">
         <v>0.97</v>
       </c>
       <c r="X37" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y37" s="61" cm="1">
         <f t="array" ref="Y37">1-SUM(IF(ISNUMBER(V37:W37), V37:W37, 0))</f>
@@ -42914,7 +42914,7 @@
         <v>570</v>
       </c>
       <c r="E38" s="48" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="F38" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B38, prodcom_data[product], 0))</f>
@@ -42935,29 +42935,29 @@
         <v>2642</v>
       </c>
       <c r="K38" s="79" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="L38" s="79">
         <v>62.5</v>
       </c>
       <c r="M38" s="80" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="N38" s="72">
         <f>M38*Calculations!$C$37/L38</f>
         <v>0.38435199999999997</v>
       </c>
       <c r="O38" s="81" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="P38" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q38" s="58">
         <v>0.98</v>
       </c>
       <c r="R38" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S38" s="61" cm="1">
         <f t="array" ref="S38">1-SUM(IF(ISNUMBER(P38:Q38), P38:Q38, 0))</f>
@@ -42966,13 +42966,13 @@
       <c r="T38" s="59"/>
       <c r="U38" s="63"/>
       <c r="V38" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W38" s="58">
         <v>0.98</v>
       </c>
       <c r="X38" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y38" s="61" cm="1">
         <f t="array" ref="Y38">1-SUM(IF(ISNUMBER(V38:W38), V38:W38, 0))</f>
@@ -43020,29 +43020,29 @@
         <v>2642</v>
       </c>
       <c r="K39" s="79" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="L39" s="79">
         <v>120.19</v>
       </c>
       <c r="M39" s="80" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="N39" s="72">
         <f>M39*Calculations!$C$37/L39</f>
         <v>0.89940094849821106</v>
       </c>
       <c r="O39" s="81" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="P39" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q39" s="58">
         <v>0.94</v>
       </c>
       <c r="R39" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S39" s="61" cm="1">
         <f t="array" ref="S39">1-SUM(IF(ISNUMBER(P39:Q39), P39:Q39, 0))</f>
@@ -43051,13 +43051,13 @@
       <c r="T39" s="59"/>
       <c r="U39" s="63"/>
       <c r="V39" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W39" s="58">
         <v>0.94</v>
       </c>
       <c r="X39" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y39" s="61" cm="1">
         <f t="array" ref="Y39">1-SUM(IF(ISNUMBER(V39:W39), V39:W39, 0))</f>
@@ -43105,23 +43105,23 @@
         <v>2642</v>
       </c>
       <c r="K40" s="79" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="L40" s="79">
         <v>53.06</v>
       </c>
       <c r="M40" s="80" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N40" s="72">
         <f>M40*Calculations!$C$37/L40</f>
         <v>0.67909913305691672</v>
       </c>
       <c r="O40" s="81" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="P40" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q40" s="58">
         <v>1</v>
@@ -43131,7 +43131,7 @@
       <c r="T40" s="59"/>
       <c r="U40" s="63"/>
       <c r="V40" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W40" s="58">
         <v>1</v>
@@ -43180,23 +43180,23 @@
         <v>2642</v>
       </c>
       <c r="K41" s="79" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="L41" s="79">
         <v>84.16</v>
       </c>
       <c r="M41" s="80" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="N41" s="72">
         <f>M41*Calculations!$C$37/L41</f>
         <v>0.85629752851711038</v>
       </c>
       <c r="O41" s="81" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="P41" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q41" s="58">
         <v>1</v>
@@ -43206,7 +43206,7 @@
       <c r="T41" s="59"/>
       <c r="U41" s="63"/>
       <c r="V41" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W41" s="58">
         <v>1</v>
@@ -43255,23 +43255,23 @@
         <v>2642</v>
       </c>
       <c r="K42" s="79" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="L42" s="79">
         <v>146.13999999999999</v>
       </c>
       <c r="M42" s="80" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="N42" s="72">
         <f>M42*Calculations!$C$37/L42</f>
         <v>0.49312987546188591</v>
       </c>
       <c r="O42" s="81" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="P42" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q42" s="58">
         <v>1</v>
@@ -43281,7 +43281,7 @@
       <c r="T42" s="59"/>
       <c r="U42" s="63"/>
       <c r="V42" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W42" s="58">
         <v>1</v>
@@ -43309,7 +43309,7 @@
         <v>115</v>
       </c>
       <c r="E43" s="48" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="F43" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B43, prodcom_data[product], 0))</f>
@@ -43330,29 +43330,29 @@
         <v>2687</v>
       </c>
       <c r="K43" s="79" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="L43" s="79">
         <v>60.1</v>
       </c>
       <c r="M43" s="80" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="N43" s="72">
         <f>M43*Calculations!$C$37/L43</f>
         <v>0.59955074875207992</v>
       </c>
       <c r="O43" s="81" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="P43" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q43" s="58">
         <v>0.82</v>
       </c>
       <c r="R43" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S43" s="61" cm="1">
         <f t="array" ref="S43">1-SUM(IF(ISNUMBER(P43:Q43), P43:Q43, 0))</f>
@@ -43361,13 +43361,13 @@
       <c r="T43" s="59"/>
       <c r="U43" s="63"/>
       <c r="V43" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W43" s="58">
         <v>0.82</v>
       </c>
       <c r="X43" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y43" s="61" cm="1">
         <f t="array" ref="Y43">1-SUM(IF(ISNUMBER(V43:W43), V43:W43, 0))</f>
@@ -43415,23 +43415,23 @@
         <v>2642</v>
       </c>
       <c r="K44" s="79" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="L44" s="79">
         <v>106.16</v>
       </c>
       <c r="M44" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N44" s="72">
         <f>M44*Calculations!$C$37/L44</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O44" s="81" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="P44" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q44" s="58">
         <v>1</v>
@@ -43441,7 +43441,7 @@
       <c r="T44" s="59"/>
       <c r="U44" s="63"/>
       <c r="V44" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W44" s="58">
         <v>1</v>
@@ -43490,29 +43490,29 @@
         <v>2689</v>
       </c>
       <c r="K45" s="79" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="L45" s="79">
         <v>128.16900000000001</v>
       </c>
       <c r="M45" s="80" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="N45" s="72">
         <f>M45*Calculations!$C$37/L45</f>
         <v>0.6559854567016985</v>
       </c>
       <c r="O45" s="81" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="P45" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q45" s="58">
         <v>0.72</v>
       </c>
       <c r="R45" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S45" s="61" cm="1">
         <f t="array" ref="S45">1-SUM(IF(ISNUMBER(P45:Q45), P45:Q45, 0))</f>
@@ -43521,13 +43521,13 @@
       <c r="T45" s="59"/>
       <c r="U45" s="63"/>
       <c r="V45" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W45" s="58">
         <v>0.72</v>
       </c>
       <c r="X45" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y45" s="61" cm="1">
         <f t="array" ref="Y45">1-SUM(IF(ISNUMBER(V45:W45), V45:W45, 0))</f>
@@ -43554,7 +43554,7 @@
         <v>543</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="F46" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B46, prodcom_data[product], 0))</f>
@@ -43575,29 +43575,29 @@
         <v>2642</v>
       </c>
       <c r="K46" s="79" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="L46" s="79">
         <v>114.14</v>
       </c>
       <c r="M46" s="80" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="N46" s="72">
         <f>M46*Calculations!$C$37/L46</f>
         <v>0.63138251270369727</v>
       </c>
       <c r="O46" s="81" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="P46" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q46" s="58">
         <v>0.87</v>
       </c>
       <c r="R46" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S46" s="61" cm="1">
         <f t="array" ref="S46">1-SUM(IF(ISNUMBER(P46:Q46), P46:Q46, 0))</f>
@@ -43606,13 +43606,13 @@
       <c r="T46" s="59"/>
       <c r="U46" s="63"/>
       <c r="V46" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W46" s="58">
         <v>0.87</v>
       </c>
       <c r="X46" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y46" s="61" cm="1">
         <f t="array" ref="Y46">1-SUM(IF(ISNUMBER(V46:W46), V46:W46, 0))</f>
@@ -43639,7 +43639,7 @@
         <v>118</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="F47" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B47, prodcom_data[product], 0))</f>
@@ -43660,23 +43660,23 @@
         <v>2642</v>
       </c>
       <c r="K47" s="79" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="L47" s="79">
         <v>74.12</v>
       </c>
       <c r="M47" s="80" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="N47" s="72">
         <f>M47*Calculations!$C$37/L47</f>
         <v>0.64819212088505118</v>
       </c>
       <c r="O47" s="81" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="P47" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q47" s="58">
         <v>1</v>
@@ -43686,7 +43686,7 @@
       <c r="T47" s="59"/>
       <c r="U47" s="63"/>
       <c r="V47" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W47" s="58">
         <v>1</v>
@@ -43714,7 +43714,7 @@
         <v>285</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="F48" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B48, prodcom_data[product], 0))</f>
@@ -43735,29 +43735,29 @@
         <v>2693</v>
       </c>
       <c r="K48" s="79" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="L48" s="79">
         <v>116.2</v>
       </c>
       <c r="M48" s="80" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="N48" s="72">
         <f>M48*Calculations!$C$37/L48</f>
         <v>0.6201893287435456</v>
       </c>
       <c r="O48" s="81" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="P48" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q48" s="58">
         <v>0.91</v>
       </c>
       <c r="R48" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S48" s="61" cm="1">
         <f t="array" ref="S48">1-SUM(IF(ISNUMBER(P48:Q48), P48:Q48, 0))</f>
@@ -43766,13 +43766,13 @@
       <c r="T48" s="59"/>
       <c r="U48" s="63"/>
       <c r="V48" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W48" s="58">
         <v>0.91</v>
       </c>
       <c r="X48" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y48" s="61" cm="1">
         <f t="array" ref="Y48">1-SUM(IF(ISNUMBER(V48:W48), V48:W48, 0))</f>
@@ -43820,23 +43820,23 @@
         <v>2642</v>
       </c>
       <c r="K49" s="79" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="L49" s="79">
         <v>88.11</v>
       </c>
       <c r="M49" s="80" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="N49" s="72">
         <f>M49*Calculations!$C$37/L49</f>
         <v>0.54527295426171829</v>
       </c>
       <c r="O49" s="81" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="P49" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="Q49" s="58">
         <v>1</v>
@@ -43846,7 +43846,7 @@
       <c r="T49" s="59"/>
       <c r="U49" s="63"/>
       <c r="V49" s="59" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="W49" s="58">
         <v>1</v>
@@ -43874,7 +43874,7 @@
         <v>582</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="F50" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B50, prodcom_data[product], 0))</f>
@@ -43889,26 +43889,26 @@
         <v>0.59226283959165005</v>
       </c>
       <c r="I50" s="51" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="J50" s="49" t="s">
         <v>2695</v>
       </c>
       <c r="K50" s="79" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="L50" s="79">
         <v>30.026</v>
       </c>
       <c r="M50" s="80" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="N50" s="72">
         <f>M50*Calculations!$C$37/L50</f>
         <v>0.40001998268167588</v>
       </c>
       <c r="O50" s="81" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="P50" s="59"/>
       <c r="Q50" s="60"/>
@@ -43941,7 +43941,7 @@
         <v>460</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="F51" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B51, prodcom_data[product], 0))</f>
@@ -43962,29 +43962,29 @@
         <v>2642</v>
       </c>
       <c r="K51" s="79" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="L51" s="79">
         <v>106.12</v>
       </c>
       <c r="M51" s="80" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="N51" s="72">
         <f>M51*Calculations!$C$37/L51</f>
         <v>0.45273275537127777</v>
       </c>
       <c r="O51" s="81" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="P51" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q51" s="58">
         <v>0.21</v>
       </c>
       <c r="R51" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S51" s="61" cm="1">
         <f t="array" ref="S51">1-SUM(IF(ISNUMBER(P51:Q51), P51:Q51, 0))</f>
@@ -43993,13 +43993,13 @@
       <c r="T51" s="59"/>
       <c r="U51" s="63"/>
       <c r="V51" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W51" s="58">
         <v>0.21</v>
       </c>
       <c r="X51" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y51" s="61" cm="1">
         <f t="array" ref="Y51">1-SUM(IF(ISNUMBER(V51:W51), V51:W51, 0))</f>
@@ -44026,7 +44026,7 @@
         <v>227</v>
       </c>
       <c r="E52" s="48" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="F52" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B52, prodcom_data[product], 0))</f>
@@ -44047,29 +44047,29 @@
         <v>2698</v>
       </c>
       <c r="K52" s="79" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="L52" s="79">
         <v>100.12</v>
       </c>
       <c r="M52" s="80" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="N52" s="72">
         <f>M52*Calculations!$C$37/L52</f>
         <v>0.59983020375549334</v>
       </c>
       <c r="O52" s="81" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="P52" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q52" s="58">
         <v>0.35</v>
       </c>
       <c r="R52" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S52" s="61" cm="1">
         <f t="array" ref="S52">1-SUM(IF(ISNUMBER(P52:Q52), P52:Q52, 0))</f>
@@ -44078,13 +44078,13 @@
       <c r="T52" s="59"/>
       <c r="U52" s="63"/>
       <c r="V52" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W52" s="58">
         <v>0.35</v>
       </c>
       <c r="X52" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y52" s="61" cm="1">
         <f t="array" ref="Y52">1-SUM(IF(ISNUMBER(V52:W52), V52:W52, 0))</f>
@@ -44132,29 +44132,29 @@
         <v>2642</v>
       </c>
       <c r="K53" s="79" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="L53" s="79">
         <v>106.16</v>
       </c>
       <c r="M53" s="80" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="N53" s="72">
         <f>M53*Calculations!$C$37/L53</f>
         <v>0.90512434061793512</v>
       </c>
       <c r="O53" s="81" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="P53" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q53" s="58">
         <v>0.51</v>
       </c>
       <c r="R53" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S53" s="61" cm="1">
         <f t="array" ref="S53">1-SUM(IF(ISNUMBER(P53:Q53), P53:Q53, 0))</f>
@@ -44163,13 +44163,13 @@
       <c r="T53" s="59"/>
       <c r="U53" s="63"/>
       <c r="V53" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W53" s="58">
         <v>0.51</v>
       </c>
       <c r="X53" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y53" s="61" cm="1">
         <f t="array" ref="Y53">1-SUM(IF(ISNUMBER(V53:W53), V53:W53, 0))</f>
@@ -44193,10 +44193,10 @@
         <v>2829</v>
       </c>
       <c r="D54" s="52" t="s">
+        <v>3010</v>
+      </c>
+      <c r="E54" s="48" t="s">
         <v>3011</v>
-      </c>
-      <c r="E54" s="48" t="s">
-        <v>3012</v>
       </c>
       <c r="F54" s="56">
         <f>Calculations!C32*(Calculations!C29/SUM(Calculations!$C$28:$C$29))</f>
@@ -44211,35 +44211,35 @@
         <v>0.88632047658515611</v>
       </c>
       <c r="I54" s="48" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="J54" s="49" t="s">
         <v>2671</v>
       </c>
       <c r="K54" s="79" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="L54" s="79">
         <v>174.16</v>
       </c>
       <c r="M54" s="80" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="N54" s="72">
         <f>M54*Calculations!$C$37/L54</f>
         <v>0.6206878732200275</v>
       </c>
       <c r="O54" s="81" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="P54" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q54" s="58">
         <v>0.88</v>
       </c>
       <c r="R54" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S54" s="61" cm="1">
         <f t="array" ref="S54">1-SUM(IF(ISNUMBER(P54:Q54), P54:Q54, 0))</f>
@@ -44248,13 +44248,13 @@
       <c r="T54" s="59"/>
       <c r="U54" s="63"/>
       <c r="V54" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W54" s="58">
         <v>0.88</v>
       </c>
       <c r="X54" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y54" s="61" cm="1">
         <f t="array" ref="Y54">1-SUM(IF(ISNUMBER(V54:W54), V54:W54, 0))</f>
@@ -44278,10 +44278,10 @@
         <v>2829</v>
       </c>
       <c r="D55" s="52" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E55" s="48" t="s">
         <v>3016</v>
-      </c>
-      <c r="E55" s="48" t="s">
-        <v>3017</v>
       </c>
       <c r="F55" s="56">
         <f>Calculations!C32*(Calculations!C28/SUM(Calculations!$C$28:$C$29))</f>
@@ -44296,35 +44296,35 @@
         <v>0.88632047658515611</v>
       </c>
       <c r="I55" s="48" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="J55" s="49" t="s">
         <v>2671</v>
       </c>
       <c r="K55" s="79" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="L55" s="79">
         <v>250.25</v>
       </c>
       <c r="M55" s="80" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="N55" s="72">
         <f>M55*Calculations!$C$37/L55</f>
         <v>0.71994005994005994</v>
       </c>
       <c r="O55" s="81" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="P55" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q55" s="58">
         <v>0.88</v>
       </c>
       <c r="R55" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S55" s="61" cm="1">
         <f t="array" ref="S55">1-SUM(IF(ISNUMBER(P55:Q55), P55:Q55, 0))</f>
@@ -44333,13 +44333,13 @@
       <c r="T55" s="59"/>
       <c r="U55" s="63"/>
       <c r="V55" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W55" s="58">
         <v>0.88</v>
       </c>
       <c r="X55" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y55" s="61" cm="1">
         <f t="array" ref="Y55">1-SUM(IF(ISNUMBER(V55:W55), V55:W55, 0))</f>
@@ -44363,10 +44363,10 @@
         <v>2819</v>
       </c>
       <c r="D56" s="52" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E56" s="48" t="s">
         <v>3021</v>
-      </c>
-      <c r="E56" s="48" t="s">
-        <v>3022</v>
       </c>
       <c r="F56" s="56">
         <f>Calculations!C6*(Calculations!C24/(Calculations!C15+Calculations!C24))</f>
@@ -44381,35 +44381,35 @@
         <v>0.87748442629671652</v>
       </c>
       <c r="I56" s="48" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="J56" s="49" t="s">
         <v>2661</v>
       </c>
       <c r="K56" s="79" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="L56" s="79">
         <v>224.3</v>
       </c>
       <c r="M56" s="80" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="N56" s="72">
         <f>M56*Calculations!$C$37/L56</f>
         <v>0.64258582255907271</v>
       </c>
       <c r="O56" s="81" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="P56" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q56" s="58">
         <v>0.91</v>
       </c>
       <c r="R56" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S56" s="61" cm="1">
         <f t="array" ref="S56">1-SUM(IF(ISNUMBER(P56:Q56), P56:Q56, 0))</f>
@@ -44418,13 +44418,13 @@
       <c r="T56" s="59"/>
       <c r="U56" s="63"/>
       <c r="V56" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W56" s="58">
         <v>0.91</v>
       </c>
       <c r="X56" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y56" s="61" cm="1">
         <f t="array" ref="Y56">1-SUM(IF(ISNUMBER(V56:W56), V56:W56, 0))</f>
@@ -44448,10 +44448,10 @@
         <v>2819</v>
       </c>
       <c r="D57" s="52" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E57" s="48" t="s">
         <v>3026</v>
-      </c>
-      <c r="E57" s="48" t="s">
-        <v>3027</v>
       </c>
       <c r="F57" s="56">
         <f>Calculations!C6*(Calculations!C15/(Calculations!C15+Calculations!C24))</f>
@@ -44466,35 +44466,35 @@
         <v>0.87748442629671652</v>
       </c>
       <c r="I57" s="48" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="J57" s="49" t="s">
         <v>2661</v>
       </c>
       <c r="K57" s="79" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="L57" s="79">
         <v>582.79999999999995</v>
       </c>
       <c r="M57" s="80" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="N57" s="72">
         <f>M57*Calculations!$C$37/L57</f>
         <v>0.61827385037748805</v>
       </c>
       <c r="O57" s="81" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="P57" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="Q57" s="58">
         <v>0.91</v>
       </c>
       <c r="R57" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="S57" s="61" cm="1">
         <f t="array" ref="S57">1-SUM(IF(ISNUMBER(P57:Q57), P57:Q57, 0))</f>
@@ -44503,13 +44503,13 @@
       <c r="T57" s="59"/>
       <c r="U57" s="63"/>
       <c r="V57" s="59" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="W57" s="58">
         <v>0.91</v>
       </c>
       <c r="X57" s="59" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="Y57" s="61" cm="1">
         <f t="array" ref="Y57">1-SUM(IF(ISNUMBER(V57:W57), V57:W57, 0))</f>
@@ -44550,10 +44550,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
+        <v>3058</v>
+      </c>
+      <c r="B1" t="s">
         <v>3059</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3060</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>

--- a/Article_data/Step 3 results from Prodcom data manipulations.xlsx
+++ b/Article_data/Step 3 results from Prodcom data manipulations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6E6228-23B6-4D98-B031-21ED139D87E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7DEA16-BD02-4A91-99C1-B4D79E905914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
@@ -46,7 +46,7 @@
     <author>Nicolas Lienart</author>
   </authors>
   <commentList>
-    <comment ref="I50" authorId="0" shapeId="0" xr:uid="{ECD7D4FD-83B1-417F-8548-0E059BE763C1}">
+    <comment ref="I53" authorId="0" shapeId="0" xr:uid="{ECD7D4FD-83B1-417F-8548-0E059BE763C1}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7448" uniqueCount="3076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7453" uniqueCount="3081">
   <si>
     <t>freq</t>
   </si>
@@ -9320,15 +9320,9 @@
     <t>Ecoinvent activity name or proxy</t>
   </si>
   <si>
-    <t>Tested with Ecoinvent 3.11 and 3.12</t>
-  </si>
-  <si>
     <t>Green columns:</t>
   </si>
   <si>
-    <t>Required in the CSV export used for listing available Ecoinvent geographies</t>
-  </si>
-  <si>
     <t>Improved some descriptions. Renamed some column titles and sheet name in export sheet.</t>
   </si>
   <si>
@@ -9336,6 +9330,27 @@
   </si>
   <si>
     <t>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.</t>
+  </si>
+  <si>
+    <t>Tested with Ecoinvent 3.11 and 3.12.</t>
+  </si>
+  <si>
+    <t>Orange columns:</t>
+  </si>
+  <si>
+    <t>Required columns to list suppliers in the BACI script.</t>
+  </si>
+  <si>
+    <t>Required to map PRODCOM code to HS22 codes.</t>
+  </si>
+  <si>
+    <t>Blue columns</t>
+  </si>
+  <si>
+    <t>Additional columns required by the LCA calculation and figure output script</t>
+  </si>
+  <si>
+    <t>Update Hotspot product export sheet description</t>
   </si>
 </sst>
 </file>
@@ -9492,7 +9507,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9530,7 +9545,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -9698,7 +9719,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="9" applyBorder="1" applyAlignment="1">
@@ -9884,11 +9905,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -10457,7 +10490,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0928EDD3-90ED-405A-8C35-7F6C77CACFAF}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:G48"/>
+  <dimension ref="B2:G49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.77734375" customWidth="1"/>
@@ -10588,274 +10621,282 @@
         <v>3057</v>
       </c>
     </row>
-    <row r="24" spans="2:3" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="19">
+    <row r="24" spans="2:3" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="37">
         <v>46247</v>
       </c>
-      <c r="C24" s="20" t="s">
-        <v>3073</v>
+      <c r="C24" s="29" t="s">
+        <v>3071</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="13" t="s">
+    <row r="25" spans="2:3" s="50" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="19">
+        <v>46248</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B28" s="13" t="s">
         <v>2724</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" s="17" t="s">
+    <row r="29" spans="2:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B30" s="17" t="s">
         <v>2725</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C30" s="18" t="s">
         <v>2713</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" s="21" t="s">
-        <v>2726</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>2727</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" s="85" t="s">
-        <v>3063</v>
-      </c>
-      <c r="C31" s="86" t="str">
-        <f>'Filtered Prodcom data'!$B$1</f>
-        <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
+      <c r="B31" s="21" t="s">
+        <v>2726</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>2727</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" s="85" t="s">
-        <v>2728</v>
+        <v>3063</v>
       </c>
       <c r="C32" s="86" t="str">
-        <f>Calculations!$B$1</f>
-        <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
+        <f>'Filtered Prodcom data'!$B$1</f>
+        <v>Prodcom data obtained from "Extract Prodcom data.ipynb"</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="85" t="s">
-        <v>3074</v>
+        <v>2728</v>
       </c>
       <c r="C33" s="86" t="str">
+        <f>Calculations!$B$1</f>
+        <v>Data and necessary calculation to split polyamides and isocyanates. Prodcom products into separate product matching with Ecoinvent datasets</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B34" s="85" t="s">
+        <v>3072</v>
+      </c>
+      <c r="C34" s="86" t="str">
         <f>'Hotspot products export'!$B$1</f>
         <v>The table below is an extraction of the table from the previous sheet, taking the top products in the list after screening and ecoinvent matching. Also polyamides and isocyanates were disaggregated below. Table to be exported for use as input CSV in the footprint calculation notebook.</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="87" t="s">
+    <row r="35" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="87" t="s">
         <v>2729</v>
       </c>
-      <c r="C34" s="88" t="str">
+      <c r="C35" s="88" t="str">
         <f>References!$B$1</f>
         <v>Bibliography: list of references used thoughout the workbook</v>
       </c>
     </row>
-    <row r="36" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="13" t="s">
+    <row r="37" spans="2:7" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="2:7" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B38" s="13" t="s">
         <v>2730</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B39" s="17" t="s">
+    <row r="39" spans="2:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B40" s="17" t="s">
         <v>2731</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C40" s="23" t="s">
         <v>2713</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D40" s="23" t="s">
         <v>2732</v>
       </c>
-      <c r="E39" s="23" t="s">
+      <c r="E40" s="23" t="s">
         <v>2733</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F40" s="23" t="s">
         <v>2734</v>
       </c>
-      <c r="G39" s="24" t="s">
+      <c r="G40" s="24" t="s">
         <v>2735</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B40" s="21" t="s">
-        <v>2736</v>
-      </c>
-      <c r="C40" t="s">
-        <v>2737</v>
-      </c>
-      <c r="D40" s="25" t="s">
-        <v>2738</v>
-      </c>
-      <c r="E40" s="25">
-        <v>15</v>
-      </c>
-      <c r="F40" s="25">
-        <v>4.1154000000000003E-2</v>
-      </c>
-      <c r="G40" s="26">
-        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B41" s="21" t="s">
-        <v>2739</v>
+        <v>2736</v>
       </c>
       <c r="C41" t="s">
-        <v>2740</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>2741</v>
-      </c>
-      <c r="E41" s="3">
+        <v>2737</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>2738</v>
+      </c>
+      <c r="E41" s="25">
         <v>15</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="25">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G41" s="76">
+      <c r="G41" s="26">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="21" t="s">
-        <v>2742</v>
+        <v>2739</v>
       </c>
       <c r="C42" t="s">
-        <v>2743</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>2744</v>
-      </c>
-      <c r="E42" s="4">
+        <v>2740</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>2741</v>
+      </c>
+      <c r="E42" s="3">
         <v>15</v>
       </c>
-      <c r="F42" s="68">
+      <c r="F42" s="3">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G42" s="69">
+      <c r="G42" s="76">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B43" s="21" t="s">
-        <v>2745</v>
+        <v>2742</v>
       </c>
       <c r="C43" t="s">
-        <v>2746</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>2747</v>
-      </c>
-      <c r="E43" s="27">
+        <v>2743</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>2744</v>
+      </c>
+      <c r="E43" s="4">
         <v>15</v>
       </c>
-      <c r="F43" s="27">
+      <c r="F43" s="68">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="69">
         <v>5.5855E-5</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B44" s="21" t="s">
-        <v>2748</v>
+        <v>2745</v>
       </c>
       <c r="C44" t="s">
-        <v>2749</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>2750</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>2751</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>2752</v>
-      </c>
-      <c r="G44" s="81" t="s">
-        <v>2753</v>
+        <v>2746</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>2747</v>
+      </c>
+      <c r="E44" s="27">
+        <v>15</v>
+      </c>
+      <c r="F44" s="27">
+        <v>4.1154000000000003E-2</v>
+      </c>
+      <c r="G44" s="28">
+        <v>5.5855E-5</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B45" s="21" t="s">
-        <v>2754</v>
+        <v>2748</v>
       </c>
       <c r="C45" t="s">
-        <v>2755</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>2756</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>2757</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>2758</v>
-      </c>
-      <c r="G45" s="73" t="s">
-        <v>2759</v>
+        <v>2749</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>2750</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>2751</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>2752</v>
+      </c>
+      <c r="G45" s="81" t="s">
+        <v>2753</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="21" t="s">
-        <v>2760</v>
+        <v>2754</v>
       </c>
       <c r="C46" t="s">
-        <v>2761</v>
-      </c>
-      <c r="D46" s="66" t="s">
-        <v>2762</v>
-      </c>
-      <c r="E46" s="66" t="s">
-        <v>2763</v>
-      </c>
-      <c r="F46" s="66" t="s">
-        <v>2764</v>
-      </c>
-      <c r="G46" s="67"/>
+        <v>2755</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>2756</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>2757</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>2758</v>
+      </c>
+      <c r="G46" s="73" t="s">
+        <v>2759</v>
+      </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="21" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D47" s="66" t="s">
+        <v>2762</v>
+      </c>
+      <c r="E47" s="66" t="s">
+        <v>2763</v>
+      </c>
+      <c r="F47" s="66" t="s">
+        <v>2764</v>
+      </c>
+      <c r="G47" s="67"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B48" s="30" t="s">
         <v>2765</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>2766</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="D48" s="31" t="s">
         <v>2767</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E48" s="31">
         <v>15</v>
       </c>
-      <c r="F47" s="31">
+      <c r="F48" s="31">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G47" s="32">
+      <c r="G48" s="32">
         <v>5.5855E-5</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="33" t="s">
+    <row r="49" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="33" t="s">
         <v>2765</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C49" s="34" t="s">
         <v>2768</v>
       </c>
-      <c r="D48" s="35" t="s">
+      <c r="D49" s="35" t="s">
         <v>2769</v>
       </c>
-      <c r="E48" s="70">
+      <c r="E49" s="70">
         <v>15</v>
       </c>
-      <c r="F48" s="36">
+      <c r="F49" s="36">
         <v>4.1154000000000003E-2</v>
       </c>
-      <c r="G48" s="77">
+      <c r="G49" s="77">
         <v>5.5855E-5</v>
       </c>
     </row>
@@ -10865,10 +10906,10 @@
     <hyperlink ref="C11" r:id="rId2" xr:uid="{41B7F739-267F-43D4-BA81-097B57D6E931}"/>
     <hyperlink ref="C15" r:id="rId3" xr:uid="{A231AF78-61FF-4A68-B4C3-3DDFEB4B0959}"/>
     <hyperlink ref="C14" r:id="rId4" xr:uid="{5739EB44-C6AF-4C59-923B-AEA8B4D6A45E}"/>
-    <hyperlink ref="B31" location="'Filtered Prodcom data'!A1" display="'Filtered Prodcom data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
-    <hyperlink ref="B32" location="'Calculations'!A1" display="'Calculations'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
-    <hyperlink ref="B33" location="'Hotspot products export'!A1" display="'Hotspot products export'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
-    <hyperlink ref="B34" location="'References'!A1" display="'References'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
+    <hyperlink ref="B32" location="'Filtered Prodcom data'!A1" display="'Filtered Prodcom data'!A1" xr:uid="{10E90DFE-AB5A-4AC1-8DF9-F7272B3062AD}"/>
+    <hyperlink ref="B33" location="'Calculations'!A1" display="'Calculations'!A1" xr:uid="{98A2ACEB-5840-4141-AD9C-D2CBBA86D412}"/>
+    <hyperlink ref="B34" location="'Hotspot products export'!A1" display="'Hotspot products export'!A1" xr:uid="{773A090A-19D3-42DC-8B76-7EEDEA334565}"/>
+    <hyperlink ref="B35" location="'References'!A1" display="'References'!A1" xr:uid="{EBC96B5D-3218-48C1-8C4C-720D5912EF5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40257,7 +40298,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A13AB6A-DCA0-44FC-B906-F1FE7AA47CE2}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" customWidth="1"/>
@@ -40280,7 +40321,7 @@
         <v>3058</v>
       </c>
       <c r="B1" t="s">
-        <v>3075</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
@@ -40291,393 +40332,185 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="50" t="s">
-        <v>3071</v>
-      </c>
-      <c r="B3" s="50" t="s">
-        <v>3072</v>
+    <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="94" t="s">
+        <v>3075</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>3077</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="F4" s="92" t="s">
-        <v>705</v>
-      </c>
-      <c r="G4" s="92"/>
-      <c r="I4" s="47" t="s">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A5" s="95" t="s">
         <v>3070</v>
       </c>
-      <c r="J4" s="47"/>
+      <c r="B5" t="s">
+        <v>3076</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="91" t="s">
-        <v>3055</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>2882</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>2808</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>2883</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>2884</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>3032</v>
-      </c>
-      <c r="G5" s="57" t="s">
-        <v>3033</v>
-      </c>
-      <c r="H5" s="57" t="s">
-        <v>3056</v>
-      </c>
-      <c r="I5" s="91" t="s">
-        <v>3069</v>
-      </c>
-      <c r="J5" s="57" t="s">
-        <v>2617</v>
-      </c>
-      <c r="K5" s="57" t="s">
-        <v>2885</v>
-      </c>
-      <c r="L5" s="57" t="s">
-        <v>2886</v>
-      </c>
-      <c r="M5" s="57" t="s">
-        <v>2887</v>
-      </c>
-      <c r="N5" s="57" t="s">
-        <v>2888</v>
-      </c>
-      <c r="O5" s="62" t="s">
-        <v>2889</v>
-      </c>
-      <c r="P5" s="57" t="s">
-        <v>3034</v>
-      </c>
-      <c r="Q5" s="57" t="s">
-        <v>3035</v>
-      </c>
-      <c r="R5" s="57" t="s">
-        <v>3037</v>
-      </c>
-      <c r="S5" s="57" t="s">
-        <v>3038</v>
-      </c>
-      <c r="T5" s="57" t="s">
-        <v>3047</v>
-      </c>
-      <c r="U5" s="62" t="s">
-        <v>3048</v>
-      </c>
-      <c r="V5" s="57" t="s">
-        <v>3040</v>
-      </c>
-      <c r="W5" s="57" t="s">
-        <v>3041</v>
-      </c>
-      <c r="X5" s="57" t="s">
-        <v>3039</v>
-      </c>
-      <c r="Y5" s="57" t="s">
-        <v>3045</v>
-      </c>
-      <c r="Z5" s="57" t="s">
-        <v>3049</v>
-      </c>
-      <c r="AA5" s="57" t="s">
-        <v>3050</v>
-      </c>
-      <c r="AB5" s="57" t="s">
-        <v>3052</v>
-      </c>
-      <c r="AC5" s="57" t="s">
-        <v>3053</v>
-      </c>
-      <c r="AD5" s="57" t="s">
-        <v>3066</v>
-      </c>
-      <c r="AE5" s="57" t="s">
-        <v>3067</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A6" s="64">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>614</v>
-      </c>
-      <c r="C6" s="64" t="s">
-        <v>2809</v>
-      </c>
-      <c r="D6" t="s">
-        <v>615</v>
-      </c>
-      <c r="E6" s="48" t="s">
-        <v>2890</v>
-      </c>
-      <c r="F6" s="56">
-        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B6, prodcom_data[product], 0))</f>
-        <v>11059816493</v>
-      </c>
-      <c r="G6" s="54">
-        <f>F6/1000000000</f>
-        <v>11.059816493</v>
-      </c>
-      <c r="H6" s="61">
-        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B6, prodcom_data[product], 0))</f>
-        <v>0.86402104863567564</v>
-      </c>
-      <c r="I6" s="49" t="s">
-        <v>2643</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>2642</v>
-      </c>
-      <c r="K6" s="79" t="s">
-        <v>2891</v>
-      </c>
-      <c r="L6" s="79">
-        <v>42.081000000000003</v>
-      </c>
-      <c r="M6" s="80" t="s">
-        <v>2892</v>
-      </c>
-      <c r="N6" s="72">
-        <f>M6*Calculations!$C$37/L6</f>
-        <v>0.85627717972481643</v>
-      </c>
-      <c r="O6" s="81" t="s">
-        <v>2893</v>
-      </c>
-      <c r="P6" s="59" t="s">
-        <v>3042</v>
-      </c>
-      <c r="Q6" s="58">
-        <v>1</v>
-      </c>
-      <c r="R6" s="59"/>
-      <c r="S6" s="60"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="63"/>
-      <c r="V6" s="59" t="s">
-        <v>3036</v>
-      </c>
-      <c r="W6" s="58">
-        <v>1</v>
-      </c>
-      <c r="X6" s="59"/>
-      <c r="Y6" s="60"/>
-      <c r="Z6" s="59"/>
-      <c r="AA6" s="60"/>
-      <c r="AB6" s="59"/>
-      <c r="AC6" s="60"/>
-      <c r="AD6" s="59"/>
-      <c r="AE6" s="60"/>
+    <row r="6" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="96" t="s">
+        <v>3078</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>3079</v>
+      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A7" s="64">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="64" t="s">
-        <v>2810</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="56">
-        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B7, prodcom_data[product], 0))</f>
-        <v>10337493766</v>
-      </c>
-      <c r="G7" s="54">
-        <f t="shared" ref="G7:G57" si="0">F7/1000000000</f>
-        <v>10.337493766</v>
-      </c>
-      <c r="H7" s="61">
-        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B7, prodcom_data[product], 0))</f>
-        <v>0.87904863332422545</v>
-      </c>
-      <c r="I7" s="49" t="s">
-        <v>2644</v>
-      </c>
-      <c r="J7" s="49" t="s">
-        <v>2642</v>
-      </c>
-      <c r="K7" s="79" t="s">
-        <v>2897</v>
-      </c>
-      <c r="L7" s="79">
-        <v>28.05</v>
-      </c>
-      <c r="M7" s="80" t="s">
-        <v>2898</v>
-      </c>
-      <c r="N7" s="72">
-        <f>M7*Calculations!$C$37/L7</f>
-        <v>0.85639928698752221</v>
-      </c>
-      <c r="O7" s="81" t="s">
-        <v>2899</v>
-      </c>
-      <c r="P7" s="59" t="s">
-        <v>3036</v>
-      </c>
-      <c r="Q7" s="58">
-        <v>1</v>
-      </c>
-      <c r="R7" s="59"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="59"/>
-      <c r="U7" s="63"/>
-      <c r="V7" s="59" t="s">
-        <v>3044</v>
-      </c>
-      <c r="W7" s="58">
-        <v>1</v>
-      </c>
-      <c r="X7" s="59"/>
-      <c r="Y7" s="60"/>
-      <c r="Z7" s="59"/>
-      <c r="AA7" s="60"/>
-      <c r="AB7" s="59"/>
-      <c r="AC7" s="60"/>
-      <c r="AD7" s="59"/>
-      <c r="AE7" s="60"/>
+      <c r="F7" s="91" t="s">
+        <v>705</v>
+      </c>
+      <c r="G7" s="91"/>
+      <c r="I7" s="47" t="s">
+        <v>3074</v>
+      </c>
+      <c r="J7" s="47"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A8" s="64">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="64" t="s">
-        <v>2810</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="48" t="s">
-        <v>2894</v>
-      </c>
-      <c r="F8" s="56">
-        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B8, prodcom_data[product], 0))</f>
-        <v>9081741202</v>
-      </c>
-      <c r="G8" s="54">
-        <f t="shared" si="0"/>
-        <v>9.0817412019999999</v>
-      </c>
-      <c r="H8" s="61">
-        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B8, prodcom_data[product], 0))</f>
-        <v>0.94409418582769256</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>2645</v>
-      </c>
-      <c r="J8" s="49" t="s">
-        <v>2642</v>
-      </c>
-      <c r="K8" s="79" t="s">
-        <v>2895</v>
-      </c>
-      <c r="L8" s="79">
-        <v>42.08</v>
-      </c>
-      <c r="M8" s="80" t="s">
-        <v>2892</v>
-      </c>
-      <c r="N8" s="72">
-        <f>M8*Calculations!$C$37/L8</f>
-        <v>0.85629752851711038</v>
-      </c>
-      <c r="O8" s="81" t="s">
-        <v>2896</v>
-      </c>
-      <c r="P8" s="59" t="s">
-        <v>3036</v>
-      </c>
-      <c r="Q8" s="58">
-        <v>1</v>
-      </c>
-      <c r="R8" s="59"/>
-      <c r="S8" s="60"/>
-      <c r="T8" s="59"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="59" t="s">
-        <v>3044</v>
-      </c>
-      <c r="W8" s="58">
-        <v>1</v>
-      </c>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="60"/>
-      <c r="Z8" s="59"/>
-      <c r="AA8" s="60"/>
-      <c r="AB8" s="59"/>
-      <c r="AC8" s="60"/>
-      <c r="AD8" s="59"/>
-      <c r="AE8" s="60"/>
+    <row r="8" spans="1:31" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="92" t="s">
+        <v>3055</v>
+      </c>
+      <c r="B8" s="93" t="s">
+        <v>2882</v>
+      </c>
+      <c r="C8" s="92" t="s">
+        <v>2808</v>
+      </c>
+      <c r="D8" s="57" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>2884</v>
+      </c>
+      <c r="F8" s="57" t="s">
+        <v>3032</v>
+      </c>
+      <c r="G8" s="57" t="s">
+        <v>3033</v>
+      </c>
+      <c r="H8" s="92" t="s">
+        <v>3056</v>
+      </c>
+      <c r="I8" s="92" t="s">
+        <v>3069</v>
+      </c>
+      <c r="J8" s="57" t="s">
+        <v>2617</v>
+      </c>
+      <c r="K8" s="57" t="s">
+        <v>2885</v>
+      </c>
+      <c r="L8" s="57" t="s">
+        <v>2886</v>
+      </c>
+      <c r="M8" s="57" t="s">
+        <v>2887</v>
+      </c>
+      <c r="N8" s="57" t="s">
+        <v>2888</v>
+      </c>
+      <c r="O8" s="62" t="s">
+        <v>2889</v>
+      </c>
+      <c r="P8" s="57" t="s">
+        <v>3034</v>
+      </c>
+      <c r="Q8" s="57" t="s">
+        <v>3035</v>
+      </c>
+      <c r="R8" s="57" t="s">
+        <v>3037</v>
+      </c>
+      <c r="S8" s="57" t="s">
+        <v>3038</v>
+      </c>
+      <c r="T8" s="57" t="s">
+        <v>3047</v>
+      </c>
+      <c r="U8" s="62" t="s">
+        <v>3048</v>
+      </c>
+      <c r="V8" s="57" t="s">
+        <v>3040</v>
+      </c>
+      <c r="W8" s="57" t="s">
+        <v>3041</v>
+      </c>
+      <c r="X8" s="57" t="s">
+        <v>3039</v>
+      </c>
+      <c r="Y8" s="57" t="s">
+        <v>3045</v>
+      </c>
+      <c r="Z8" s="57" t="s">
+        <v>3049</v>
+      </c>
+      <c r="AA8" s="57" t="s">
+        <v>3050</v>
+      </c>
+      <c r="AB8" s="57" t="s">
+        <v>3052</v>
+      </c>
+      <c r="AC8" s="57" t="s">
+        <v>3053</v>
+      </c>
+      <c r="AD8" s="57" t="s">
+        <v>3066</v>
+      </c>
+      <c r="AE8" s="57" t="s">
+        <v>3067</v>
+      </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>539</v>
+        <v>614</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>2811</v>
+        <v>2809</v>
       </c>
       <c r="D9" t="s">
-        <v>540</v>
+        <v>615</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>2900</v>
+        <v>2890</v>
       </c>
       <c r="F9" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B9, prodcom_data[product], 0))</f>
-        <v>7628879471</v>
+        <v>11059816493</v>
       </c>
       <c r="G9" s="54">
-        <f t="shared" si="0"/>
-        <v>7.6288794710000003</v>
+        <f>F9/1000000000</f>
+        <v>11.059816493</v>
       </c>
       <c r="H9" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B9, prodcom_data[product], 0))</f>
-        <v>0.78369292184089345</v>
+        <v>0.86402104863567564</v>
       </c>
       <c r="I9" s="49" t="s">
-        <v>2646</v>
+        <v>2643</v>
       </c>
       <c r="J9" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K9" s="79" t="s">
-        <v>2901</v>
+        <v>2891</v>
       </c>
       <c r="L9" s="79">
-        <v>28.053999999999998</v>
+        <v>42.081000000000003</v>
       </c>
       <c r="M9" s="80" t="s">
-        <v>2898</v>
+        <v>2892</v>
       </c>
       <c r="N9" s="72">
         <f>M9*Calculations!$C$37/L9</f>
         <v>0.85627717972481643</v>
       </c>
       <c r="O9" s="81" t="s">
-        <v>2902</v>
+        <v>2893</v>
       </c>
       <c r="P9" s="59" t="s">
         <v>3042</v>
@@ -40706,154 +40539,128 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="89" t="s">
-        <v>3065</v>
+        <v>8</v>
+      </c>
+      <c r="C10" s="64" t="s">
+        <v>2810</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>2903</v>
+        <v>9</v>
       </c>
       <c r="F10" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B10, prodcom_data[product], 0))</f>
-        <v>6904732058</v>
+        <v>10337493766</v>
       </c>
       <c r="G10" s="54">
-        <f t="shared" si="0"/>
-        <v>6.9047320579999996</v>
+        <f t="shared" ref="G10:G60" si="0">F10/1000000000</f>
+        <v>10.337493766</v>
       </c>
       <c r="H10" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B10, prodcom_data[product], 0))</f>
-        <v>0.14193164800139446</v>
+        <v>0.87904863332422545</v>
       </c>
       <c r="I10" s="49" t="s">
-        <v>2647</v>
+        <v>2644</v>
       </c>
       <c r="J10" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K10" s="79" t="s">
-        <v>2904</v>
+        <v>2897</v>
       </c>
       <c r="L10" s="79">
-        <v>32.042000000000002</v>
+        <v>28.05</v>
       </c>
       <c r="M10" s="80" t="s">
-        <v>2905</v>
+        <v>2898</v>
       </c>
       <c r="N10" s="72">
         <f>M10*Calculations!$C$37/L10</f>
-        <v>0.3748517570688471</v>
+        <v>0.85639928698752221</v>
       </c>
       <c r="O10" s="81" t="s">
-        <v>2906</v>
+        <v>2899</v>
       </c>
       <c r="P10" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q10" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="R10" s="59" t="s">
-        <v>3046</v>
-      </c>
-      <c r="S10" s="58">
-        <v>0.23</v>
-      </c>
-      <c r="T10" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="U10" s="61">
-        <f>1-Q10-S10</f>
-        <v>0.42000000000000004</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R10" s="59"/>
+      <c r="S10" s="60"/>
+      <c r="T10" s="59"/>
+      <c r="U10" s="63"/>
       <c r="V10" s="59" t="s">
         <v>3044</v>
       </c>
       <c r="W10" s="58">
-        <v>0.18</v>
-      </c>
-      <c r="X10" s="59" t="s">
-        <v>3051</v>
-      </c>
-      <c r="Y10" s="58">
-        <v>0.21</v>
-      </c>
-      <c r="Z10" s="59" t="s">
-        <v>3046</v>
-      </c>
-      <c r="AA10" s="58">
-        <v>0.23</v>
-      </c>
-      <c r="AB10" s="59" t="s">
-        <v>3054</v>
-      </c>
-      <c r="AC10" s="60">
-        <v>0.16</v>
-      </c>
-      <c r="AD10" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="AE10" s="61" cm="1">
-        <f t="array" ref="AE10">1-SUM(IF(ISNUMBER(V10:AC10), V10:AC10, 0))</f>
-        <v>0.21999999999999997</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X10" s="59"/>
+      <c r="Y10" s="60"/>
+      <c r="Z10" s="59"/>
+      <c r="AA10" s="60"/>
+      <c r="AB10" s="59"/>
+      <c r="AC10" s="60"/>
+      <c r="AD10" s="59"/>
+      <c r="AE10" s="60"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>2813</v>
+        <v>2810</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>35</v>
+        <v>2894</v>
       </c>
       <c r="F11" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B11, prodcom_data[product], 0))</f>
-        <v>6234476067</v>
+        <v>9081741202</v>
       </c>
       <c r="G11" s="54">
         <f t="shared" si="0"/>
-        <v>6.2344760670000001</v>
+        <v>9.0817412019999999</v>
       </c>
       <c r="H11" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B11, prodcom_data[product], 0))</f>
-        <v>0.88287081478020857</v>
+        <v>0.94409418582769256</v>
       </c>
       <c r="I11" s="49" t="s">
-        <v>2648</v>
+        <v>2645</v>
       </c>
       <c r="J11" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K11" s="79" t="s">
-        <v>2907</v>
+        <v>2895</v>
       </c>
       <c r="L11" s="79">
-        <v>78.11</v>
+        <v>42.08</v>
       </c>
       <c r="M11" s="80" t="s">
-        <v>2908</v>
+        <v>2892</v>
       </c>
       <c r="N11" s="72">
         <f>M11*Calculations!$C$37/L11</f>
-        <v>0.92262194341313541</v>
+        <v>0.85629752851711038</v>
       </c>
       <c r="O11" s="81" t="s">
-        <v>2909</v>
+        <v>2896</v>
       </c>
       <c r="P11" s="59" t="s">
         <v>3036</v>
@@ -40866,7 +40673,7 @@
       <c r="T11" s="59"/>
       <c r="U11" s="63"/>
       <c r="V11" s="59" t="s">
-        <v>3036</v>
+        <v>3044</v>
       </c>
       <c r="W11" s="58">
         <v>1</v>
@@ -40882,56 +40689,56 @@
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="64">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>2814</v>
+        <v>2811</v>
       </c>
       <c r="D12" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>2910</v>
+        <v>2900</v>
       </c>
       <c r="F12" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B12, prodcom_data[product], 0))</f>
-        <v>5008047468</v>
+        <v>7628879471</v>
       </c>
       <c r="G12" s="54">
         <f t="shared" si="0"/>
-        <v>5.008047468</v>
+        <v>7.6288794710000003</v>
       </c>
       <c r="H12" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B12, prodcom_data[product], 0))</f>
-        <v>0.89272188364169869</v>
+        <v>0.78369292184089345</v>
       </c>
       <c r="I12" s="49" t="s">
-        <v>2650</v>
+        <v>2646</v>
       </c>
       <c r="J12" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K12" s="79" t="s">
-        <v>2911</v>
+        <v>2901</v>
       </c>
       <c r="L12" s="79">
-        <v>62.5</v>
+        <v>28.053999999999998</v>
       </c>
       <c r="M12" s="80" t="s">
         <v>2898</v>
       </c>
       <c r="N12" s="72">
         <f>M12*Calculations!$C$37/L12</f>
-        <v>0.38435199999999997</v>
+        <v>0.85627717972481643</v>
       </c>
       <c r="O12" s="81" t="s">
-        <v>2912</v>
+        <v>2902</v>
       </c>
       <c r="P12" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q12" s="58">
         <v>1</v>
@@ -40957,131 +40764,157 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="64">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>536</v>
-      </c>
-      <c r="C13" s="64" t="s">
-        <v>2812</v>
+        <v>111</v>
+      </c>
+      <c r="C13" s="89" t="s">
+        <v>3065</v>
       </c>
       <c r="D13" t="s">
-        <v>537</v>
+        <v>112</v>
       </c>
       <c r="E13" s="48" t="s">
-        <v>2900</v>
+        <v>2903</v>
       </c>
       <c r="F13" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B13, prodcom_data[product], 0))</f>
-        <v>4474213876</v>
+        <v>6904732058</v>
       </c>
       <c r="G13" s="54">
         <f t="shared" si="0"/>
-        <v>4.4742138760000003</v>
+        <v>6.9047320579999996</v>
       </c>
       <c r="H13" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B13, prodcom_data[product], 0))</f>
-        <v>0.7961067883023123</v>
+        <v>0.14193164800139446</v>
       </c>
       <c r="I13" s="49" t="s">
-        <v>2651</v>
+        <v>2647</v>
       </c>
       <c r="J13" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K13" s="79" t="s">
-        <v>2901</v>
+        <v>2904</v>
       </c>
       <c r="L13" s="79">
-        <v>28.053999999999998</v>
+        <v>32.042000000000002</v>
       </c>
       <c r="M13" s="80" t="s">
-        <v>2898</v>
+        <v>2905</v>
       </c>
       <c r="N13" s="72">
         <f>M13*Calculations!$C$37/L13</f>
-        <v>0.85627717972481643</v>
+        <v>0.3748517570688471</v>
       </c>
       <c r="O13" s="81" t="s">
-        <v>2902</v>
+        <v>2906</v>
       </c>
       <c r="P13" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q13" s="58">
-        <v>1</v>
-      </c>
-      <c r="R13" s="59"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="59"/>
-      <c r="U13" s="63"/>
+        <v>0.35</v>
+      </c>
+      <c r="R13" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="S13" s="58">
+        <v>0.23</v>
+      </c>
+      <c r="T13" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="U13" s="61">
+        <f>1-Q13-S13</f>
+        <v>0.42000000000000004</v>
+      </c>
       <c r="V13" s="59" t="s">
-        <v>3036</v>
+        <v>3044</v>
       </c>
       <c r="W13" s="58">
-        <v>1</v>
-      </c>
-      <c r="X13" s="59"/>
-      <c r="Y13" s="60"/>
-      <c r="Z13" s="59"/>
-      <c r="AA13" s="60"/>
-      <c r="AB13" s="59"/>
-      <c r="AC13" s="60"/>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="60"/>
+        <v>0.18</v>
+      </c>
+      <c r="X13" s="59" t="s">
+        <v>3051</v>
+      </c>
+      <c r="Y13" s="58">
+        <v>0.21</v>
+      </c>
+      <c r="Z13" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="AA13" s="58">
+        <v>0.23</v>
+      </c>
+      <c r="AB13" s="59" t="s">
+        <v>3054</v>
+      </c>
+      <c r="AC13" s="60">
+        <v>0.16</v>
+      </c>
+      <c r="AD13" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AE13" s="61" cm="1">
+        <f t="array" ref="AE13">1-SUM(IF(ISNUMBER(V13:AC13), V13:AC13, 0))</f>
+        <v>0.21999999999999997</v>
+      </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="64">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>533</v>
+        <v>34</v>
       </c>
       <c r="C14" s="64" t="s">
-        <v>2812</v>
+        <v>2813</v>
       </c>
       <c r="D14" t="s">
-        <v>534</v>
+        <v>35</v>
       </c>
       <c r="E14" s="48" t="s">
-        <v>2900</v>
+        <v>35</v>
       </c>
       <c r="F14" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B14, prodcom_data[product], 0))</f>
-        <v>4238710053</v>
+        <v>6234476067</v>
       </c>
       <c r="G14" s="54">
         <f t="shared" si="0"/>
-        <v>4.2387100530000001</v>
+        <v>6.2344760670000001</v>
       </c>
       <c r="H14" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B14, prodcom_data[product], 0))</f>
-        <v>0.8225375065540016</v>
+        <v>0.88287081478020857</v>
       </c>
       <c r="I14" s="49" t="s">
-        <v>2653</v>
+        <v>2648</v>
       </c>
       <c r="J14" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K14" s="79" t="s">
-        <v>2901</v>
+        <v>2907</v>
       </c>
       <c r="L14" s="79">
-        <v>28.053999999999998</v>
+        <v>78.11</v>
       </c>
       <c r="M14" s="80" t="s">
-        <v>2898</v>
+        <v>2908</v>
       </c>
       <c r="N14" s="72">
         <f>M14*Calculations!$C$37/L14</f>
-        <v>0.85627717972481643</v>
+        <v>0.92262194341313541</v>
       </c>
       <c r="O14" s="81" t="s">
-        <v>2902</v>
+        <v>2909</v>
       </c>
       <c r="P14" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q14" s="58">
         <v>1</v>
@@ -41091,7 +40924,7 @@
       <c r="T14" s="59"/>
       <c r="U14" s="63"/>
       <c r="V14" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W14" s="58">
         <v>1</v>
@@ -41107,53 +40940,53 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" s="64">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>563</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>564</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>50</v>
+        <v>2910</v>
       </c>
       <c r="F15" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B15, prodcom_data[product], 0))</f>
-        <v>3627976392</v>
+        <v>5008047468</v>
       </c>
       <c r="G15" s="54">
         <f t="shared" si="0"/>
-        <v>3.6279763919999999</v>
+        <v>5.008047468</v>
       </c>
       <c r="H15" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B15, prodcom_data[product], 0))</f>
-        <v>0.82690725513409014</v>
+        <v>0.89272188364169869</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>2654</v>
+        <v>2650</v>
       </c>
       <c r="J15" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K15" s="79" t="s">
-        <v>2921</v>
+        <v>2911</v>
       </c>
       <c r="L15" s="79">
-        <v>104.15</v>
+        <v>62.5</v>
       </c>
       <c r="M15" s="80" t="s">
-        <v>2915</v>
+        <v>2898</v>
       </c>
       <c r="N15" s="72">
         <f>M15*Calculations!$C$37/L15</f>
-        <v>0.92259241478636567</v>
+        <v>0.38435199999999997</v>
       </c>
       <c r="O15" s="81" t="s">
-        <v>2922</v>
+        <v>2912</v>
       </c>
       <c r="P15" s="59" t="s">
         <v>3036</v>
@@ -41182,53 +41015,53 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" s="64">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>263</v>
+        <v>536</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>2816</v>
+        <v>2812</v>
       </c>
       <c r="D16" t="s">
-        <v>264</v>
+        <v>537</v>
       </c>
       <c r="E16" s="48" t="s">
-        <v>2913</v>
+        <v>2900</v>
       </c>
       <c r="F16" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B16, prodcom_data[product], 0))</f>
-        <v>3491283735</v>
+        <v>4474213876</v>
       </c>
       <c r="G16" s="54">
         <f t="shared" si="0"/>
-        <v>3.4912837350000001</v>
+        <v>4.4742138760000003</v>
       </c>
       <c r="H16" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B16, prodcom_data[product], 0))</f>
-        <v>0.80199726304971886</v>
+        <v>0.7961067883023123</v>
       </c>
       <c r="I16" s="49" t="s">
-        <v>2655</v>
+        <v>2651</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>2656</v>
+        <v>2642</v>
       </c>
       <c r="K16" s="79" t="s">
-        <v>2914</v>
+        <v>2901</v>
       </c>
       <c r="L16" s="79">
-        <v>166.13</v>
+        <v>28.053999999999998</v>
       </c>
       <c r="M16" s="80" t="s">
-        <v>2915</v>
+        <v>2898</v>
       </c>
       <c r="N16" s="72">
         <f>M16*Calculations!$C$37/L16</f>
-        <v>0.57839041714320105</v>
+        <v>0.85627717972481643</v>
       </c>
       <c r="O16" s="81" t="s">
-        <v>2916</v>
+        <v>2902</v>
       </c>
       <c r="P16" s="59" t="s">
         <v>3042</v>
@@ -41241,7 +41074,7 @@
       <c r="T16" s="59"/>
       <c r="U16" s="63"/>
       <c r="V16" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W16" s="58">
         <v>1</v>
@@ -41257,53 +41090,53 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" s="64">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>599</v>
+        <v>533</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>2817</v>
+        <v>2812</v>
       </c>
       <c r="D17" t="s">
-        <v>600</v>
+        <v>534</v>
       </c>
       <c r="E17" s="48" t="s">
-        <v>2917</v>
+        <v>2900</v>
       </c>
       <c r="F17" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B17, prodcom_data[product], 0))</f>
-        <v>3349184970</v>
+        <v>4238710053</v>
       </c>
       <c r="G17" s="54">
         <f t="shared" si="0"/>
-        <v>3.34918497</v>
+        <v>4.2387100530000001</v>
       </c>
       <c r="H17" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B17, prodcom_data[product], 0))</f>
-        <v>0.6568762309953875</v>
+        <v>0.8225375065540016</v>
       </c>
       <c r="I17" s="49" t="s">
-        <v>2657</v>
+        <v>2653</v>
       </c>
       <c r="J17" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K17" s="79" t="s">
-        <v>2918</v>
+        <v>2901</v>
       </c>
       <c r="L17" s="79">
-        <v>222.24</v>
+        <v>28.053999999999998</v>
       </c>
       <c r="M17" s="80" t="s">
-        <v>2919</v>
+        <v>2898</v>
       </c>
       <c r="N17" s="72">
         <f>M17*Calculations!$C$37/L17</f>
-        <v>0.64854211663066952</v>
+        <v>0.85627717972481643</v>
       </c>
       <c r="O17" s="81" t="s">
-        <v>2920</v>
+        <v>2902</v>
       </c>
       <c r="P17" s="59" t="s">
         <v>3042</v>
@@ -41332,53 +41165,53 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" s="64">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>2818</v>
+        <v>2815</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>2923</v>
+        <v>50</v>
       </c>
       <c r="F18" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B18, prodcom_data[product], 0))</f>
-        <v>2808940257</v>
+        <v>3627976392</v>
       </c>
       <c r="G18" s="54">
         <f t="shared" si="0"/>
-        <v>2.8089402570000002</v>
+        <v>3.6279763919999999</v>
       </c>
       <c r="H18" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B18, prodcom_data[product], 0))</f>
-        <v>0.9968172135460267</v>
+        <v>0.82690725513409014</v>
       </c>
       <c r="I18" s="49" t="s">
-        <v>2659</v>
+        <v>2654</v>
       </c>
       <c r="J18" s="49" t="s">
-        <v>2660</v>
+        <v>2642</v>
       </c>
       <c r="K18" s="79" t="s">
-        <v>2924</v>
+        <v>2921</v>
       </c>
       <c r="L18" s="79">
-        <v>54.09</v>
+        <v>104.15</v>
       </c>
       <c r="M18" s="80" t="s">
-        <v>2925</v>
+        <v>2915</v>
       </c>
       <c r="N18" s="72">
         <f>M18*Calculations!$C$37/L18</f>
-        <v>0.88822333148456267</v>
+        <v>0.92259241478636567</v>
       </c>
       <c r="O18" s="81" t="s">
-        <v>2926</v>
+        <v>2922</v>
       </c>
       <c r="P18" s="59" t="s">
         <v>3036</v>
@@ -41391,7 +41224,7 @@
       <c r="T18" s="59"/>
       <c r="U18" s="63"/>
       <c r="V18" s="59" t="s">
-        <v>3044</v>
+        <v>3036</v>
       </c>
       <c r="W18" s="58">
         <v>1</v>
@@ -41407,56 +41240,56 @@
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" s="64">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>263</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>2820</v>
+        <v>2816</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="E19" s="48" t="s">
-        <v>2927</v>
+        <v>2913</v>
       </c>
       <c r="F19" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B19, prodcom_data[product], 0))</f>
-        <v>2000046666</v>
+        <v>3491283735</v>
       </c>
       <c r="G19" s="54">
         <f t="shared" si="0"/>
-        <v>2.0000466659999998</v>
+        <v>3.4912837350000001</v>
       </c>
       <c r="H19" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B19, prodcom_data[product], 0))</f>
-        <v>0.99997666754441616</v>
+        <v>0.80199726304971886</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>2662</v>
+        <v>2655</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>2642</v>
+        <v>2656</v>
       </c>
       <c r="K19" s="79" t="s">
-        <v>2928</v>
+        <v>2914</v>
       </c>
       <c r="L19" s="79">
-        <v>112.21</v>
+        <v>166.13</v>
       </c>
       <c r="M19" s="80" t="s">
         <v>2915</v>
       </c>
       <c r="N19" s="72">
         <f>M19*Calculations!$C$37/L19</f>
-        <v>0.85632296586756973</v>
+        <v>0.57839041714320105</v>
       </c>
       <c r="O19" s="81" t="s">
-        <v>2929</v>
+        <v>2916</v>
       </c>
       <c r="P19" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q19" s="58">
         <v>1</v>
@@ -41466,7 +41299,7 @@
       <c r="T19" s="59"/>
       <c r="U19" s="63"/>
       <c r="V19" s="59" t="s">
-        <v>3044</v>
+        <v>3042</v>
       </c>
       <c r="W19" s="58">
         <v>1</v>
@@ -41482,53 +41315,53 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" s="64">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>548</v>
+        <v>599</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>2821</v>
+        <v>2817</v>
       </c>
       <c r="D20" t="s">
-        <v>549</v>
+        <v>600</v>
       </c>
       <c r="E20" s="48" t="s">
-        <v>2930</v>
+        <v>2917</v>
       </c>
       <c r="F20" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B20, prodcom_data[product], 0))</f>
-        <v>1864065177</v>
+        <v>3349184970</v>
       </c>
       <c r="G20" s="54">
         <f t="shared" si="0"/>
-        <v>1.8640651770000001</v>
+        <v>3.34918497</v>
       </c>
       <c r="H20" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B20, prodcom_data[product], 0))</f>
-        <v>0.88707249478326589</v>
+        <v>0.6568762309953875</v>
       </c>
       <c r="I20" s="49" t="s">
-        <v>2663</v>
+        <v>2657</v>
       </c>
       <c r="J20" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K20" s="79" t="s">
-        <v>2931</v>
+        <v>2918</v>
       </c>
       <c r="L20" s="79">
-        <v>104.15199999999999</v>
+        <v>222.24</v>
       </c>
       <c r="M20" s="80" t="s">
-        <v>2915</v>
+        <v>2919</v>
       </c>
       <c r="N20" s="72">
         <f>M20*Calculations!$C$37/L20</f>
-        <v>0.92257469851755136</v>
+        <v>0.64854211663066952</v>
       </c>
       <c r="O20" s="81" t="s">
-        <v>2932</v>
+        <v>2920</v>
       </c>
       <c r="P20" s="59" t="s">
         <v>3042</v>
@@ -41541,7 +41374,7 @@
       <c r="T20" s="59"/>
       <c r="U20" s="63"/>
       <c r="V20" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W20" s="58">
         <v>1</v>
@@ -41557,82 +41390,72 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" s="64">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>2822</v>
+        <v>2818</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>18</v>
       </c>
       <c r="E21" s="48" t="s">
-        <v>2936</v>
+        <v>2923</v>
       </c>
       <c r="F21" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B21, prodcom_data[product], 0))</f>
-        <v>1795747967</v>
+        <v>2808940257</v>
       </c>
       <c r="G21" s="54">
         <f t="shared" si="0"/>
-        <v>1.7957479670000001</v>
+        <v>2.8089402570000002</v>
       </c>
       <c r="H21" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B21, prodcom_data[product], 0))</f>
-        <v>0.55687101886052137</v>
+        <v>0.9968172135460267</v>
       </c>
       <c r="I21" s="49" t="s">
-        <v>2664</v>
+        <v>2659</v>
       </c>
       <c r="J21" s="49" t="s">
-        <v>2642</v>
+        <v>2660</v>
       </c>
       <c r="K21" s="79" t="s">
-        <v>2937</v>
+        <v>2924</v>
       </c>
       <c r="L21" s="79">
-        <v>62.07</v>
+        <v>54.09</v>
       </c>
       <c r="M21" s="80" t="s">
-        <v>2898</v>
+        <v>2925</v>
       </c>
       <c r="N21" s="72">
         <f>M21*Calculations!$C$37/L21</f>
-        <v>0.38701466086676328</v>
+        <v>0.88822333148456267</v>
       </c>
       <c r="O21" s="81" t="s">
-        <v>2938</v>
+        <v>2926</v>
       </c>
       <c r="P21" s="59" t="s">
         <v>3036</v>
       </c>
-      <c r="Q21" s="60">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="R21" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S21" s="61" cm="1">
-        <f t="array" ref="S21">1-SUM(IF(ISNUMBER(P21:Q21), P21:Q21, 0))</f>
-        <v>0.43999999999999995</v>
-      </c>
+      <c r="Q21" s="58">
+        <v>1</v>
+      </c>
+      <c r="R21" s="59"/>
+      <c r="S21" s="60"/>
       <c r="T21" s="59"/>
       <c r="U21" s="63"/>
       <c r="V21" s="59" t="s">
-        <v>3036</v>
-      </c>
-      <c r="W21" s="60">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="X21" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y21" s="61" cm="1">
-        <f t="array" ref="Y21">1-SUM(IF(ISNUMBER(V21:W21), V21:W21, 0))</f>
-        <v>0.43999999999999995</v>
-      </c>
+        <v>3044</v>
+      </c>
+      <c r="W21" s="58">
+        <v>1</v>
+      </c>
+      <c r="X21" s="59"/>
+      <c r="Y21" s="60"/>
       <c r="Z21" s="59"/>
       <c r="AA21" s="60"/>
       <c r="AB21" s="59"/>
@@ -41642,53 +41465,53 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" s="64">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>476</v>
+        <v>14</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>2823</v>
+        <v>2820</v>
       </c>
       <c r="D22" t="s">
-        <v>477</v>
+        <v>15</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>2933</v>
+        <v>2927</v>
       </c>
       <c r="F22" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B22, prodcom_data[product], 0))</f>
-        <v>1650938177</v>
+        <v>2000046666</v>
       </c>
       <c r="G22" s="54">
         <f t="shared" si="0"/>
-        <v>1.650938177</v>
+        <v>2.0000466659999998</v>
       </c>
       <c r="H22" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B22, prodcom_data[product], 0))</f>
-        <v>0.98168669522505081</v>
+        <v>0.99997666754441616</v>
       </c>
       <c r="I22" s="49" t="s">
-        <v>2665</v>
+        <v>2662</v>
       </c>
       <c r="J22" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K22" s="79" t="s">
-        <v>2934</v>
+        <v>2928</v>
       </c>
       <c r="L22" s="79">
-        <v>58.08</v>
+        <v>112.21</v>
       </c>
       <c r="M22" s="80" t="s">
-        <v>2892</v>
+        <v>2915</v>
       </c>
       <c r="N22" s="72">
         <f>M22*Calculations!$C$37/L22</f>
-        <v>0.62040289256198355</v>
+        <v>0.85632296586756973</v>
       </c>
       <c r="O22" s="81" t="s">
-        <v>2935</v>
+        <v>2929</v>
       </c>
       <c r="P22" s="59" t="s">
         <v>3036</v>
@@ -41701,7 +41524,7 @@
       <c r="T22" s="59"/>
       <c r="U22" s="63"/>
       <c r="V22" s="59" t="s">
-        <v>3036</v>
+        <v>3044</v>
       </c>
       <c r="W22" s="58">
         <v>1</v>
@@ -41717,34 +41540,34 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" s="64">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>2824</v>
+        <v>2821</v>
       </c>
       <c r="D23" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E23" s="48" t="s">
         <v>2930</v>
       </c>
       <c r="F23" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B23, prodcom_data[product], 0))</f>
-        <v>1592476459</v>
+        <v>1864065177</v>
       </c>
       <c r="G23" s="54">
         <f t="shared" si="0"/>
-        <v>1.592476459</v>
+        <v>1.8640651770000001</v>
       </c>
       <c r="H23" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B23, prodcom_data[product], 0))</f>
-        <v>0.93163807390386044</v>
+        <v>0.88707249478326589</v>
       </c>
       <c r="I23" s="49" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="J23" s="49" t="s">
         <v>2642</v>
@@ -41776,7 +41599,7 @@
       <c r="T23" s="59"/>
       <c r="U23" s="63"/>
       <c r="V23" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W23" s="58">
         <v>1</v>
@@ -41792,81 +41615,81 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" s="64">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>2825</v>
+        <v>2822</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="E24" s="48" t="s">
-        <v>2943</v>
+        <v>2936</v>
       </c>
       <c r="F24" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B24, prodcom_data[product], 0))</f>
-        <v>1202939382</v>
+        <v>1795747967</v>
       </c>
       <c r="G24" s="54">
         <f t="shared" si="0"/>
-        <v>1.2029393820000001</v>
+        <v>1.7957479670000001</v>
       </c>
       <c r="H24" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B24, prodcom_data[product], 0))</f>
-        <v>0.7564803460728331</v>
+        <v>0.55687101886052137</v>
       </c>
       <c r="I24" s="49" t="s">
-        <v>2667</v>
+        <v>2664</v>
       </c>
       <c r="J24" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K24" s="79" t="s">
-        <v>2944</v>
+        <v>2937</v>
       </c>
       <c r="L24" s="79">
-        <v>98.96</v>
+        <v>62.07</v>
       </c>
       <c r="M24" s="80" t="s">
         <v>2898</v>
       </c>
       <c r="N24" s="72">
         <f>M24*Calculations!$C$37/L24</f>
-        <v>0.24274454324979791</v>
+        <v>0.38701466086676328</v>
       </c>
       <c r="O24" s="81" t="s">
-        <v>2945</v>
+        <v>2938</v>
       </c>
       <c r="P24" s="59" t="s">
         <v>3036</v>
       </c>
-      <c r="Q24" s="58">
-        <v>0.86</v>
+      <c r="Q24" s="60">
+        <v>0.56000000000000005</v>
       </c>
       <c r="R24" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S24" s="61" cm="1">
         <f t="array" ref="S24">1-SUM(IF(ISNUMBER(P24:Q24), P24:Q24, 0))</f>
-        <v>0.14000000000000001</v>
+        <v>0.43999999999999995</v>
       </c>
       <c r="T24" s="59"/>
       <c r="U24" s="63"/>
       <c r="V24" s="59" t="s">
         <v>3036</v>
       </c>
-      <c r="W24" s="58">
-        <v>0.86</v>
+      <c r="W24" s="60">
+        <v>0.56000000000000005</v>
       </c>
       <c r="X24" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y24" s="61" cm="1">
         <f t="array" ref="Y24">1-SUM(IF(ISNUMBER(V24:W24), V24:W24, 0))</f>
-        <v>0.14000000000000001</v>
+        <v>0.43999999999999995</v>
       </c>
       <c r="Z24" s="59"/>
       <c r="AA24" s="60"/>
@@ -41877,82 +41700,72 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" s="64">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>476</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>2826</v>
+        <v>2823</v>
       </c>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="E25" s="48" t="s">
-        <v>44</v>
+        <v>2933</v>
       </c>
       <c r="F25" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B25, prodcom_data[product], 0))</f>
-        <v>1191905947</v>
+        <v>1650938177</v>
       </c>
       <c r="G25" s="54">
         <f t="shared" si="0"/>
-        <v>1.191905947</v>
+        <v>1.650938177</v>
       </c>
       <c r="H25" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B25, prodcom_data[product], 0))</f>
-        <v>0.46597635861951109</v>
+        <v>0.98168669522505081</v>
       </c>
       <c r="I25" s="49" t="s">
-        <v>2668</v>
+        <v>2665</v>
       </c>
       <c r="J25" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K25" s="79" t="s">
-        <v>2980</v>
+        <v>2934</v>
       </c>
       <c r="L25" s="79">
-        <v>106.16</v>
+        <v>58.08</v>
       </c>
       <c r="M25" s="80" t="s">
-        <v>2915</v>
+        <v>2892</v>
       </c>
       <c r="N25" s="72">
         <f>M25*Calculations!$C$37/L25</f>
-        <v>0.90512434061793512</v>
+        <v>0.62040289256198355</v>
       </c>
       <c r="O25" s="81" t="s">
-        <v>2981</v>
+        <v>2935</v>
       </c>
       <c r="P25" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q25" s="58">
-        <v>0.48</v>
-      </c>
-      <c r="R25" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S25" s="61" cm="1">
-        <f t="array" ref="S25">1-SUM(IF(ISNUMBER(P25:Q25), P25:Q25, 0))</f>
-        <v>0.52</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R25" s="59"/>
+      <c r="S25" s="60"/>
       <c r="T25" s="59"/>
       <c r="U25" s="63"/>
       <c r="V25" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W25" s="58">
-        <v>0.48</v>
-      </c>
-      <c r="X25" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y25" s="61" cm="1">
-        <f t="array" ref="Y25">1-SUM(IF(ISNUMBER(V25:W25), V25:W25, 0))</f>
-        <v>0.52</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X25" s="59"/>
+      <c r="Y25" s="60"/>
       <c r="Z25" s="59"/>
       <c r="AA25" s="60"/>
       <c r="AB25" s="59"/>
@@ -41962,56 +41775,56 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" s="64">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>551</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>2827</v>
+        <v>2824</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>552</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>38</v>
+        <v>2930</v>
       </c>
       <c r="F26" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B26, prodcom_data[product], 0))</f>
-        <v>1120381615</v>
+        <v>1592476459</v>
       </c>
       <c r="G26" s="54">
         <f t="shared" si="0"/>
-        <v>1.1203816150000001</v>
+        <v>1.592476459</v>
       </c>
       <c r="H26" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B26, prodcom_data[product], 0))</f>
-        <v>0.97878773028598831</v>
+        <v>0.93163807390386044</v>
       </c>
       <c r="I26" s="49" t="s">
-        <v>2669</v>
+        <v>2666</v>
       </c>
       <c r="J26" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K26" s="79" t="s">
-        <v>2946</v>
+        <v>2931</v>
       </c>
       <c r="L26" s="79">
-        <v>92.14</v>
+        <v>104.15199999999999</v>
       </c>
       <c r="M26" s="80" t="s">
-        <v>2947</v>
+        <v>2915</v>
       </c>
       <c r="N26" s="72">
         <f>M26*Calculations!$C$37/L26</f>
-        <v>0.91249186021271977</v>
+        <v>0.92257469851755136</v>
       </c>
       <c r="O26" s="81" t="s">
-        <v>2948</v>
+        <v>2932</v>
       </c>
       <c r="P26" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q26" s="58">
         <v>1</v>
@@ -42021,7 +41834,7 @@
       <c r="T26" s="59"/>
       <c r="U26" s="63"/>
       <c r="V26" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W26" s="58">
         <v>1</v>
@@ -42037,66 +41850,66 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" s="64">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>420</v>
+        <v>72</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>2828</v>
+        <v>2825</v>
       </c>
       <c r="D27" t="s">
-        <v>421</v>
+        <v>73</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>421</v>
+        <v>2943</v>
       </c>
       <c r="F27" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B27, prodcom_data[product], 0))</f>
-        <v>1090852807</v>
+        <v>1202939382</v>
       </c>
       <c r="G27" s="54">
         <f t="shared" si="0"/>
-        <v>1.0908528070000001</v>
+        <v>1.2029393820000001</v>
       </c>
       <c r="H27" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B27, prodcom_data[product], 0))</f>
-        <v>0.92846915963429333</v>
+        <v>0.7564803460728331</v>
       </c>
       <c r="I27" s="49" t="s">
-        <v>2670</v>
+        <v>2667</v>
       </c>
       <c r="J27" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K27" s="79" t="s">
-        <v>2934</v>
+        <v>2944</v>
       </c>
       <c r="L27" s="79">
-        <v>58.08</v>
+        <v>98.96</v>
       </c>
       <c r="M27" s="80" t="s">
-        <v>2892</v>
+        <v>2898</v>
       </c>
       <c r="N27" s="72">
         <f>M27*Calculations!$C$37/L27</f>
-        <v>0.62040289256198355</v>
+        <v>0.24274454324979791</v>
       </c>
       <c r="O27" s="81" t="s">
-        <v>2942</v>
+        <v>2945</v>
       </c>
       <c r="P27" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q27" s="58">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="R27" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S27" s="61" cm="1">
         <f t="array" ref="S27">1-SUM(IF(ISNUMBER(P27:Q27), P27:Q27, 0))</f>
-        <v>6.9999999999999951E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="T27" s="59"/>
       <c r="U27" s="63"/>
@@ -42104,14 +41917,14 @@
         <v>3036</v>
       </c>
       <c r="W27" s="58">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="X27" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y27" s="61" cm="1">
         <f t="array" ref="Y27">1-SUM(IF(ISNUMBER(V27:W27), V27:W27, 0))</f>
-        <v>6.9999999999999951E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Z27" s="59"/>
       <c r="AA27" s="60"/>
@@ -42122,72 +41935,82 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" s="64">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>387</v>
+        <v>43</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>2830</v>
+        <v>2826</v>
       </c>
       <c r="D28" t="s">
-        <v>388</v>
+        <v>44</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>2952</v>
+        <v>44</v>
       </c>
       <c r="F28" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B28, prodcom_data[product], 0))</f>
-        <v>931200527</v>
+        <v>1191905947</v>
       </c>
       <c r="G28" s="54">
         <f t="shared" si="0"/>
-        <v>0.931200527</v>
+        <v>1.191905947</v>
       </c>
       <c r="H28" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B28, prodcom_data[product], 0))</f>
-        <v>0.97723312392412343</v>
+        <v>0.46597635861951109</v>
       </c>
       <c r="I28" s="49" t="s">
-        <v>2672</v>
+        <v>2668</v>
       </c>
       <c r="J28" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K28" s="79" t="s">
-        <v>2953</v>
+        <v>2980</v>
       </c>
       <c r="L28" s="79">
-        <v>30.026</v>
+        <v>106.16</v>
       </c>
       <c r="M28" s="80" t="s">
-        <v>2905</v>
+        <v>2915</v>
       </c>
       <c r="N28" s="72">
         <f>M28*Calculations!$C$37/L28</f>
-        <v>0.40001998268167588</v>
+        <v>0.90512434061793512</v>
       </c>
       <c r="O28" s="81" t="s">
-        <v>2954</v>
+        <v>2981</v>
       </c>
       <c r="P28" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q28" s="58">
-        <v>1</v>
-      </c>
-      <c r="R28" s="59"/>
-      <c r="S28" s="60"/>
+        <v>0.48</v>
+      </c>
+      <c r="R28" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S28" s="61" cm="1">
+        <f t="array" ref="S28">1-SUM(IF(ISNUMBER(P28:Q28), P28:Q28, 0))</f>
+        <v>0.52</v>
+      </c>
       <c r="T28" s="59"/>
       <c r="U28" s="63"/>
       <c r="V28" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W28" s="58">
-        <v>1</v>
-      </c>
-      <c r="X28" s="59"/>
-      <c r="Y28" s="60"/>
+        <v>0.48</v>
+      </c>
+      <c r="X28" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y28" s="61" cm="1">
+        <f t="array" ref="Y28">1-SUM(IF(ISNUMBER(V28:W28), V28:W28, 0))</f>
+        <v>0.52</v>
+      </c>
       <c r="Z28" s="59"/>
       <c r="AA28" s="60"/>
       <c r="AB28" s="59"/>
@@ -42197,53 +42020,53 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" s="64">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>620</v>
+        <v>37</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>2831</v>
+        <v>2827</v>
       </c>
       <c r="D29" t="s">
-        <v>621</v>
+        <v>38</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>2939</v>
+        <v>38</v>
       </c>
       <c r="F29" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B29, prodcom_data[product], 0))</f>
-        <v>914892768</v>
+        <v>1120381615</v>
       </c>
       <c r="G29" s="54">
         <f t="shared" si="0"/>
-        <v>0.91489276799999997</v>
+        <v>1.1203816150000001</v>
       </c>
       <c r="H29" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B29, prodcom_data[product], 0))</f>
-        <v>0.98372184312642852</v>
+        <v>0.97878773028598831</v>
       </c>
       <c r="I29" s="49" t="s">
-        <v>2673</v>
+        <v>2669</v>
       </c>
       <c r="J29" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K29" s="79" t="s">
-        <v>2940</v>
+        <v>2946</v>
       </c>
       <c r="L29" s="79">
-        <v>86.09</v>
+        <v>92.14</v>
       </c>
       <c r="M29" s="80" t="s">
-        <v>2925</v>
+        <v>2947</v>
       </c>
       <c r="N29" s="72">
         <f>M29*Calculations!$C$37/L29</f>
-        <v>0.55806713904053895</v>
+        <v>0.91249186021271977</v>
       </c>
       <c r="O29" s="81" t="s">
-        <v>2941</v>
+        <v>2948</v>
       </c>
       <c r="P29" s="59" t="s">
         <v>3036</v>
@@ -42272,72 +42095,82 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" s="64">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>205</v>
+        <v>420</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>2832</v>
+        <v>2828</v>
       </c>
       <c r="D30" t="s">
-        <v>206</v>
+        <v>421</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>206</v>
+        <v>421</v>
       </c>
       <c r="F30" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B30, prodcom_data[product], 0))</f>
-        <v>888564975</v>
+        <v>1090852807</v>
       </c>
       <c r="G30" s="54">
         <f t="shared" si="0"/>
-        <v>0.88856497499999998</v>
+        <v>1.0908528070000001</v>
       </c>
       <c r="H30" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B30, prodcom_data[product], 0))</f>
-        <v>0.16881151544376369</v>
+        <v>0.92846915963429333</v>
       </c>
       <c r="I30" s="49" t="s">
-        <v>2674</v>
+        <v>2670</v>
       </c>
       <c r="J30" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K30" s="79" t="s">
-        <v>2955</v>
+        <v>2934</v>
       </c>
       <c r="L30" s="79">
-        <v>60.05</v>
+        <v>58.08</v>
       </c>
       <c r="M30" s="80" t="s">
-        <v>2898</v>
+        <v>2892</v>
       </c>
       <c r="N30" s="72">
         <f>M30*Calculations!$C$37/L30</f>
-        <v>0.40003330557868444</v>
+        <v>0.62040289256198355</v>
       </c>
       <c r="O30" s="81" t="s">
-        <v>2956</v>
+        <v>2942</v>
       </c>
       <c r="P30" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q30" s="58">
-        <v>1</v>
-      </c>
-      <c r="R30" s="59"/>
-      <c r="S30" s="60"/>
+        <v>0.93</v>
+      </c>
+      <c r="R30" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S30" s="61" cm="1">
+        <f t="array" ref="S30">1-SUM(IF(ISNUMBER(P30:Q30), P30:Q30, 0))</f>
+        <v>6.9999999999999951E-2</v>
+      </c>
       <c r="T30" s="59"/>
       <c r="U30" s="63"/>
       <c r="V30" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W30" s="58">
-        <v>1</v>
-      </c>
-      <c r="X30" s="59"/>
-      <c r="Y30" s="60"/>
+        <v>0.93</v>
+      </c>
+      <c r="X30" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y30" s="61" cm="1">
+        <f t="array" ref="Y30">1-SUM(IF(ISNUMBER(V30:W30), V30:W30, 0))</f>
+        <v>6.9999999999999951E-2</v>
+      </c>
       <c r="Z30" s="59"/>
       <c r="AA30" s="60"/>
       <c r="AB30" s="59"/>
@@ -42347,53 +42180,53 @@
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" s="64">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>473</v>
+        <v>387</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>2833</v>
+        <v>2830</v>
       </c>
       <c r="D31" t="s">
-        <v>474</v>
+        <v>388</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>2962</v>
+        <v>2952</v>
       </c>
       <c r="F31" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B31, prodcom_data[product], 0))</f>
-        <v>886759378</v>
+        <v>931200527</v>
       </c>
       <c r="G31" s="54">
         <f t="shared" si="0"/>
-        <v>0.88675937800000004</v>
+        <v>0.931200527</v>
       </c>
       <c r="H31" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B31, prodcom_data[product], 0))</f>
-        <v>0.9949802605865421</v>
+        <v>0.97723312392412343</v>
       </c>
       <c r="I31" s="49" t="s">
-        <v>2675</v>
+        <v>2672</v>
       </c>
       <c r="J31" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K31" s="79" t="s">
-        <v>2963</v>
+        <v>2953</v>
       </c>
       <c r="L31" s="79">
-        <v>44.05</v>
+        <v>30.026</v>
       </c>
       <c r="M31" s="80" t="s">
-        <v>2898</v>
+        <v>2905</v>
       </c>
       <c r="N31" s="72">
         <f>M31*Calculations!$C$37/L31</f>
-        <v>0.54533484676503974</v>
+        <v>0.40001998268167588</v>
       </c>
       <c r="O31" s="81" t="s">
-        <v>2964</v>
+        <v>2954</v>
       </c>
       <c r="P31" s="59" t="s">
         <v>3036</v>
@@ -42406,7 +42239,7 @@
       <c r="T31" s="59"/>
       <c r="U31" s="63"/>
       <c r="V31" s="59" t="s">
-        <v>3044</v>
+        <v>3036</v>
       </c>
       <c r="W31" s="58">
         <v>1</v>
@@ -42422,53 +42255,53 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" s="64">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>620</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>2834</v>
+        <v>2831</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>621</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>2961</v>
+        <v>2939</v>
       </c>
       <c r="F32" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B32, prodcom_data[product], 0))</f>
-        <v>882272543</v>
+        <v>914892768</v>
       </c>
       <c r="G32" s="54">
         <f t="shared" si="0"/>
-        <v>0.88227254300000002</v>
+        <v>0.91489276799999997</v>
       </c>
       <c r="H32" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B32, prodcom_data[product], 0))</f>
-        <v>0.90674928778782138</v>
+        <v>0.98372184312642852</v>
       </c>
       <c r="I32" s="49" t="s">
-        <v>2676</v>
+        <v>2673</v>
       </c>
       <c r="J32" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K32" s="79" t="s">
-        <v>2911</v>
+        <v>2940</v>
       </c>
       <c r="L32" s="79">
-        <v>62.5</v>
+        <v>86.09</v>
       </c>
       <c r="M32" s="80" t="s">
-        <v>2898</v>
+        <v>2925</v>
       </c>
       <c r="N32" s="72">
         <f>M32*Calculations!$C$37/L32</f>
-        <v>0.38435199999999997</v>
+        <v>0.55806713904053895</v>
       </c>
       <c r="O32" s="81" t="s">
-        <v>2912</v>
+        <v>2941</v>
       </c>
       <c r="P32" s="59" t="s">
         <v>3036</v>
@@ -42497,82 +42330,72 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33" s="64">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B33" t="s">
-        <v>293</v>
+        <v>205</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>2835</v>
+        <v>2832</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>206</v>
       </c>
       <c r="E33" s="48" t="s">
-        <v>2949</v>
+        <v>206</v>
       </c>
       <c r="F33" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B33, prodcom_data[product], 0))</f>
-        <v>881884158</v>
+        <v>888564975</v>
       </c>
       <c r="G33" s="54">
         <f t="shared" si="0"/>
-        <v>0.88188415799999997</v>
+        <v>0.88856497499999998</v>
       </c>
       <c r="H33" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B33, prodcom_data[product], 0))</f>
-        <v>0.54958148029233567</v>
+        <v>0.16881151544376369</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="J33" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K33" s="79" t="s">
-        <v>2950</v>
+        <v>2955</v>
       </c>
       <c r="L33" s="79">
-        <v>93.13</v>
+        <v>60.05</v>
       </c>
       <c r="M33" s="80" t="s">
-        <v>2908</v>
+        <v>2898</v>
       </c>
       <c r="N33" s="72">
         <f>M33*Calculations!$C$37/L33</f>
-        <v>0.77382153978309898</v>
+        <v>0.40003330557868444</v>
       </c>
       <c r="O33" s="81" t="s">
-        <v>2951</v>
+        <v>2956</v>
       </c>
       <c r="P33" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q33" s="58">
-        <v>0.8</v>
-      </c>
-      <c r="R33" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S33" s="61" cm="1">
-        <f t="array" ref="S33">1-SUM(IF(ISNUMBER(P33:Q33), P33:Q33, 0))</f>
-        <v>0.19999999999999996</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R33" s="59"/>
+      <c r="S33" s="60"/>
       <c r="T33" s="59"/>
       <c r="U33" s="63"/>
       <c r="V33" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W33" s="58">
-        <v>0.8</v>
-      </c>
-      <c r="X33" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y33" s="61" cm="1">
-        <f t="array" ref="Y33">1-SUM(IF(ISNUMBER(V33:W33), V33:W33, 0))</f>
-        <v>0.19999999999999996</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X33" s="59"/>
+      <c r="Y33" s="60"/>
       <c r="Z33" s="59"/>
       <c r="AA33" s="60"/>
       <c r="AB33" s="59"/>
@@ -42582,56 +42405,56 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34" s="64">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>602</v>
+        <v>473</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>2836</v>
+        <v>2833</v>
       </c>
       <c r="D34" t="s">
-        <v>603</v>
+        <v>474</v>
       </c>
       <c r="E34" s="48" t="s">
-        <v>2917</v>
+        <v>2962</v>
       </c>
       <c r="F34" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B34, prodcom_data[product], 0))</f>
-        <v>872335906</v>
+        <v>886759378</v>
       </c>
       <c r="G34" s="54">
         <f t="shared" si="0"/>
-        <v>0.87233590599999999</v>
+        <v>0.88675937800000004</v>
       </c>
       <c r="H34" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B34, prodcom_data[product], 0))</f>
-        <v>0.50439285712492499</v>
+        <v>0.9949802605865421</v>
       </c>
       <c r="I34" s="49" t="s">
-        <v>2657</v>
+        <v>2675</v>
       </c>
       <c r="J34" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K34" s="79" t="s">
-        <v>2918</v>
+        <v>2963</v>
       </c>
       <c r="L34" s="79">
-        <v>222.24</v>
+        <v>44.05</v>
       </c>
       <c r="M34" s="80" t="s">
-        <v>2919</v>
+        <v>2898</v>
       </c>
       <c r="N34" s="72">
         <f>M34*Calculations!$C$37/L34</f>
-        <v>0.64854211663066952</v>
+        <v>0.54533484676503974</v>
       </c>
       <c r="O34" s="81" t="s">
-        <v>2920</v>
+        <v>2964</v>
       </c>
       <c r="P34" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q34" s="58">
         <v>1</v>
@@ -42641,7 +42464,7 @@
       <c r="T34" s="59"/>
       <c r="U34" s="63"/>
       <c r="V34" s="59" t="s">
-        <v>3042</v>
+        <v>3044</v>
       </c>
       <c r="W34" s="58">
         <v>1</v>
@@ -42657,82 +42480,72 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" s="64">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>2837</v>
+        <v>2834</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="E35" s="48" t="s">
-        <v>2983</v>
+        <v>2961</v>
       </c>
       <c r="F35" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B35, prodcom_data[product], 0))</f>
-        <v>848026699</v>
+        <v>882272543</v>
       </c>
       <c r="G35" s="54">
         <f t="shared" si="0"/>
-        <v>0.84802669900000005</v>
+        <v>0.88227254300000002</v>
       </c>
       <c r="H35" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B35, prodcom_data[product], 0))</f>
-        <v>0.94336652483154892</v>
+        <v>0.90674928778782138</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="J35" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K35" s="79" t="s">
-        <v>2984</v>
+        <v>2911</v>
       </c>
       <c r="L35" s="79">
-        <v>76.09</v>
+        <v>62.5</v>
       </c>
       <c r="M35" s="80" t="s">
-        <v>2892</v>
+        <v>2898</v>
       </c>
       <c r="N35" s="72">
         <f>M35*Calculations!$C$37/L35</f>
-        <v>0.47355762912340649</v>
+        <v>0.38435199999999997</v>
       </c>
       <c r="O35" s="81" t="s">
-        <v>2985</v>
+        <v>2912</v>
       </c>
       <c r="P35" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q35" s="58">
-        <v>0.95</v>
-      </c>
-      <c r="R35" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S35" s="61" cm="1">
-        <f t="array" ref="S35">1-SUM(IF(ISNUMBER(P35:Q35), P35:Q35, 0))</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R35" s="59"/>
+      <c r="S35" s="60"/>
       <c r="T35" s="59"/>
       <c r="U35" s="63"/>
       <c r="V35" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W35" s="58">
-        <v>0.95</v>
-      </c>
-      <c r="X35" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y35" s="61" cm="1">
-        <f t="array" ref="Y35">1-SUM(IF(ISNUMBER(V35:W35), V35:W35, 0))</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X35" s="59"/>
+      <c r="Y35" s="60"/>
       <c r="Z35" s="59"/>
       <c r="AA35" s="60"/>
       <c r="AB35" s="59"/>
@@ -42742,72 +42555,82 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" s="64">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B36" t="s">
-        <v>557</v>
+        <v>293</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>2838</v>
+        <v>2835</v>
       </c>
       <c r="D36" t="s">
-        <v>558</v>
+        <v>294</v>
       </c>
       <c r="E36" s="48" t="s">
-        <v>2957</v>
+        <v>2949</v>
       </c>
       <c r="F36" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B36, prodcom_data[product], 0))</f>
-        <v>846217183</v>
+        <v>881884158</v>
       </c>
       <c r="G36" s="54">
         <f t="shared" si="0"/>
-        <v>0.84621718300000004</v>
+        <v>0.88188415799999997</v>
       </c>
       <c r="H36" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B36, prodcom_data[product], 0))</f>
-        <v>0.71535186139088358</v>
+        <v>0.54958148029233567</v>
       </c>
       <c r="I36" s="49" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="J36" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K36" s="79" t="s">
-        <v>2958</v>
+        <v>2950</v>
       </c>
       <c r="L36" s="79">
-        <v>211.3</v>
+        <v>93.13</v>
       </c>
       <c r="M36" s="80" t="s">
-        <v>2959</v>
+        <v>2908</v>
       </c>
       <c r="N36" s="72">
         <f>M36*Calculations!$C$37/L36</f>
-        <v>0.85265026029342161</v>
+        <v>0.77382153978309898</v>
       </c>
       <c r="O36" s="81" t="s">
-        <v>2960</v>
+        <v>2951</v>
       </c>
       <c r="P36" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q36" s="58">
-        <v>1</v>
-      </c>
-      <c r="R36" s="59"/>
-      <c r="S36" s="60"/>
+        <v>0.8</v>
+      </c>
+      <c r="R36" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S36" s="61" cm="1">
+        <f t="array" ref="S36">1-SUM(IF(ISNUMBER(P36:Q36), P36:Q36, 0))</f>
+        <v>0.19999999999999996</v>
+      </c>
       <c r="T36" s="59"/>
       <c r="U36" s="63"/>
       <c r="V36" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W36" s="58">
-        <v>1</v>
-      </c>
-      <c r="X36" s="59"/>
-      <c r="Y36" s="60"/>
+        <v>0.8</v>
+      </c>
+      <c r="X36" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y36" s="61" cm="1">
+        <f t="array" ref="Y36">1-SUM(IF(ISNUMBER(V36:W36), V36:W36, 0))</f>
+        <v>0.19999999999999996</v>
+      </c>
       <c r="Z36" s="59"/>
       <c r="AA36" s="60"/>
       <c r="AB36" s="59"/>
@@ -42817,82 +42640,72 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" s="64">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>602</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>2839</v>
+        <v>2836</v>
       </c>
       <c r="D37" t="s">
-        <v>47</v>
+        <v>603</v>
       </c>
       <c r="E37" s="48" t="s">
-        <v>2992</v>
+        <v>2917</v>
       </c>
       <c r="F37" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B37, prodcom_data[product], 0))</f>
-        <v>821433537</v>
+        <v>872335906</v>
       </c>
       <c r="G37" s="54">
         <f t="shared" si="0"/>
-        <v>0.82143353699999999</v>
+        <v>0.87233590599999999</v>
       </c>
       <c r="H37" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B37, prodcom_data[product], 0))</f>
-        <v>0.97390715616715806</v>
+        <v>0.50439285712492499</v>
       </c>
       <c r="I37" s="49" t="s">
-        <v>2680</v>
+        <v>2657</v>
       </c>
       <c r="J37" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K37" s="79" t="s">
-        <v>2980</v>
+        <v>2918</v>
       </c>
       <c r="L37" s="79">
-        <v>106.16</v>
+        <v>222.24</v>
       </c>
       <c r="M37" s="80" t="s">
-        <v>2915</v>
+        <v>2919</v>
       </c>
       <c r="N37" s="72">
         <f>M37*Calculations!$C$37/L37</f>
-        <v>0.90512434061793512</v>
+        <v>0.64854211663066952</v>
       </c>
       <c r="O37" s="81" t="s">
-        <v>2993</v>
+        <v>2920</v>
       </c>
       <c r="P37" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q37" s="58">
-        <v>0.97</v>
-      </c>
-      <c r="R37" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S37" s="61" cm="1">
-        <f t="array" ref="S37">1-SUM(IF(ISNUMBER(P37:Q37), P37:Q37, 0))</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R37" s="59"/>
+      <c r="S37" s="60"/>
       <c r="T37" s="59"/>
       <c r="U37" s="63"/>
       <c r="V37" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W37" s="58">
-        <v>0.97</v>
-      </c>
-      <c r="X37" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y37" s="61" cm="1">
-        <f t="array" ref="Y37">1-SUM(IF(ISNUMBER(V37:W37), V37:W37, 0))</f>
-        <v>3.0000000000000027E-2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X37" s="59"/>
+      <c r="Y37" s="60"/>
       <c r="Z37" s="59"/>
       <c r="AA37" s="60"/>
       <c r="AB37" s="59"/>
@@ -42902,66 +42715,66 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" s="64">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B38" t="s">
-        <v>569</v>
+        <v>135</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>2840</v>
+        <v>2837</v>
       </c>
       <c r="D38" t="s">
-        <v>570</v>
+        <v>136</v>
       </c>
       <c r="E38" s="48" t="s">
-        <v>2910</v>
+        <v>2983</v>
       </c>
       <c r="F38" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B38, prodcom_data[product], 0))</f>
-        <v>790721030</v>
+        <v>848026699</v>
       </c>
       <c r="G38" s="54">
         <f t="shared" si="0"/>
-        <v>0.79072103000000005</v>
+        <v>0.84802669900000005</v>
       </c>
       <c r="H38" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B38, prodcom_data[product], 0))</f>
-        <v>0.93548794446506622</v>
+        <v>0.94336652483154892</v>
       </c>
       <c r="I38" s="49" t="s">
-        <v>2681</v>
+        <v>2678</v>
       </c>
       <c r="J38" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K38" s="79" t="s">
-        <v>2911</v>
+        <v>2984</v>
       </c>
       <c r="L38" s="79">
-        <v>62.5</v>
+        <v>76.09</v>
       </c>
       <c r="M38" s="80" t="s">
-        <v>2898</v>
+        <v>2892</v>
       </c>
       <c r="N38" s="72">
         <f>M38*Calculations!$C$37/L38</f>
-        <v>0.38435199999999997</v>
+        <v>0.47355762912340649</v>
       </c>
       <c r="O38" s="81" t="s">
-        <v>2912</v>
+        <v>2985</v>
       </c>
       <c r="P38" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q38" s="58">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="R38" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S38" s="61" cm="1">
         <f t="array" ref="S38">1-SUM(IF(ISNUMBER(P38:Q38), P38:Q38, 0))</f>
-        <v>2.0000000000000018E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="T38" s="59"/>
       <c r="U38" s="63"/>
@@ -42969,14 +42782,14 @@
         <v>3036</v>
       </c>
       <c r="W38" s="58">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="X38" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y38" s="61" cm="1">
         <f t="array" ref="Y38">1-SUM(IF(ISNUMBER(V38:W38), V38:W38, 0))</f>
-        <v>2.0000000000000018E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="Z38" s="59"/>
       <c r="AA38" s="60"/>
@@ -42987,82 +42800,72 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" s="64">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>557</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>2841</v>
+        <v>2838</v>
       </c>
       <c r="D39" t="s">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="E39" s="48" t="s">
-        <v>56</v>
+        <v>2957</v>
       </c>
       <c r="F39" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B39, prodcom_data[product], 0))</f>
-        <v>778495527</v>
+        <v>846217183</v>
       </c>
       <c r="G39" s="54">
         <f t="shared" si="0"/>
-        <v>0.77849552700000002</v>
+        <v>0.84621718300000004</v>
       </c>
       <c r="H39" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B39, prodcom_data[product], 0))</f>
-        <v>0.9345821199560983</v>
+        <v>0.71535186139088358</v>
       </c>
       <c r="I39" s="49" t="s">
-        <v>2682</v>
+        <v>2679</v>
       </c>
       <c r="J39" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K39" s="79" t="s">
-        <v>2973</v>
+        <v>2958</v>
       </c>
       <c r="L39" s="79">
-        <v>120.19</v>
+        <v>211.3</v>
       </c>
       <c r="M39" s="80" t="s">
-        <v>2974</v>
+        <v>2959</v>
       </c>
       <c r="N39" s="72">
         <f>M39*Calculations!$C$37/L39</f>
-        <v>0.89940094849821106</v>
+        <v>0.85265026029342161</v>
       </c>
       <c r="O39" s="81" t="s">
-        <v>2975</v>
+        <v>2960</v>
       </c>
       <c r="P39" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q39" s="58">
-        <v>0.94</v>
-      </c>
-      <c r="R39" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S39" s="61" cm="1">
-        <f t="array" ref="S39">1-SUM(IF(ISNUMBER(P39:Q39), P39:Q39, 0))</f>
-        <v>6.0000000000000053E-2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R39" s="59"/>
+      <c r="S39" s="60"/>
       <c r="T39" s="59"/>
       <c r="U39" s="63"/>
       <c r="V39" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W39" s="58">
-        <v>0.94</v>
-      </c>
-      <c r="X39" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y39" s="61" cm="1">
-        <f t="array" ref="Y39">1-SUM(IF(ISNUMBER(V39:W39), V39:W39, 0))</f>
-        <v>6.0000000000000053E-2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X39" s="59"/>
+      <c r="Y39" s="60"/>
       <c r="Z39" s="59"/>
       <c r="AA39" s="60"/>
       <c r="AB39" s="59"/>
@@ -43072,72 +42875,82 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" s="64">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>332</v>
+        <v>46</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>2842</v>
+        <v>2839</v>
       </c>
       <c r="D40" t="s">
-        <v>333</v>
+        <v>47</v>
       </c>
       <c r="E40" s="48" t="s">
-        <v>333</v>
+        <v>2992</v>
       </c>
       <c r="F40" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B40, prodcom_data[product], 0))</f>
-        <v>705069102</v>
+        <v>821433537</v>
       </c>
       <c r="G40" s="54">
         <f t="shared" si="0"/>
-        <v>0.70506910199999995</v>
+        <v>0.82143353699999999</v>
       </c>
       <c r="H40" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B40, prodcom_data[product], 0))</f>
-        <v>0.85098041922137724</v>
+        <v>0.97390715616715806</v>
       </c>
       <c r="I40" s="49" t="s">
-        <v>2683</v>
+        <v>2680</v>
       </c>
       <c r="J40" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K40" s="79" t="s">
-        <v>2998</v>
+        <v>2980</v>
       </c>
       <c r="L40" s="79">
-        <v>53.06</v>
+        <v>106.16</v>
       </c>
       <c r="M40" s="80" t="s">
-        <v>2892</v>
+        <v>2915</v>
       </c>
       <c r="N40" s="72">
         <f>M40*Calculations!$C$37/L40</f>
-        <v>0.67909913305691672</v>
+        <v>0.90512434061793512</v>
       </c>
       <c r="O40" s="81" t="s">
-        <v>2999</v>
+        <v>2993</v>
       </c>
       <c r="P40" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q40" s="58">
-        <v>1</v>
-      </c>
-      <c r="R40" s="59"/>
-      <c r="S40" s="60"/>
+        <v>0.97</v>
+      </c>
+      <c r="R40" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S40" s="61" cm="1">
+        <f t="array" ref="S40">1-SUM(IF(ISNUMBER(P40:Q40), P40:Q40, 0))</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
       <c r="T40" s="59"/>
       <c r="U40" s="63"/>
       <c r="V40" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W40" s="58">
-        <v>1</v>
-      </c>
-      <c r="X40" s="59"/>
-      <c r="Y40" s="60"/>
+        <v>0.97</v>
+      </c>
+      <c r="X40" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y40" s="61" cm="1">
+        <f t="array" ref="Y40">1-SUM(IF(ISNUMBER(V40:W40), V40:W40, 0))</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
       <c r="Z40" s="59"/>
       <c r="AA40" s="60"/>
       <c r="AB40" s="59"/>
@@ -43147,72 +42960,82 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" s="64">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>569</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>570</v>
       </c>
       <c r="E41" s="48" t="s">
-        <v>29</v>
+        <v>2910</v>
       </c>
       <c r="F41" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B41, prodcom_data[product], 0))</f>
-        <v>683315016</v>
+        <v>790721030</v>
       </c>
       <c r="G41" s="54">
         <f t="shared" si="0"/>
-        <v>0.683315016</v>
+        <v>0.79072103000000005</v>
       </c>
       <c r="H41" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B41, prodcom_data[product], 0))</f>
-        <v>0.35122892718634474</v>
+        <v>0.93548794446506622</v>
       </c>
       <c r="I41" s="49" t="s">
-        <v>2684</v>
+        <v>2681</v>
       </c>
       <c r="J41" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K41" s="79" t="s">
-        <v>2976</v>
+        <v>2911</v>
       </c>
       <c r="L41" s="79">
-        <v>84.16</v>
+        <v>62.5</v>
       </c>
       <c r="M41" s="80" t="s">
-        <v>2908</v>
+        <v>2898</v>
       </c>
       <c r="N41" s="72">
         <f>M41*Calculations!$C$37/L41</f>
-        <v>0.85629752851711038</v>
+        <v>0.38435199999999997</v>
       </c>
       <c r="O41" s="81" t="s">
-        <v>2977</v>
+        <v>2912</v>
       </c>
       <c r="P41" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q41" s="58">
-        <v>1</v>
-      </c>
-      <c r="R41" s="59"/>
-      <c r="S41" s="60"/>
+        <v>0.98</v>
+      </c>
+      <c r="R41" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S41" s="61" cm="1">
+        <f t="array" ref="S41">1-SUM(IF(ISNUMBER(P41:Q41), P41:Q41, 0))</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
       <c r="T41" s="59"/>
       <c r="U41" s="63"/>
       <c r="V41" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W41" s="58">
-        <v>1</v>
-      </c>
-      <c r="X41" s="59"/>
-      <c r="Y41" s="60"/>
+        <v>0.98</v>
+      </c>
+      <c r="X41" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y41" s="61" cm="1">
+        <f t="array" ref="Y41">1-SUM(IF(ISNUMBER(V41:W41), V41:W41, 0))</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
       <c r="Z41" s="59"/>
       <c r="AA41" s="60"/>
       <c r="AB41" s="59"/>
@@ -43222,72 +43045,82 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" s="64">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>252</v>
+        <v>55</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>2844</v>
+        <v>2841</v>
       </c>
       <c r="D42" t="s">
-        <v>253</v>
+        <v>56</v>
       </c>
       <c r="E42" s="48" t="s">
-        <v>2867</v>
+        <v>56</v>
       </c>
       <c r="F42" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B42, prodcom_data[product], 0))</f>
-        <v>667655569</v>
+        <v>778495527</v>
       </c>
       <c r="G42" s="54">
         <f t="shared" si="0"/>
-        <v>0.667655569</v>
+        <v>0.77849552700000002</v>
       </c>
       <c r="H42" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B42, prodcom_data[product], 0))</f>
-        <v>0.85514301162071182</v>
+        <v>0.9345821199560983</v>
       </c>
       <c r="I42" s="49" t="s">
-        <v>2685</v>
+        <v>2682</v>
       </c>
       <c r="J42" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K42" s="79" t="s">
-        <v>2978</v>
+        <v>2973</v>
       </c>
       <c r="L42" s="79">
-        <v>146.13999999999999</v>
+        <v>120.19</v>
       </c>
       <c r="M42" s="80" t="s">
-        <v>2908</v>
+        <v>2974</v>
       </c>
       <c r="N42" s="72">
         <f>M42*Calculations!$C$37/L42</f>
-        <v>0.49312987546188591</v>
+        <v>0.89940094849821106</v>
       </c>
       <c r="O42" s="81" t="s">
-        <v>2979</v>
+        <v>2975</v>
       </c>
       <c r="P42" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q42" s="58">
-        <v>1</v>
-      </c>
-      <c r="R42" s="59"/>
-      <c r="S42" s="60"/>
+        <v>0.94</v>
+      </c>
+      <c r="R42" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S42" s="61" cm="1">
+        <f t="array" ref="S42">1-SUM(IF(ISNUMBER(P42:Q42), P42:Q42, 0))</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
       <c r="T42" s="59"/>
       <c r="U42" s="63"/>
       <c r="V42" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W42" s="58">
-        <v>1</v>
-      </c>
-      <c r="X42" s="59"/>
-      <c r="Y42" s="60"/>
+        <v>0.94</v>
+      </c>
+      <c r="X42" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y42" s="61" cm="1">
+        <f t="array" ref="Y42">1-SUM(IF(ISNUMBER(V42:W42), V42:W42, 0))</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
       <c r="Z42" s="59"/>
       <c r="AA42" s="60"/>
       <c r="AB42" s="59"/>
@@ -43297,82 +43130,72 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" s="64">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>332</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>2845</v>
+        <v>2842</v>
       </c>
       <c r="D43" t="s">
-        <v>115</v>
+        <v>333</v>
       </c>
       <c r="E43" s="48" t="s">
-        <v>2970</v>
+        <v>333</v>
       </c>
       <c r="F43" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B43, prodcom_data[product], 0))</f>
-        <v>667347651</v>
+        <v>705069102</v>
       </c>
       <c r="G43" s="54">
         <f t="shared" si="0"/>
-        <v>0.66734765100000004</v>
+        <v>0.70506910199999995</v>
       </c>
       <c r="H43" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B43, prodcom_data[product], 0))</f>
-        <v>0.80917344833809868</v>
+        <v>0.85098041922137724</v>
       </c>
       <c r="I43" s="49" t="s">
-        <v>2686</v>
+        <v>2683</v>
       </c>
       <c r="J43" s="49" t="s">
-        <v>2687</v>
+        <v>2642</v>
       </c>
       <c r="K43" s="79" t="s">
-        <v>2971</v>
+        <v>2998</v>
       </c>
       <c r="L43" s="79">
-        <v>60.1</v>
+        <v>53.06</v>
       </c>
       <c r="M43" s="80" t="s">
         <v>2892</v>
       </c>
       <c r="N43" s="72">
         <f>M43*Calculations!$C$37/L43</f>
-        <v>0.59955074875207992</v>
+        <v>0.67909913305691672</v>
       </c>
       <c r="O43" s="81" t="s">
-        <v>2972</v>
+        <v>2999</v>
       </c>
       <c r="P43" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q43" s="58">
-        <v>0.82</v>
-      </c>
-      <c r="R43" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S43" s="61" cm="1">
-        <f t="array" ref="S43">1-SUM(IF(ISNUMBER(P43:Q43), P43:Q43, 0))</f>
-        <v>0.18000000000000005</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R43" s="59"/>
+      <c r="S43" s="60"/>
       <c r="T43" s="59"/>
       <c r="U43" s="63"/>
       <c r="V43" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W43" s="58">
-        <v>0.82</v>
-      </c>
-      <c r="X43" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y43" s="61" cm="1">
-        <f t="array" ref="Y43">1-SUM(IF(ISNUMBER(V43:W43), V43:W43, 0))</f>
-        <v>0.18000000000000005</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X43" s="59"/>
+      <c r="Y43" s="60"/>
       <c r="Z43" s="59"/>
       <c r="AA43" s="60"/>
       <c r="AB43" s="59"/>
@@ -43382,56 +43205,56 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" s="64">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B44" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E44" s="48" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F44" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B44, prodcom_data[product], 0))</f>
-        <v>642497260</v>
+        <v>683315016</v>
       </c>
       <c r="G44" s="54">
         <f t="shared" si="0"/>
-        <v>0.64249725999999996</v>
+        <v>0.683315016</v>
       </c>
       <c r="H44" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B44, prodcom_data[product], 0))</f>
-        <v>0.93385612259264728</v>
+        <v>0.35122892718634474</v>
       </c>
       <c r="I44" s="49" t="s">
-        <v>2688</v>
+        <v>2684</v>
       </c>
       <c r="J44" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K44" s="79" t="s">
-        <v>2980</v>
+        <v>2976</v>
       </c>
       <c r="L44" s="79">
-        <v>106.16</v>
+        <v>84.16</v>
       </c>
       <c r="M44" s="80" t="s">
-        <v>2915</v>
+        <v>2908</v>
       </c>
       <c r="N44" s="72">
         <f>M44*Calculations!$C$37/L44</f>
-        <v>0.90512434061793512</v>
+        <v>0.85629752851711038</v>
       </c>
       <c r="O44" s="81" t="s">
-        <v>2982</v>
+        <v>2977</v>
       </c>
       <c r="P44" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q44" s="58">
         <v>1</v>
@@ -43441,7 +43264,7 @@
       <c r="T44" s="59"/>
       <c r="U44" s="63"/>
       <c r="V44" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W44" s="58">
         <v>1</v>
@@ -43457,82 +43280,72 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A45" s="64">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B45" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>2847</v>
+        <v>2844</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>221</v>
+        <v>2867</v>
       </c>
       <c r="F45" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B45, prodcom_data[product], 0))</f>
-        <v>604861873</v>
+        <v>667655569</v>
       </c>
       <c r="G45" s="54">
         <f t="shared" si="0"/>
-        <v>0.60486187300000005</v>
+        <v>0.667655569</v>
       </c>
       <c r="H45" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B45, prodcom_data[product], 0))</f>
-        <v>0.66130800742337414</v>
+        <v>0.85514301162071182</v>
       </c>
       <c r="I45" s="49" t="s">
-        <v>2652</v>
+        <v>2685</v>
       </c>
       <c r="J45" s="49" t="s">
-        <v>2689</v>
+        <v>2642</v>
       </c>
       <c r="K45" s="79" t="s">
-        <v>2968</v>
+        <v>2978</v>
       </c>
       <c r="L45" s="79">
-        <v>128.16900000000001</v>
+        <v>146.13999999999999</v>
       </c>
       <c r="M45" s="80" t="s">
-        <v>2947</v>
+        <v>2908</v>
       </c>
       <c r="N45" s="72">
         <f>M45*Calculations!$C$37/L45</f>
-        <v>0.6559854567016985</v>
+        <v>0.49312987546188591</v>
       </c>
       <c r="O45" s="81" t="s">
-        <v>2969</v>
+        <v>2979</v>
       </c>
       <c r="P45" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q45" s="58">
-        <v>0.72</v>
-      </c>
-      <c r="R45" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S45" s="61" cm="1">
-        <f t="array" ref="S45">1-SUM(IF(ISNUMBER(P45:Q45), P45:Q45, 0))</f>
-        <v>0.28000000000000003</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R45" s="59"/>
+      <c r="S45" s="60"/>
       <c r="T45" s="59"/>
       <c r="U45" s="63"/>
       <c r="V45" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W45" s="58">
-        <v>0.72</v>
-      </c>
-      <c r="X45" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y45" s="61" cm="1">
-        <f t="array" ref="Y45">1-SUM(IF(ISNUMBER(V45:W45), V45:W45, 0))</f>
-        <v>0.28000000000000003</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X45" s="59"/>
+      <c r="Y45" s="60"/>
       <c r="Z45" s="59"/>
       <c r="AA45" s="60"/>
       <c r="AB45" s="59"/>
@@ -43542,66 +43355,66 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A46" s="64">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>542</v>
+        <v>114</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>2848</v>
+        <v>2845</v>
       </c>
       <c r="D46" t="s">
-        <v>543</v>
+        <v>115</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>2965</v>
+        <v>2970</v>
       </c>
       <c r="F46" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B46, prodcom_data[product], 0))</f>
-        <v>593659673</v>
+        <v>667347651</v>
       </c>
       <c r="G46" s="54">
         <f t="shared" si="0"/>
-        <v>0.593659673</v>
+        <v>0.66734765100000004</v>
       </c>
       <c r="H46" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B46, prodcom_data[product], 0))</f>
-        <v>0.84223339185782964</v>
+        <v>0.80917344833809868</v>
       </c>
       <c r="I46" s="49" t="s">
-        <v>2690</v>
+        <v>2686</v>
       </c>
       <c r="J46" s="49" t="s">
-        <v>2642</v>
+        <v>2687</v>
       </c>
       <c r="K46" s="79" t="s">
-        <v>2966</v>
+        <v>2971</v>
       </c>
       <c r="L46" s="79">
-        <v>114.14</v>
+        <v>60.1</v>
       </c>
       <c r="M46" s="80" t="s">
-        <v>2908</v>
+        <v>2892</v>
       </c>
       <c r="N46" s="72">
         <f>M46*Calculations!$C$37/L46</f>
-        <v>0.63138251270369727</v>
+        <v>0.59955074875207992</v>
       </c>
       <c r="O46" s="81" t="s">
-        <v>2967</v>
+        <v>2972</v>
       </c>
       <c r="P46" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q46" s="58">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="R46" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S46" s="61" cm="1">
         <f t="array" ref="S46">1-SUM(IF(ISNUMBER(P46:Q46), P46:Q46, 0))</f>
-        <v>0.13</v>
+        <v>0.18000000000000005</v>
       </c>
       <c r="T46" s="59"/>
       <c r="U46" s="63"/>
@@ -43609,14 +43422,14 @@
         <v>3036</v>
       </c>
       <c r="W46" s="58">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="X46" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y46" s="61" cm="1">
         <f t="array" ref="Y46">1-SUM(IF(ISNUMBER(V46:W46), V46:W46, 0))</f>
-        <v>0.13</v>
+        <v>0.18000000000000005</v>
       </c>
       <c r="Z46" s="59"/>
       <c r="AA46" s="60"/>
@@ -43627,56 +43440,56 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A47" s="64">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B47" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>2849</v>
+        <v>2846</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>2986</v>
+        <v>53</v>
       </c>
       <c r="F47" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B47, prodcom_data[product], 0))</f>
-        <v>507331541</v>
+        <v>642497260</v>
       </c>
       <c r="G47" s="54">
         <f t="shared" si="0"/>
-        <v>0.507331541</v>
+        <v>0.64249725999999996</v>
       </c>
       <c r="H47" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B47, prodcom_data[product], 0))</f>
-        <v>0.78843905350643284</v>
+        <v>0.93385612259264728</v>
       </c>
       <c r="I47" s="49" t="s">
-        <v>2691</v>
+        <v>2688</v>
       </c>
       <c r="J47" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K47" s="79" t="s">
-        <v>2987</v>
+        <v>2980</v>
       </c>
       <c r="L47" s="79">
-        <v>74.12</v>
+        <v>106.16</v>
       </c>
       <c r="M47" s="80" t="s">
-        <v>2925</v>
+        <v>2915</v>
       </c>
       <c r="N47" s="72">
         <f>M47*Calculations!$C$37/L47</f>
-        <v>0.64819212088505118</v>
+        <v>0.90512434061793512</v>
       </c>
       <c r="O47" s="81" t="s">
-        <v>2988</v>
+        <v>2982</v>
       </c>
       <c r="P47" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q47" s="58">
         <v>1</v>
@@ -43686,7 +43499,7 @@
       <c r="T47" s="59"/>
       <c r="U47" s="63"/>
       <c r="V47" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W47" s="58">
         <v>1</v>
@@ -43702,66 +43515,66 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A48" s="64">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>2850</v>
+        <v>2847</v>
       </c>
       <c r="D48" t="s">
-        <v>285</v>
+        <v>221</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>2989</v>
+        <v>221</v>
       </c>
       <c r="F48" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B48, prodcom_data[product], 0))</f>
-        <v>443739559</v>
+        <v>604861873</v>
       </c>
       <c r="G48" s="54">
         <f t="shared" si="0"/>
-        <v>0.44373955900000001</v>
+        <v>0.60486187300000005</v>
       </c>
       <c r="H48" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B48, prodcom_data[product], 0))</f>
-        <v>0.9014296604554024</v>
+        <v>0.66130800742337414</v>
       </c>
       <c r="I48" s="49" t="s">
-        <v>2692</v>
+        <v>2652</v>
       </c>
       <c r="J48" s="49" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="K48" s="79" t="s">
-        <v>2990</v>
+        <v>2968</v>
       </c>
       <c r="L48" s="79">
-        <v>116.2</v>
+        <v>128.16900000000001</v>
       </c>
       <c r="M48" s="80" t="s">
-        <v>2908</v>
+        <v>2947</v>
       </c>
       <c r="N48" s="72">
         <f>M48*Calculations!$C$37/L48</f>
-        <v>0.6201893287435456</v>
+        <v>0.6559854567016985</v>
       </c>
       <c r="O48" s="81" t="s">
-        <v>2991</v>
+        <v>2969</v>
       </c>
       <c r="P48" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q48" s="58">
-        <v>0.91</v>
+        <v>0.72</v>
       </c>
       <c r="R48" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S48" s="61" cm="1">
         <f t="array" ref="S48">1-SUM(IF(ISNUMBER(P48:Q48), P48:Q48, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="T48" s="59"/>
       <c r="U48" s="63"/>
@@ -43769,14 +43582,14 @@
         <v>3036</v>
       </c>
       <c r="W48" s="58">
-        <v>0.91</v>
+        <v>0.72</v>
       </c>
       <c r="X48" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y48" s="61" cm="1">
         <f t="array" ref="Y48">1-SUM(IF(ISNUMBER(V48:W48), V48:W48, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Z48" s="59"/>
       <c r="AA48" s="60"/>
@@ -43787,72 +43600,82 @@
     </row>
     <row r="49" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A49" s="64">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>186</v>
+        <v>542</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>2851</v>
+        <v>2848</v>
       </c>
       <c r="D49" t="s">
-        <v>187</v>
+        <v>543</v>
       </c>
       <c r="E49" s="48" t="s">
-        <v>187</v>
+        <v>2965</v>
       </c>
       <c r="F49" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B49, prodcom_data[product], 0))</f>
-        <v>377601386</v>
+        <v>593659673</v>
       </c>
       <c r="G49" s="54">
         <f t="shared" si="0"/>
-        <v>0.37760138599999998</v>
+        <v>0.593659673</v>
       </c>
       <c r="H49" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B49, prodcom_data[product], 0))</f>
-        <v>0.11917329138193365</v>
+        <v>0.84223339185782964</v>
       </c>
       <c r="I49" s="49" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="J49" s="49" t="s">
         <v>2642</v>
       </c>
       <c r="K49" s="79" t="s">
-        <v>3004</v>
+        <v>2966</v>
       </c>
       <c r="L49" s="79">
-        <v>88.11</v>
+        <v>114.14</v>
       </c>
       <c r="M49" s="80" t="s">
-        <v>2925</v>
+        <v>2908</v>
       </c>
       <c r="N49" s="72">
         <f>M49*Calculations!$C$37/L49</f>
-        <v>0.54527295426171829</v>
+        <v>0.63138251270369727</v>
       </c>
       <c r="O49" s="81" t="s">
-        <v>3005</v>
+        <v>2967</v>
       </c>
       <c r="P49" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="Q49" s="58">
-        <v>1</v>
-      </c>
-      <c r="R49" s="59"/>
-      <c r="S49" s="60"/>
+        <v>0.87</v>
+      </c>
+      <c r="R49" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S49" s="61" cm="1">
+        <f t="array" ref="S49">1-SUM(IF(ISNUMBER(P49:Q49), P49:Q49, 0))</f>
+        <v>0.13</v>
+      </c>
       <c r="T49" s="59"/>
       <c r="U49" s="63"/>
       <c r="V49" s="59" t="s">
-        <v>3042</v>
+        <v>3036</v>
       </c>
       <c r="W49" s="58">
-        <v>1</v>
-      </c>
-      <c r="X49" s="59"/>
-      <c r="Y49" s="60"/>
+        <v>0.87</v>
+      </c>
+      <c r="X49" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y49" s="61" cm="1">
+        <f t="array" ref="Y49">1-SUM(IF(ISNUMBER(V49:W49), V49:W49, 0))</f>
+        <v>0.13</v>
+      </c>
       <c r="Z49" s="59"/>
       <c r="AA49" s="60"/>
       <c r="AB49" s="59"/>
@@ -43862,62 +43685,70 @@
     </row>
     <row r="50" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A50" s="64">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B50" t="s">
-        <v>581</v>
+        <v>117</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>2852</v>
+        <v>2849</v>
       </c>
       <c r="D50" t="s">
-        <v>582</v>
+        <v>118</v>
       </c>
       <c r="E50" s="48" t="s">
-        <v>3000</v>
+        <v>2986</v>
       </c>
       <c r="F50" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B50, prodcom_data[product], 0))</f>
-        <v>334412816</v>
+        <v>507331541</v>
       </c>
       <c r="G50" s="54">
         <f t="shared" si="0"/>
-        <v>0.334412816</v>
+        <v>0.507331541</v>
       </c>
       <c r="H50" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B50, prodcom_data[product], 0))</f>
-        <v>0.59226283959165005</v>
-      </c>
-      <c r="I50" s="51" t="s">
-        <v>3001</v>
+        <v>0.78843905350643284</v>
+      </c>
+      <c r="I50" s="49" t="s">
+        <v>2691</v>
       </c>
       <c r="J50" s="49" t="s">
-        <v>2695</v>
+        <v>2642</v>
       </c>
       <c r="K50" s="79" t="s">
-        <v>3002</v>
+        <v>2987</v>
       </c>
       <c r="L50" s="79">
-        <v>30.026</v>
+        <v>74.12</v>
       </c>
       <c r="M50" s="80" t="s">
-        <v>2905</v>
+        <v>2925</v>
       </c>
       <c r="N50" s="72">
         <f>M50*Calculations!$C$37/L50</f>
-        <v>0.40001998268167588</v>
+        <v>0.64819212088505118</v>
       </c>
       <c r="O50" s="81" t="s">
-        <v>3003</v>
-      </c>
-      <c r="P50" s="59"/>
-      <c r="Q50" s="60"/>
+        <v>2988</v>
+      </c>
+      <c r="P50" s="59" t="s">
+        <v>3042</v>
+      </c>
+      <c r="Q50" s="58">
+        <v>1</v>
+      </c>
       <c r="R50" s="59"/>
       <c r="S50" s="60"/>
       <c r="T50" s="59"/>
       <c r="U50" s="63"/>
-      <c r="V50" s="59"/>
-      <c r="W50" s="60"/>
+      <c r="V50" s="59" t="s">
+        <v>3042</v>
+      </c>
+      <c r="W50" s="58">
+        <v>1</v>
+      </c>
       <c r="X50" s="59"/>
       <c r="Y50" s="60"/>
       <c r="Z50" s="59"/>
@@ -43929,66 +43760,66 @@
     </row>
     <row r="51" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A51" s="64">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B51" t="s">
-        <v>459</v>
+        <v>284</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>2853</v>
+        <v>2850</v>
       </c>
       <c r="D51" t="s">
-        <v>460</v>
+        <v>285</v>
       </c>
       <c r="E51" s="48" t="s">
-        <v>3006</v>
+        <v>2989</v>
       </c>
       <c r="F51" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B51, prodcom_data[product], 0))</f>
-        <v>321846701</v>
+        <v>443739559</v>
       </c>
       <c r="G51" s="54">
         <f t="shared" si="0"/>
-        <v>0.32184670100000001</v>
+        <v>0.44373955900000001</v>
       </c>
       <c r="H51" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B51, prodcom_data[product], 0))</f>
-        <v>0.18642415725740188</v>
+        <v>0.9014296604554024</v>
       </c>
       <c r="I51" s="49" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="J51" s="49" t="s">
-        <v>2642</v>
+        <v>2693</v>
       </c>
       <c r="K51" s="79" t="s">
-        <v>3007</v>
+        <v>2990</v>
       </c>
       <c r="L51" s="79">
-        <v>106.12</v>
+        <v>116.2</v>
       </c>
       <c r="M51" s="80" t="s">
-        <v>2925</v>
+        <v>2908</v>
       </c>
       <c r="N51" s="72">
         <f>M51*Calculations!$C$37/L51</f>
-        <v>0.45273275537127777</v>
+        <v>0.6201893287435456</v>
       </c>
       <c r="O51" s="81" t="s">
-        <v>3008</v>
+        <v>2991</v>
       </c>
       <c r="P51" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q51" s="58">
-        <v>0.21</v>
+        <v>0.91</v>
       </c>
       <c r="R51" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S51" s="61" cm="1">
         <f t="array" ref="S51">1-SUM(IF(ISNUMBER(P51:Q51), P51:Q51, 0))</f>
-        <v>0.79</v>
+        <v>8.9999999999999969E-2</v>
       </c>
       <c r="T51" s="59"/>
       <c r="U51" s="63"/>
@@ -43996,14 +43827,14 @@
         <v>3036</v>
       </c>
       <c r="W51" s="58">
-        <v>0.21</v>
+        <v>0.91</v>
       </c>
       <c r="X51" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y51" s="61" cm="1">
         <f t="array" ref="Y51">1-SUM(IF(ISNUMBER(V51:W51), V51:W51, 0))</f>
-        <v>0.79</v>
+        <v>8.9999999999999969E-2</v>
       </c>
       <c r="Z51" s="59"/>
       <c r="AA51" s="60"/>
@@ -44014,82 +43845,72 @@
     </row>
     <row r="52" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A52" s="64">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>2854</v>
+        <v>2851</v>
       </c>
       <c r="D52" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="E52" s="48" t="s">
-        <v>2994</v>
+        <v>187</v>
       </c>
       <c r="F52" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B52, prodcom_data[product], 0))</f>
-        <v>321638245</v>
+        <v>377601386</v>
       </c>
       <c r="G52" s="54">
         <f t="shared" si="0"/>
-        <v>0.32163824499999999</v>
+        <v>0.37760138599999998</v>
       </c>
       <c r="H52" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B52, prodcom_data[product], 0))</f>
-        <v>0.27981747008972768</v>
+        <v>0.11917329138193365</v>
       </c>
       <c r="I52" s="49" t="s">
-        <v>2697</v>
+        <v>2694</v>
       </c>
       <c r="J52" s="49" t="s">
-        <v>2698</v>
+        <v>2642</v>
       </c>
       <c r="K52" s="79" t="s">
-        <v>2995</v>
+        <v>3004</v>
       </c>
       <c r="L52" s="79">
-        <v>100.12</v>
+        <v>88.11</v>
       </c>
       <c r="M52" s="80" t="s">
-        <v>2996</v>
+        <v>2925</v>
       </c>
       <c r="N52" s="72">
         <f>M52*Calculations!$C$37/L52</f>
-        <v>0.59983020375549334</v>
+        <v>0.54527295426171829</v>
       </c>
       <c r="O52" s="81" t="s">
-        <v>2997</v>
+        <v>3005</v>
       </c>
       <c r="P52" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q52" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="R52" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S52" s="61" cm="1">
-        <f t="array" ref="S52">1-SUM(IF(ISNUMBER(P52:Q52), P52:Q52, 0))</f>
-        <v>0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R52" s="59"/>
+      <c r="S52" s="60"/>
       <c r="T52" s="59"/>
       <c r="U52" s="63"/>
       <c r="V52" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W52" s="58">
-        <v>0.35</v>
-      </c>
-      <c r="X52" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y52" s="61" cm="1">
-        <f t="array" ref="Y52">1-SUM(IF(ISNUMBER(V52:W52), V52:W52, 0))</f>
-        <v>0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X52" s="59"/>
+      <c r="Y52" s="60"/>
       <c r="Z52" s="59"/>
       <c r="AA52" s="60"/>
       <c r="AB52" s="59"/>
@@ -44099,82 +43920,64 @@
     </row>
     <row r="53" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A53" s="64">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>581</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>2855</v>
+        <v>2852</v>
       </c>
       <c r="D53" t="s">
-        <v>41</v>
+        <v>582</v>
       </c>
       <c r="E53" s="48" t="s">
-        <v>41</v>
+        <v>3000</v>
       </c>
       <c r="F53" s="56">
         <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B53, prodcom_data[product], 0))</f>
-        <v>318208407</v>
+        <v>334412816</v>
       </c>
       <c r="G53" s="54">
         <f t="shared" si="0"/>
-        <v>0.31820840700000003</v>
+        <v>0.334412816</v>
       </c>
       <c r="H53" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B53, prodcom_data[product], 0))</f>
-        <v>0.44804616680036363</v>
-      </c>
-      <c r="I53" s="49" t="s">
-        <v>2699</v>
+        <v>0.59226283959165005</v>
+      </c>
+      <c r="I53" s="51" t="s">
+        <v>3001</v>
       </c>
       <c r="J53" s="49" t="s">
-        <v>2642</v>
+        <v>2695</v>
       </c>
       <c r="K53" s="79" t="s">
-        <v>2980</v>
+        <v>3002</v>
       </c>
       <c r="L53" s="79">
-        <v>106.16</v>
+        <v>30.026</v>
       </c>
       <c r="M53" s="80" t="s">
-        <v>2915</v>
+        <v>2905</v>
       </c>
       <c r="N53" s="72">
         <f>M53*Calculations!$C$37/L53</f>
-        <v>0.90512434061793512</v>
+        <v>0.40001998268167588</v>
       </c>
       <c r="O53" s="81" t="s">
-        <v>3009</v>
-      </c>
-      <c r="P53" s="59" t="s">
-        <v>3036</v>
-      </c>
-      <c r="Q53" s="58">
-        <v>0.51</v>
-      </c>
-      <c r="R53" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S53" s="61" cm="1">
-        <f t="array" ref="S53">1-SUM(IF(ISNUMBER(P53:Q53), P53:Q53, 0))</f>
-        <v>0.49</v>
-      </c>
+        <v>3003</v>
+      </c>
+      <c r="P53" s="59"/>
+      <c r="Q53" s="60"/>
+      <c r="R53" s="59"/>
+      <c r="S53" s="60"/>
       <c r="T53" s="59"/>
       <c r="U53" s="63"/>
-      <c r="V53" s="59" t="s">
-        <v>3036</v>
-      </c>
-      <c r="W53" s="58">
-        <v>0.51</v>
-      </c>
-      <c r="X53" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y53" s="61" cm="1">
-        <f t="array" ref="Y53">1-SUM(IF(ISNUMBER(V53:W53), V53:W53, 0))</f>
-        <v>0.49</v>
-      </c>
+      <c r="V53" s="59"/>
+      <c r="W53" s="60"/>
+      <c r="X53" s="59"/>
+      <c r="Y53" s="60"/>
       <c r="Z53" s="59"/>
       <c r="AA53" s="60"/>
       <c r="AB53" s="59"/>
@@ -44184,66 +43987,66 @@
     </row>
     <row r="54" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A54" s="64">
-        <v>48</v>
-      </c>
-      <c r="B54" s="65" t="s">
-        <v>345</v>
+        <v>45</v>
+      </c>
+      <c r="B54" t="s">
+        <v>459</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>2829</v>
-      </c>
-      <c r="D54" s="52" t="s">
-        <v>3010</v>
+        <v>2853</v>
+      </c>
+      <c r="D54" t="s">
+        <v>460</v>
       </c>
       <c r="E54" s="48" t="s">
-        <v>3011</v>
+        <v>3006</v>
       </c>
       <c r="F54" s="56">
-        <f>Calculations!C32*(Calculations!C29/SUM(Calculations!$C$28:$C$29))</f>
-        <v>242141968.15384617</v>
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B54, prodcom_data[product], 0))</f>
+        <v>321846701</v>
       </c>
       <c r="G54" s="54">
         <f t="shared" si="0"/>
-        <v>0.24214196815384617</v>
+        <v>0.32184670100000001</v>
       </c>
       <c r="H54" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B54, prodcom_data[product], 0))</f>
-        <v>0.88632047658515611</v>
-      </c>
-      <c r="I54" s="48" t="s">
-        <v>3012</v>
+        <v>0.18642415725740188</v>
+      </c>
+      <c r="I54" s="49" t="s">
+        <v>2696</v>
       </c>
       <c r="J54" s="49" t="s">
-        <v>2671</v>
+        <v>2642</v>
       </c>
       <c r="K54" s="79" t="s">
-        <v>3013</v>
+        <v>3007</v>
       </c>
       <c r="L54" s="79">
-        <v>174.16</v>
+        <v>106.12</v>
       </c>
       <c r="M54" s="80" t="s">
-        <v>2974</v>
+        <v>2925</v>
       </c>
       <c r="N54" s="72">
         <f>M54*Calculations!$C$37/L54</f>
-        <v>0.6206878732200275</v>
+        <v>0.45273275537127777</v>
       </c>
       <c r="O54" s="81" t="s">
-        <v>3014</v>
+        <v>3008</v>
       </c>
       <c r="P54" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q54" s="58">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="R54" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S54" s="61" cm="1">
         <f t="array" ref="S54">1-SUM(IF(ISNUMBER(P54:Q54), P54:Q54, 0))</f>
-        <v>0.12</v>
+        <v>0.79</v>
       </c>
       <c r="T54" s="59"/>
       <c r="U54" s="63"/>
@@ -44251,14 +44054,14 @@
         <v>3036</v>
       </c>
       <c r="W54" s="58">
-        <v>0.88</v>
+        <v>0.21</v>
       </c>
       <c r="X54" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y54" s="61" cm="1">
         <f t="array" ref="Y54">1-SUM(IF(ISNUMBER(V54:W54), V54:W54, 0))</f>
-        <v>0.12</v>
+        <v>0.79</v>
       </c>
       <c r="Z54" s="59"/>
       <c r="AA54" s="60"/>
@@ -44269,66 +44072,66 @@
     </row>
     <row r="55" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A55" s="64">
-        <v>49</v>
-      </c>
-      <c r="B55" s="65" t="s">
-        <v>345</v>
+        <v>46</v>
+      </c>
+      <c r="B55" t="s">
+        <v>226</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>2829</v>
-      </c>
-      <c r="D55" s="52" t="s">
-        <v>3015</v>
+        <v>2854</v>
+      </c>
+      <c r="D55" t="s">
+        <v>227</v>
       </c>
       <c r="E55" s="48" t="s">
-        <v>3016</v>
+        <v>2994</v>
       </c>
       <c r="F55" s="56">
-        <f>Calculations!C32*(Calculations!C28/SUM(Calculations!$C$28:$C$29))</f>
-        <v>807139893.84615386</v>
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B55, prodcom_data[product], 0))</f>
+        <v>321638245</v>
       </c>
       <c r="G55" s="54">
         <f t="shared" si="0"/>
-        <v>0.80713989384615381</v>
+        <v>0.32163824499999999</v>
       </c>
       <c r="H55" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B55, prodcom_data[product], 0))</f>
-        <v>0.88632047658515611</v>
-      </c>
-      <c r="I55" s="48" t="s">
-        <v>3017</v>
+        <v>0.27981747008972768</v>
+      </c>
+      <c r="I55" s="49" t="s">
+        <v>2697</v>
       </c>
       <c r="J55" s="49" t="s">
-        <v>2671</v>
+        <v>2698</v>
       </c>
       <c r="K55" s="79" t="s">
-        <v>3018</v>
+        <v>2995</v>
       </c>
       <c r="L55" s="79">
-        <v>250.25</v>
+        <v>100.12</v>
       </c>
       <c r="M55" s="80" t="s">
-        <v>2959</v>
+        <v>2996</v>
       </c>
       <c r="N55" s="72">
         <f>M55*Calculations!$C$37/L55</f>
-        <v>0.71994005994005994</v>
+        <v>0.59983020375549334</v>
       </c>
       <c r="O55" s="81" t="s">
-        <v>3019</v>
+        <v>2997</v>
       </c>
       <c r="P55" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q55" s="58">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="R55" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S55" s="61" cm="1">
         <f t="array" ref="S55">1-SUM(IF(ISNUMBER(P55:Q55), P55:Q55, 0))</f>
-        <v>0.12</v>
+        <v>0.65</v>
       </c>
       <c r="T55" s="59"/>
       <c r="U55" s="63"/>
@@ -44336,14 +44139,14 @@
         <v>3036</v>
       </c>
       <c r="W55" s="58">
-        <v>0.88</v>
+        <v>0.35</v>
       </c>
       <c r="X55" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y55" s="61" cm="1">
         <f t="array" ref="Y55">1-SUM(IF(ISNUMBER(V55:W55), V55:W55, 0))</f>
-        <v>0.12</v>
+        <v>0.65</v>
       </c>
       <c r="Z55" s="59"/>
       <c r="AA55" s="60"/>
@@ -44354,66 +44157,66 @@
     </row>
     <row r="56" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A56" s="64">
-        <v>50</v>
-      </c>
-      <c r="B56" s="65" t="s">
-        <v>634</v>
+        <v>47</v>
+      </c>
+      <c r="B56" t="s">
+        <v>40</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>2819</v>
-      </c>
-      <c r="D56" s="52" t="s">
-        <v>3020</v>
+        <v>2855</v>
+      </c>
+      <c r="D56" t="s">
+        <v>41</v>
       </c>
       <c r="E56" s="48" t="s">
-        <v>3021</v>
+        <v>41</v>
       </c>
       <c r="F56" s="56">
-        <f>Calculations!C6*(Calculations!C24/(Calculations!C15+Calculations!C24))</f>
-        <v>1089108418.3783784</v>
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B56, prodcom_data[product], 0))</f>
+        <v>318208407</v>
       </c>
       <c r="G56" s="54">
         <f t="shared" si="0"/>
-        <v>1.0891084183783784</v>
+        <v>0.31820840700000003</v>
       </c>
       <c r="H56" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B56, prodcom_data[product], 0))</f>
-        <v>0.87748442629671652</v>
-      </c>
-      <c r="I56" s="48" t="s">
-        <v>3022</v>
+        <v>0.44804616680036363</v>
+      </c>
+      <c r="I56" s="49" t="s">
+        <v>2699</v>
       </c>
       <c r="J56" s="49" t="s">
-        <v>2661</v>
+        <v>2642</v>
       </c>
       <c r="K56" s="79" t="s">
-        <v>3023</v>
+        <v>2980</v>
       </c>
       <c r="L56" s="79">
-        <v>224.3</v>
+        <v>106.16</v>
       </c>
       <c r="M56" s="80" t="s">
-        <v>2919</v>
+        <v>2915</v>
       </c>
       <c r="N56" s="72">
         <f>M56*Calculations!$C$37/L56</f>
-        <v>0.64258582255907271</v>
+        <v>0.90512434061793512</v>
       </c>
       <c r="O56" s="81" t="s">
-        <v>3024</v>
+        <v>3009</v>
       </c>
       <c r="P56" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q56" s="58">
-        <v>0.91</v>
+        <v>0.51</v>
       </c>
       <c r="R56" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S56" s="61" cm="1">
         <f t="array" ref="S56">1-SUM(IF(ISNUMBER(P56:Q56), P56:Q56, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.49</v>
       </c>
       <c r="T56" s="59"/>
       <c r="U56" s="63"/>
@@ -44421,14 +44224,14 @@
         <v>3036</v>
       </c>
       <c r="W56" s="58">
-        <v>0.91</v>
+        <v>0.51</v>
       </c>
       <c r="X56" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y56" s="61" cm="1">
         <f t="array" ref="Y56">1-SUM(IF(ISNUMBER(V56:W56), V56:W56, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.49</v>
       </c>
       <c r="Z56" s="59"/>
       <c r="AA56" s="60"/>
@@ -44439,66 +44242,66 @@
     </row>
     <row r="57" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A57" s="64">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B57" s="65" t="s">
-        <v>634</v>
+        <v>345</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>2819</v>
+        <v>2829</v>
       </c>
       <c r="D57" s="52" t="s">
-        <v>3025</v>
+        <v>3010</v>
       </c>
       <c r="E57" s="48" t="s">
-        <v>3026</v>
+        <v>3011</v>
       </c>
       <c r="F57" s="56">
-        <f>Calculations!C6*(Calculations!C15/(Calculations!C15+Calculations!C24))</f>
-        <v>1281304021.6216214</v>
+        <f>Calculations!C32*(Calculations!C29/SUM(Calculations!$C$28:$C$29))</f>
+        <v>242141968.15384617</v>
       </c>
       <c r="G57" s="54">
         <f t="shared" si="0"/>
-        <v>1.2813040216216214</v>
+        <v>0.24214196815384617</v>
       </c>
       <c r="H57" s="61">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B57, prodcom_data[product], 0))</f>
-        <v>0.87748442629671652</v>
+        <v>0.88632047658515611</v>
       </c>
       <c r="I57" s="48" t="s">
-        <v>3027</v>
+        <v>3012</v>
       </c>
       <c r="J57" s="49" t="s">
-        <v>2661</v>
+        <v>2671</v>
       </c>
       <c r="K57" s="79" t="s">
-        <v>3028</v>
+        <v>3013</v>
       </c>
       <c r="L57" s="79">
-        <v>582.79999999999995</v>
+        <v>174.16</v>
       </c>
       <c r="M57" s="80" t="s">
-        <v>3029</v>
+        <v>2974</v>
       </c>
       <c r="N57" s="72">
         <f>M57*Calculations!$C$37/L57</f>
-        <v>0.61827385037748805</v>
+        <v>0.6206878732200275</v>
       </c>
       <c r="O57" s="81" t="s">
-        <v>3030</v>
+        <v>3014</v>
       </c>
       <c r="P57" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q57" s="58">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="R57" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S57" s="61" cm="1">
         <f t="array" ref="S57">1-SUM(IF(ISNUMBER(P57:Q57), P57:Q57, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.12</v>
       </c>
       <c r="T57" s="59"/>
       <c r="U57" s="63"/>
@@ -44506,14 +44309,14 @@
         <v>3036</v>
       </c>
       <c r="W57" s="58">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="X57" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y57" s="61" cm="1">
         <f t="array" ref="Y57">1-SUM(IF(ISNUMBER(V57:W57), V57:W57, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.12</v>
       </c>
       <c r="Z57" s="59"/>
       <c r="AA57" s="60"/>
@@ -44522,14 +44325,269 @@
       <c r="AD57" s="59"/>
       <c r="AE57" s="60"/>
     </row>
-    <row r="107" spans="32:32" x14ac:dyDescent="0.3">
-      <c r="AF107" t="s">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A58" s="64">
+        <v>49</v>
+      </c>
+      <c r="B58" s="65" t="s">
+        <v>345</v>
+      </c>
+      <c r="C58" s="64" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D58" s="52" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E58" s="48" t="s">
+        <v>3016</v>
+      </c>
+      <c r="F58" s="56">
+        <f>Calculations!C32*(Calculations!C28/SUM(Calculations!$C$28:$C$29))</f>
+        <v>807139893.84615386</v>
+      </c>
+      <c r="G58" s="54">
+        <f t="shared" si="0"/>
+        <v>0.80713989384615381</v>
+      </c>
+      <c r="H58" s="61">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B58, prodcom_data[product], 0))</f>
+        <v>0.88632047658515611</v>
+      </c>
+      <c r="I58" s="48" t="s">
+        <v>3017</v>
+      </c>
+      <c r="J58" s="49" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K58" s="79" t="s">
+        <v>3018</v>
+      </c>
+      <c r="L58" s="79">
+        <v>250.25</v>
+      </c>
+      <c r="M58" s="80" t="s">
+        <v>2959</v>
+      </c>
+      <c r="N58" s="72">
+        <f>M58*Calculations!$C$37/L58</f>
+        <v>0.71994005994005994</v>
+      </c>
+      <c r="O58" s="81" t="s">
+        <v>3019</v>
+      </c>
+      <c r="P58" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Q58" s="58">
+        <v>0.88</v>
+      </c>
+      <c r="R58" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S58" s="61" cm="1">
+        <f t="array" ref="S58">1-SUM(IF(ISNUMBER(P58:Q58), P58:Q58, 0))</f>
+        <v>0.12</v>
+      </c>
+      <c r="T58" s="59"/>
+      <c r="U58" s="63"/>
+      <c r="V58" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="W58" s="58">
+        <v>0.88</v>
+      </c>
+      <c r="X58" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y58" s="61" cm="1">
+        <f t="array" ref="Y58">1-SUM(IF(ISNUMBER(V58:W58), V58:W58, 0))</f>
+        <v>0.12</v>
+      </c>
+      <c r="Z58" s="59"/>
+      <c r="AA58" s="60"/>
+      <c r="AB58" s="59"/>
+      <c r="AC58" s="60"/>
+      <c r="AD58" s="59"/>
+      <c r="AE58" s="60"/>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A59" s="64">
+        <v>50</v>
+      </c>
+      <c r="B59" s="65" t="s">
+        <v>634</v>
+      </c>
+      <c r="C59" s="64" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D59" s="52" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E59" s="48" t="s">
+        <v>3021</v>
+      </c>
+      <c r="F59" s="56">
+        <f>Calculations!C6*(Calculations!C24/(Calculations!C15+Calculations!C24))</f>
+        <v>1089108418.3783784</v>
+      </c>
+      <c r="G59" s="54">
+        <f t="shared" si="0"/>
+        <v>1.0891084183783784</v>
+      </c>
+      <c r="H59" s="61">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B59, prodcom_data[product], 0))</f>
+        <v>0.87748442629671652</v>
+      </c>
+      <c r="I59" s="48" t="s">
+        <v>3022</v>
+      </c>
+      <c r="J59" s="49" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K59" s="79" t="s">
+        <v>3023</v>
+      </c>
+      <c r="L59" s="79">
+        <v>224.3</v>
+      </c>
+      <c r="M59" s="80" t="s">
+        <v>2919</v>
+      </c>
+      <c r="N59" s="72">
+        <f>M59*Calculations!$C$37/L59</f>
+        <v>0.64258582255907271</v>
+      </c>
+      <c r="O59" s="81" t="s">
+        <v>3024</v>
+      </c>
+      <c r="P59" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Q59" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="R59" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S59" s="61" cm="1">
+        <f t="array" ref="S59">1-SUM(IF(ISNUMBER(P59:Q59), P59:Q59, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="T59" s="59"/>
+      <c r="U59" s="63"/>
+      <c r="V59" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="W59" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="X59" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y59" s="61" cm="1">
+        <f t="array" ref="Y59">1-SUM(IF(ISNUMBER(V59:W59), V59:W59, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="Z59" s="59"/>
+      <c r="AA59" s="60"/>
+      <c r="AB59" s="59"/>
+      <c r="AC59" s="60"/>
+      <c r="AD59" s="59"/>
+      <c r="AE59" s="60"/>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A60" s="64">
+        <v>51</v>
+      </c>
+      <c r="B60" s="65" t="s">
+        <v>634</v>
+      </c>
+      <c r="C60" s="64" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D60" s="52" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E60" s="48" t="s">
+        <v>3026</v>
+      </c>
+      <c r="F60" s="56">
+        <f>Calculations!C6*(Calculations!C15/(Calculations!C15+Calculations!C24))</f>
+        <v>1281304021.6216214</v>
+      </c>
+      <c r="G60" s="54">
+        <f t="shared" si="0"/>
+        <v>1.2813040216216214</v>
+      </c>
+      <c r="H60" s="61">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B60, prodcom_data[product], 0))</f>
+        <v>0.87748442629671652</v>
+      </c>
+      <c r="I60" s="48" t="s">
+        <v>3027</v>
+      </c>
+      <c r="J60" s="49" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K60" s="79" t="s">
+        <v>3028</v>
+      </c>
+      <c r="L60" s="79">
+        <v>582.79999999999995</v>
+      </c>
+      <c r="M60" s="80" t="s">
+        <v>3029</v>
+      </c>
+      <c r="N60" s="72">
+        <f>M60*Calculations!$C$37/L60</f>
+        <v>0.61827385037748805</v>
+      </c>
+      <c r="O60" s="81" t="s">
+        <v>3030</v>
+      </c>
+      <c r="P60" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Q60" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="R60" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S60" s="61" cm="1">
+        <f t="array" ref="S60">1-SUM(IF(ISNUMBER(P60:Q60), P60:Q60, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="T60" s="59"/>
+      <c r="U60" s="63"/>
+      <c r="V60" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="W60" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="X60" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y60" s="61" cm="1">
+        <f t="array" ref="Y60">1-SUM(IF(ISNUMBER(V60:W60), V60:W60, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="Z60" s="59"/>
+      <c r="AA60" s="60"/>
+      <c r="AB60" s="59"/>
+      <c r="AC60" s="60"/>
+      <c r="AD60" s="59"/>
+      <c r="AE60" s="60"/>
+    </row>
+    <row r="110" spans="32:32" x14ac:dyDescent="0.3">
+      <c r="AF110" t="s">
         <v>2658</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="F7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Article_data/Step 3 results from Prodcom data manipulations.xlsx
+++ b/Article_data/Step 3 results from Prodcom data manipulations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7DEA16-BD02-4A91-99C1-B4D79E905914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A660D838-64B7-4AB0-934B-596014D9CB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-28935" yWindow="-45" windowWidth="29070" windowHeight="15750" tabRatio="570" activeTab="3" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,54 @@
     <author>Nicolas Lienart</author>
   </authors>
   <commentList>
+    <comment ref="X9" authorId="0" shapeId="0" xr:uid="{4DDA655F-A03F-4A8A-9FBE-8E0ECEC195C2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nicolas Lienart:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Saudi Arabia and South Korea</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X15" authorId="0" shapeId="0" xr:uid="{59700EF9-EB1E-4FC4-A0CF-E1B9A01EFC14}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Nicolas Lienart:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+United States + Mexico</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="I53" authorId="0" shapeId="0" xr:uid="{ECD7D4FD-83B1-417F-8548-0E059BE763C1}">
       <text>
         <r>
@@ -108,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7453" uniqueCount="3081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7537" uniqueCount="3100">
   <si>
     <t>freq</t>
   </si>
@@ -9351,6 +9399,63 @@
   </si>
   <si>
     <t>Update Hotspot product export sheet description</t>
+  </si>
+  <si>
+    <t>Chloromethane</t>
+  </si>
+  <si>
+    <t>Butanal</t>
+  </si>
+  <si>
+    <t>Bisphenol A</t>
+  </si>
+  <si>
+    <t>market for bisphenol A, powder</t>
+  </si>
+  <si>
+    <t>market for acetic anhydride</t>
+  </si>
+  <si>
+    <t>market for methyl chloride</t>
+  </si>
+  <si>
+    <t>"Methane, chloro-" (chloromethane) 450 kt &lt; US production (2019) &lt; 453,592 kt; "Ethane, chloro-" (chloroethane) 9 kt &lt; US production (2019) &lt; 45 kt (US EPA, 2022)</t>
+  </si>
+  <si>
+    <t>CH3Cl</t>
+  </si>
+  <si>
+    <t>Source : 15-08-2026 - https://pubchem.ncbi.nlm.nih.gov/compound/6327</t>
+  </si>
+  <si>
+    <t>C4H6O3</t>
+  </si>
+  <si>
+    <t>Source : 26-03-2026 - https://pubchem.ncbi.nlm.nih.gov/compound/7918</t>
+  </si>
+  <si>
+    <t>C15H16O2</t>
+  </si>
+  <si>
+    <t>Source : 26-03-2026 - https://pubchem.ncbi.nlm.nih.gov/compound/6623</t>
+  </si>
+  <si>
+    <t>C4H8O</t>
+  </si>
+  <si>
+    <t>Source : 26-03-2026 - https://pubchem.ncbi.nlm.nih.gov/compound/261</t>
+  </si>
+  <si>
+    <t>Asia without China</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>RNA</t>
+  </si>
+  <si>
+    <t>CN</t>
   </si>
 </sst>
 </file>
@@ -9360,7 +9465,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9505,6 +9610,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -9719,7 +9837,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="9" applyBorder="1" applyAlignment="1">
@@ -9905,9 +10023,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9922,6 +10037,15 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -40298,7 +40422,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A13AB6A-DCA0-44FC-B906-F1FE7AA47CE2}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.5546875" customWidth="1"/>
@@ -40334,7 +40458,7 @@
     </row>
     <row r="3" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="93" t="s">
         <v>3075</v>
       </c>
       <c r="B4" s="50" t="s">
@@ -40342,7 +40466,7 @@
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A5" s="95" t="s">
+      <c r="A5" s="94" t="s">
         <v>3070</v>
       </c>
       <c r="B5" t="s">
@@ -40350,7 +40474,7 @@
       </c>
     </row>
     <row r="6" spans="1:31" s="50" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="95" t="s">
         <v>3078</v>
       </c>
       <c r="B6" s="50" t="s">
@@ -40358,23 +40482,23 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="F7" s="91" t="s">
+      <c r="F7" s="96" t="s">
         <v>705</v>
       </c>
-      <c r="G7" s="91"/>
+      <c r="G7" s="96"/>
       <c r="I7" s="47" t="s">
         <v>3074</v>
       </c>
       <c r="J7" s="47"/>
     </row>
     <row r="8" spans="1:31" s="15" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="91" t="s">
         <v>3055</v>
       </c>
-      <c r="B8" s="93" t="s">
+      <c r="B8" s="92" t="s">
         <v>2882</v>
       </c>
-      <c r="C8" s="92" t="s">
+      <c r="C8" s="91" t="s">
         <v>2808</v>
       </c>
       <c r="D8" s="57" t="s">
@@ -40389,10 +40513,10 @@
       <c r="G8" s="57" t="s">
         <v>3033</v>
       </c>
-      <c r="H8" s="92" t="s">
+      <c r="H8" s="91" t="s">
         <v>3056</v>
       </c>
-      <c r="I8" s="92" t="s">
+      <c r="I8" s="91" t="s">
         <v>3069</v>
       </c>
       <c r="J8" s="57" t="s">
@@ -40464,7 +40588,7 @@
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" s="64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
         <v>614</v>
@@ -40486,7 +40610,7 @@
         <f>F9/1000000000</f>
         <v>11.059816493</v>
       </c>
-      <c r="H9" s="61">
+      <c r="H9" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B9, prodcom_data[product], 0))</f>
         <v>0.86402104863567564</v>
       </c>
@@ -40526,12 +40650,22 @@
         <v>3036</v>
       </c>
       <c r="W9" s="58">
-        <v>1</v>
-      </c>
-      <c r="X9" s="59"/>
-      <c r="Y9" s="60"/>
-      <c r="Z9" s="59"/>
-      <c r="AA9" s="60"/>
+        <v>0.89</v>
+      </c>
+      <c r="X9" s="59" t="s">
+        <v>3096</v>
+      </c>
+      <c r="Y9" s="61">
+        <f>0.05+0.01</f>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="Z9" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AA9" s="61" cm="1">
+        <f t="array" ref="AA9">1-SUM(IF(ISNUMBER(V9:Y9), V9:Y9, 0))</f>
+        <v>4.9999999999999933E-2</v>
+      </c>
       <c r="AB9" s="59"/>
       <c r="AC9" s="60"/>
       <c r="AD9" s="59"/>
@@ -40539,7 +40673,7 @@
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" s="64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>8</v>
@@ -40558,10 +40692,10 @@
         <v>10337493766</v>
       </c>
       <c r="G10" s="54">
-        <f t="shared" ref="G10:G60" si="0">F10/1000000000</f>
+        <f t="shared" ref="G10:G65" si="0">F10/1000000000</f>
         <v>10.337493766</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B10, prodcom_data[product], 0))</f>
         <v>0.87904863332422545</v>
       </c>
@@ -40591,30 +40725,47 @@
         <v>3036</v>
       </c>
       <c r="Q10" s="58">
-        <v>1</v>
-      </c>
-      <c r="R10" s="59"/>
-      <c r="S10" s="60"/>
+        <v>0.96</v>
+      </c>
+      <c r="R10" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S10" s="61" cm="1">
+        <f t="array" ref="S10">1-SUM(IF(ISNUMBER(P10:Q10), P10:Q10, 0))</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
       <c r="T10" s="59"/>
       <c r="U10" s="63"/>
       <c r="V10" s="59" t="s">
         <v>3044</v>
       </c>
       <c r="W10" s="58">
-        <v>1</v>
-      </c>
-      <c r="X10" s="59"/>
-      <c r="Y10" s="60"/>
-      <c r="Z10" s="59"/>
-      <c r="AA10" s="60"/>
-      <c r="AB10" s="59"/>
-      <c r="AC10" s="60"/>
+        <v>0.94</v>
+      </c>
+      <c r="X10" s="59" t="s">
+        <v>3097</v>
+      </c>
+      <c r="Y10" s="60">
+        <v>0.03</v>
+      </c>
+      <c r="Z10" s="59" t="s">
+        <v>3054</v>
+      </c>
+      <c r="AA10" s="60">
+        <v>0.02</v>
+      </c>
+      <c r="AB10" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="AC10" s="60">
+        <v>0.01</v>
+      </c>
       <c r="AD10" s="59"/>
       <c r="AE10" s="60"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -40636,7 +40787,7 @@
         <f t="shared" si="0"/>
         <v>9.0817412019999999</v>
       </c>
-      <c r="H11" s="61">
+      <c r="H11" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B11, prodcom_data[product], 0))</f>
         <v>0.94409418582769256</v>
       </c>
@@ -40666,30 +40817,48 @@
         <v>3036</v>
       </c>
       <c r="Q11" s="58">
-        <v>1</v>
-      </c>
-      <c r="R11" s="59"/>
-      <c r="S11" s="60"/>
+        <v>0.98</v>
+      </c>
+      <c r="R11" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S11" s="61" cm="1">
+        <f t="array" ref="S11">1-SUM(IF(ISNUMBER(P11:Q11), P11:Q11, 0))</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
       <c r="T11" s="59"/>
       <c r="U11" s="63"/>
       <c r="V11" s="59" t="s">
         <v>3044</v>
       </c>
       <c r="W11" s="58">
-        <v>1</v>
-      </c>
-      <c r="X11" s="59"/>
-      <c r="Y11" s="60"/>
-      <c r="Z11" s="59"/>
-      <c r="AA11" s="60"/>
-      <c r="AB11" s="59"/>
-      <c r="AC11" s="60"/>
+        <v>0.97</v>
+      </c>
+      <c r="X11" s="59" t="s">
+        <v>3097</v>
+      </c>
+      <c r="Y11" s="60">
+        <v>0.01</v>
+      </c>
+      <c r="Z11" s="59" t="s">
+        <v>3054</v>
+      </c>
+      <c r="AA11" s="60">
+        <v>0.01</v>
+      </c>
+      <c r="AB11" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AC11" s="61" cm="1">
+        <f t="array" ref="AC11">1-SUM(IF(ISNUMBER(V11:AA11), V11:AA11, 0))</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="AD11" s="59"/>
       <c r="AE11" s="60"/>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>539</v>
@@ -40711,7 +40880,7 @@
         <f t="shared" si="0"/>
         <v>7.6288794710000003</v>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B12, prodcom_data[product], 0))</f>
         <v>0.78369292184089345</v>
       </c>
@@ -40751,12 +40920,21 @@
         <v>3036</v>
       </c>
       <c r="W12" s="58">
-        <v>1</v>
-      </c>
-      <c r="X12" s="59"/>
-      <c r="Y12" s="60"/>
-      <c r="Z12" s="59"/>
-      <c r="AA12" s="60"/>
+        <v>0.81</v>
+      </c>
+      <c r="X12" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="Y12" s="60">
+        <v>0.05</v>
+      </c>
+      <c r="Z12" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AA12" s="61" cm="1">
+        <f t="array" ref="AA12">1-SUM(IF(ISNUMBER(V12:Y12), V12:Y12, 0))</f>
+        <v>0.1399999999999999</v>
+      </c>
       <c r="AB12" s="59"/>
       <c r="AC12" s="60"/>
       <c r="AD12" s="59"/>
@@ -40764,7 +40942,7 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" s="64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
         <v>111</v>
@@ -40786,7 +40964,7 @@
         <f t="shared" si="0"/>
         <v>6.9047320579999996</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B13, prodcom_data[product], 0))</f>
         <v>0.14193164800139446</v>
       </c>
@@ -40865,7 +41043,7 @@
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" s="64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
         <v>34</v>
@@ -40887,7 +41065,7 @@
         <f t="shared" si="0"/>
         <v>6.2344760670000001</v>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B14, prodcom_data[product], 0))</f>
         <v>0.88287081478020857</v>
       </c>
@@ -40917,20 +41095,30 @@
         <v>3036</v>
       </c>
       <c r="Q14" s="58">
-        <v>1</v>
-      </c>
-      <c r="R14" s="59"/>
-      <c r="S14" s="60"/>
+        <v>0.93</v>
+      </c>
+      <c r="R14" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S14" s="61" cm="1">
+        <f t="array" ref="S14">1-SUM(IF(ISNUMBER(P14:Q14), P14:Q14, 0))</f>
+        <v>6.9999999999999951E-2</v>
+      </c>
       <c r="T14" s="59"/>
       <c r="U14" s="63"/>
       <c r="V14" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W14" s="58">
-        <v>1</v>
-      </c>
-      <c r="X14" s="59"/>
-      <c r="Y14" s="60"/>
+        <v>0.93</v>
+      </c>
+      <c r="X14" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y14" s="61" cm="1">
+        <f t="array" ref="Y14">1-SUM(IF(ISNUMBER(V14:W14), V14:W14, 0))</f>
+        <v>6.9999999999999951E-2</v>
+      </c>
       <c r="Z14" s="59"/>
       <c r="AA14" s="60"/>
       <c r="AB14" s="59"/>
@@ -40940,7 +41128,7 @@
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" s="64">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
         <v>563</v>
@@ -40962,7 +41150,7 @@
         <f t="shared" si="0"/>
         <v>5.008047468</v>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B15, prodcom_data[product], 0))</f>
         <v>0.89272188364169869</v>
       </c>
@@ -40992,22 +41180,37 @@
         <v>3036</v>
       </c>
       <c r="Q15" s="58">
-        <v>1</v>
-      </c>
-      <c r="R15" s="59"/>
-      <c r="S15" s="60"/>
+        <v>0.92</v>
+      </c>
+      <c r="R15" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S15" s="61" cm="1">
+        <f t="array" ref="S15">1-SUM(IF(ISNUMBER(P15:Q15), P15:Q15, 0))</f>
+        <v>7.999999999999996E-2</v>
+      </c>
       <c r="T15" s="59"/>
       <c r="U15" s="63"/>
       <c r="V15" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W15" s="58">
-        <v>1</v>
-      </c>
-      <c r="X15" s="59"/>
-      <c r="Y15" s="60"/>
-      <c r="Z15" s="59"/>
-      <c r="AA15" s="60"/>
+        <v>0.92</v>
+      </c>
+      <c r="X15" s="59" t="s">
+        <v>3098</v>
+      </c>
+      <c r="Y15" s="61">
+        <f>0.03+0.03</f>
+        <v>0.06</v>
+      </c>
+      <c r="Z15" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AA15" s="61" cm="1">
+        <f t="array" ref="AA15">1-SUM(IF(ISNUMBER(V15:Y15), V15:Y15, 0))</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
       <c r="AB15" s="59"/>
       <c r="AC15" s="60"/>
       <c r="AD15" s="59"/>
@@ -41015,7 +41218,7 @@
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" s="64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
         <v>536</v>
@@ -41037,7 +41240,7 @@
         <f t="shared" si="0"/>
         <v>4.4742138760000003</v>
       </c>
-      <c r="H16" s="61">
+      <c r="H16" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B16, prodcom_data[product], 0))</f>
         <v>0.7961067883023123</v>
       </c>
@@ -41077,12 +41280,21 @@
         <v>3036</v>
       </c>
       <c r="W16" s="58">
-        <v>1</v>
-      </c>
-      <c r="X16" s="59"/>
-      <c r="Y16" s="60"/>
-      <c r="Z16" s="59"/>
-      <c r="AA16" s="60"/>
+        <v>0.84</v>
+      </c>
+      <c r="X16" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="Y16" s="60">
+        <v>0.04</v>
+      </c>
+      <c r="Z16" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AA16" s="61" cm="1">
+        <f t="array" ref="AA16">1-SUM(IF(ISNUMBER(V16:Y16), V16:Y16, 0))</f>
+        <v>0.12</v>
+      </c>
       <c r="AB16" s="59"/>
       <c r="AC16" s="60"/>
       <c r="AD16" s="59"/>
@@ -41090,7 +41302,7 @@
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" s="64">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
         <v>533</v>
@@ -41112,7 +41324,7 @@
         <f t="shared" si="0"/>
         <v>4.2387100530000001</v>
       </c>
-      <c r="H17" s="61">
+      <c r="H17" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B17, prodcom_data[product], 0))</f>
         <v>0.8225375065540016</v>
       </c>
@@ -41165,7 +41377,7 @@
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A18" s="64">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
         <v>49</v>
@@ -41187,7 +41399,7 @@
         <f t="shared" si="0"/>
         <v>3.6279763919999999</v>
       </c>
-      <c r="H18" s="61">
+      <c r="H18" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B18, prodcom_data[product], 0))</f>
         <v>0.82690725513409014</v>
       </c>
@@ -41217,30 +41429,48 @@
         <v>3036</v>
       </c>
       <c r="Q18" s="58">
-        <v>1</v>
-      </c>
-      <c r="R18" s="59"/>
-      <c r="S18" s="60"/>
+        <v>0.84</v>
+      </c>
+      <c r="R18" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S18" s="61" cm="1">
+        <f t="array" ref="S18">1-SUM(IF(ISNUMBER(P18:Q18), P18:Q18, 0))</f>
+        <v>0.16000000000000003</v>
+      </c>
       <c r="T18" s="59"/>
       <c r="U18" s="63"/>
       <c r="V18" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W18" s="58">
-        <v>1</v>
-      </c>
-      <c r="X18" s="59"/>
-      <c r="Y18" s="60"/>
-      <c r="Z18" s="59"/>
-      <c r="AA18" s="60"/>
-      <c r="AB18" s="59"/>
-      <c r="AC18" s="60"/>
+        <v>0.84</v>
+      </c>
+      <c r="X18" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="Y18" s="60">
+        <v>0.06</v>
+      </c>
+      <c r="Z18" s="59" t="s">
+        <v>3099</v>
+      </c>
+      <c r="AA18" s="60">
+        <v>0.03</v>
+      </c>
+      <c r="AB18" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AC18" s="61" cm="1">
+        <f t="array" ref="AC18">1-SUM(IF(ISNUMBER(V18:AA18), V18:AA18, 0))</f>
+        <v>7.0000000000000062E-2</v>
+      </c>
       <c r="AD18" s="59"/>
       <c r="AE18" s="60"/>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A19" s="64">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
         <v>263</v>
@@ -41262,7 +41492,7 @@
         <f t="shared" si="0"/>
         <v>3.4912837350000001</v>
       </c>
-      <c r="H19" s="61">
+      <c r="H19" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B19, prodcom_data[product], 0))</f>
         <v>0.80199726304971886</v>
       </c>
@@ -41315,7 +41545,7 @@
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" s="64">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
         <v>599</v>
@@ -41337,7 +41567,7 @@
         <f t="shared" si="0"/>
         <v>3.34918497</v>
       </c>
-      <c r="H20" s="61">
+      <c r="H20" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B20, prodcom_data[product], 0))</f>
         <v>0.6568762309953875</v>
       </c>
@@ -41390,7 +41620,7 @@
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" s="64">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -41412,7 +41642,7 @@
         <f t="shared" si="0"/>
         <v>2.8089402570000002</v>
       </c>
-      <c r="H21" s="61">
+      <c r="H21" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B21, prodcom_data[product], 0))</f>
         <v>0.9968172135460267</v>
       </c>
@@ -41465,7 +41695,7 @@
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" s="64">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" t="s">
         <v>14</v>
@@ -41487,7 +41717,7 @@
         <f t="shared" si="0"/>
         <v>2.0000466659999998</v>
       </c>
-      <c r="H22" s="61">
+      <c r="H22" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B22, prodcom_data[product], 0))</f>
         <v>0.99997666754441616</v>
       </c>
@@ -41540,7 +41770,7 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" s="64">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
         <v>548</v>
@@ -41562,7 +41792,7 @@
         <f t="shared" si="0"/>
         <v>1.8640651770000001</v>
       </c>
-      <c r="H23" s="61">
+      <c r="H23" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B23, prodcom_data[product], 0))</f>
         <v>0.88707249478326589</v>
       </c>
@@ -41602,10 +41832,15 @@
         <v>3036</v>
       </c>
       <c r="W23" s="58">
-        <v>1</v>
-      </c>
-      <c r="X23" s="59"/>
-      <c r="Y23" s="60"/>
+        <v>0.91</v>
+      </c>
+      <c r="X23" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y23" s="61" cm="1">
+        <f t="array" ref="Y23">1-SUM(IF(ISNUMBER(V23:W23), V23:W23, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
       <c r="Z23" s="59"/>
       <c r="AA23" s="60"/>
       <c r="AB23" s="59"/>
@@ -41615,7 +41850,7 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" s="64">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
         <v>132</v>
@@ -41637,7 +41872,7 @@
         <f t="shared" si="0"/>
         <v>1.7957479670000001</v>
       </c>
-      <c r="H24" s="61">
+      <c r="H24" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B24, prodcom_data[product], 0))</f>
         <v>0.55687101886052137</v>
       </c>
@@ -41700,7 +41935,7 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" s="64">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
         <v>476</v>
@@ -41722,7 +41957,7 @@
         <f t="shared" si="0"/>
         <v>1.650938177</v>
       </c>
-      <c r="H25" s="61">
+      <c r="H25" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B25, prodcom_data[product], 0))</f>
         <v>0.98168669522505081</v>
       </c>
@@ -41752,20 +41987,29 @@
         <v>3036</v>
       </c>
       <c r="Q25" s="58">
-        <v>1</v>
-      </c>
-      <c r="R25" s="59"/>
-      <c r="S25" s="60"/>
+        <v>0.98</v>
+      </c>
+      <c r="R25" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S25" s="61" cm="1">
+        <f t="array" ref="S25">1-SUM(IF(ISNUMBER(P25:Q25), P25:Q25, 0))</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
       <c r="T25" s="59"/>
       <c r="U25" s="63"/>
       <c r="V25" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W25" s="58">
-        <v>1</v>
-      </c>
-      <c r="X25" s="59"/>
-      <c r="Y25" s="60"/>
+        <v>0.98</v>
+      </c>
+      <c r="X25" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="Y25" s="60">
+        <v>0.02</v>
+      </c>
       <c r="Z25" s="59"/>
       <c r="AA25" s="60"/>
       <c r="AB25" s="59"/>
@@ -41775,7 +42019,7 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" s="64">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
         <v>551</v>
@@ -41797,7 +42041,7 @@
         <f t="shared" si="0"/>
         <v>1.592476459</v>
       </c>
-      <c r="H26" s="61">
+      <c r="H26" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B26, prodcom_data[product], 0))</f>
         <v>0.93163807390386044</v>
       </c>
@@ -41850,7 +42094,7 @@
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" s="64">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
         <v>72</v>
@@ -41872,7 +42116,7 @@
         <f t="shared" si="0"/>
         <v>1.2029393820000001</v>
       </c>
-      <c r="H27" s="61">
+      <c r="H27" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B27, prodcom_data[product], 0))</f>
         <v>0.7564803460728331</v>
       </c>
@@ -41935,7 +42179,7 @@
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" s="64">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
         <v>43</v>
@@ -41957,7 +42201,7 @@
         <f t="shared" si="0"/>
         <v>1.191905947</v>
       </c>
-      <c r="H28" s="61">
+      <c r="H28" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B28, prodcom_data[product], 0))</f>
         <v>0.46597635861951109</v>
       </c>
@@ -42020,7 +42264,7 @@
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" s="64">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
         <v>37</v>
@@ -42042,7 +42286,7 @@
         <f t="shared" si="0"/>
         <v>1.1203816150000001</v>
       </c>
-      <c r="H29" s="61">
+      <c r="H29" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B29, prodcom_data[product], 0))</f>
         <v>0.97878773028598831</v>
       </c>
@@ -42095,7 +42339,7 @@
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" s="64">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
         <v>420</v>
@@ -42117,7 +42361,7 @@
         <f t="shared" si="0"/>
         <v>1.0908528070000001</v>
       </c>
-      <c r="H30" s="61">
+      <c r="H30" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B30, prodcom_data[product], 0))</f>
         <v>0.92846915963429333</v>
       </c>
@@ -42180,7 +42424,7 @@
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" s="64">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
         <v>387</v>
@@ -42202,7 +42446,7 @@
         <f t="shared" si="0"/>
         <v>0.931200527</v>
       </c>
-      <c r="H31" s="61">
+      <c r="H31" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B31, prodcom_data[product], 0))</f>
         <v>0.97723312392412343</v>
       </c>
@@ -42232,20 +42476,30 @@
         <v>3036</v>
       </c>
       <c r="Q31" s="58">
-        <v>1</v>
-      </c>
-      <c r="R31" s="59"/>
-      <c r="S31" s="60"/>
+        <v>0.99</v>
+      </c>
+      <c r="R31" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S31" s="61" cm="1">
+        <f t="array" ref="S31">1-SUM(IF(ISNUMBER(P31:Q31), P31:Q31, 0))</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="T31" s="59"/>
       <c r="U31" s="63"/>
       <c r="V31" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W31" s="58">
-        <v>1</v>
-      </c>
-      <c r="X31" s="59"/>
-      <c r="Y31" s="60"/>
+        <v>0.99</v>
+      </c>
+      <c r="X31" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y31" s="61" cm="1">
+        <f t="array" ref="Y31">1-SUM(IF(ISNUMBER(V31:W31), V31:W31, 0))</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="Z31" s="59"/>
       <c r="AA31" s="60"/>
       <c r="AB31" s="59"/>
@@ -42255,7 +42509,7 @@
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" s="64">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B32" t="s">
         <v>620</v>
@@ -42277,7 +42531,7 @@
         <f t="shared" si="0"/>
         <v>0.91489276799999997</v>
       </c>
-      <c r="H32" s="61">
+      <c r="H32" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B32, prodcom_data[product], 0))</f>
         <v>0.98372184312642852</v>
       </c>
@@ -42307,20 +42561,30 @@
         <v>3036</v>
       </c>
       <c r="Q32" s="58">
-        <v>1</v>
-      </c>
-      <c r="R32" s="59"/>
-      <c r="S32" s="60"/>
+        <v>0.99</v>
+      </c>
+      <c r="R32" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S32" s="61" cm="1">
+        <f t="array" ref="S32">1-SUM(IF(ISNUMBER(P32:Q32), P32:Q32, 0))</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="T32" s="59"/>
       <c r="U32" s="63"/>
       <c r="V32" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W32" s="58">
-        <v>1</v>
-      </c>
-      <c r="X32" s="59"/>
-      <c r="Y32" s="60"/>
+        <v>0.99</v>
+      </c>
+      <c r="X32" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y32" s="61" cm="1">
+        <f t="array" ref="Y32">1-SUM(IF(ISNUMBER(V32:W32), V32:W32, 0))</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="Z32" s="59"/>
       <c r="AA32" s="60"/>
       <c r="AB32" s="59"/>
@@ -42330,7 +42594,7 @@
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A33" s="64">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
         <v>205</v>
@@ -42352,7 +42616,7 @@
         <f t="shared" si="0"/>
         <v>0.88856497499999998</v>
       </c>
-      <c r="H33" s="61">
+      <c r="H33" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B33, prodcom_data[product], 0))</f>
         <v>0.16881151544376369</v>
       </c>
@@ -42405,7 +42669,7 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A34" s="64">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B34" t="s">
         <v>473</v>
@@ -42427,7 +42691,7 @@
         <f t="shared" si="0"/>
         <v>0.88675937800000004</v>
       </c>
-      <c r="H34" s="61">
+      <c r="H34" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B34, prodcom_data[product], 0))</f>
         <v>0.9949802605865421</v>
       </c>
@@ -42480,7 +42744,7 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A35" s="64">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
         <v>78</v>
@@ -42502,7 +42766,7 @@
         <f t="shared" si="0"/>
         <v>0.88227254300000002</v>
       </c>
-      <c r="H35" s="61">
+      <c r="H35" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B35, prodcom_data[product], 0))</f>
         <v>0.90674928778782138</v>
       </c>
@@ -42532,22 +42796,36 @@
         <v>3036</v>
       </c>
       <c r="Q35" s="58">
-        <v>1</v>
-      </c>
-      <c r="R35" s="59"/>
-      <c r="S35" s="60"/>
+        <v>0.98</v>
+      </c>
+      <c r="R35" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S35" s="61" cm="1">
+        <f t="array" ref="S35">1-SUM(IF(ISNUMBER(P35:Q35), P35:Q35, 0))</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
       <c r="T35" s="59"/>
       <c r="U35" s="63"/>
       <c r="V35" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W35" s="58">
-        <v>1</v>
-      </c>
-      <c r="X35" s="59"/>
-      <c r="Y35" s="60"/>
-      <c r="Z35" s="59"/>
-      <c r="AA35" s="60"/>
+        <v>0.98</v>
+      </c>
+      <c r="X35" s="59" t="s">
+        <v>3096</v>
+      </c>
+      <c r="Y35" s="60">
+        <v>0.01</v>
+      </c>
+      <c r="Z35" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="AA35" s="61" cm="1">
+        <f t="array" ref="AA35">1-SUM(IF(ISNUMBER(V35:Y35), V35:Y35, 0))</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="AB35" s="59"/>
       <c r="AC35" s="60"/>
       <c r="AD35" s="59"/>
@@ -42555,7 +42833,7 @@
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A36" s="64">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
         <v>293</v>
@@ -42577,7 +42855,7 @@
         <f t="shared" si="0"/>
         <v>0.88188415799999997</v>
       </c>
-      <c r="H36" s="61">
+      <c r="H36" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B36, prodcom_data[product], 0))</f>
         <v>0.54958148029233567</v>
       </c>
@@ -42640,7 +42918,7 @@
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A37" s="64">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
         <v>602</v>
@@ -42662,7 +42940,7 @@
         <f t="shared" si="0"/>
         <v>0.87233590599999999</v>
       </c>
-      <c r="H37" s="61">
+      <c r="H37" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B37, prodcom_data[product], 0))</f>
         <v>0.50439285712492499</v>
       </c>
@@ -42715,7 +42993,7 @@
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A38" s="64">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
         <v>135</v>
@@ -42737,7 +43015,7 @@
         <f t="shared" si="0"/>
         <v>0.84802669900000005</v>
       </c>
-      <c r="H38" s="61">
+      <c r="H38" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B38, prodcom_data[product], 0))</f>
         <v>0.94336652483154892</v>
       </c>
@@ -42800,7 +43078,7 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A39" s="64">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B39" t="s">
         <v>557</v>
@@ -42822,7 +43100,7 @@
         <f t="shared" si="0"/>
         <v>0.84621718300000004</v>
       </c>
-      <c r="H39" s="61">
+      <c r="H39" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B39, prodcom_data[product], 0))</f>
         <v>0.71535186139088358</v>
       </c>
@@ -42875,7 +43153,7 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A40" s="64">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
         <v>46</v>
@@ -42897,7 +43175,7 @@
         <f t="shared" si="0"/>
         <v>0.82143353699999999</v>
       </c>
-      <c r="H40" s="61">
+      <c r="H40" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B40, prodcom_data[product], 0))</f>
         <v>0.97390715616715806</v>
       </c>
@@ -42960,7 +43238,7 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A41" s="64">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
         <v>569</v>
@@ -42982,7 +43260,7 @@
         <f t="shared" si="0"/>
         <v>0.79072103000000005</v>
       </c>
-      <c r="H41" s="61">
+      <c r="H41" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B41, prodcom_data[product], 0))</f>
         <v>0.93548794446506622</v>
       </c>
@@ -43045,7 +43323,7 @@
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A42" s="64">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
         <v>55</v>
@@ -43067,7 +43345,7 @@
         <f t="shared" si="0"/>
         <v>0.77849552700000002</v>
       </c>
-      <c r="H42" s="61">
+      <c r="H42" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B42, prodcom_data[product], 0))</f>
         <v>0.9345821199560983</v>
       </c>
@@ -43130,7 +43408,7 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A43" s="64">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B43" t="s">
         <v>332</v>
@@ -43152,7 +43430,7 @@
         <f t="shared" si="0"/>
         <v>0.70506910199999995</v>
       </c>
-      <c r="H43" s="61">
+      <c r="H43" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B43, prodcom_data[product], 0))</f>
         <v>0.85098041922137724</v>
       </c>
@@ -43205,7 +43483,7 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A44" s="64">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B44" t="s">
         <v>28</v>
@@ -43227,7 +43505,7 @@
         <f t="shared" si="0"/>
         <v>0.683315016</v>
       </c>
-      <c r="H44" s="61">
+      <c r="H44" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B44, prodcom_data[product], 0))</f>
         <v>0.35122892718634474</v>
       </c>
@@ -43280,7 +43558,7 @@
     </row>
     <row r="45" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A45" s="64">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
         <v>252</v>
@@ -43302,7 +43580,7 @@
         <f t="shared" si="0"/>
         <v>0.667655569</v>
       </c>
-      <c r="H45" s="61">
+      <c r="H45" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B45, prodcom_data[product], 0))</f>
         <v>0.85514301162071182</v>
       </c>
@@ -43355,7 +43633,7 @@
     </row>
     <row r="46" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A46" s="64">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
         <v>114</v>
@@ -43377,7 +43655,7 @@
         <f t="shared" si="0"/>
         <v>0.66734765100000004</v>
       </c>
-      <c r="H46" s="61">
+      <c r="H46" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B46, prodcom_data[product], 0))</f>
         <v>0.80917344833809868</v>
       </c>
@@ -43440,7 +43718,7 @@
     </row>
     <row r="47" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A47" s="64">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B47" t="s">
         <v>52</v>
@@ -43462,7 +43740,7 @@
         <f t="shared" si="0"/>
         <v>0.64249725999999996</v>
       </c>
-      <c r="H47" s="61">
+      <c r="H47" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B47, prodcom_data[product], 0))</f>
         <v>0.93385612259264728</v>
       </c>
@@ -43492,20 +43770,29 @@
         <v>3036</v>
       </c>
       <c r="Q47" s="58">
-        <v>1</v>
-      </c>
-      <c r="R47" s="59"/>
-      <c r="S47" s="60"/>
+        <v>0.99</v>
+      </c>
+      <c r="R47" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S47" s="61" cm="1">
+        <f t="array" ref="S47">1-SUM(IF(ISNUMBER(P47:Q47), P47:Q47, 0))</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="T47" s="59"/>
       <c r="U47" s="63"/>
       <c r="V47" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W47" s="58">
-        <v>1</v>
-      </c>
-      <c r="X47" s="59"/>
-      <c r="Y47" s="60"/>
+        <v>0.99</v>
+      </c>
+      <c r="X47" s="59" t="s">
+        <v>3046</v>
+      </c>
+      <c r="Y47" s="60">
+        <v>0.01</v>
+      </c>
       <c r="Z47" s="59"/>
       <c r="AA47" s="60"/>
       <c r="AB47" s="59"/>
@@ -43515,7 +43802,7 @@
     </row>
     <row r="48" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A48" s="64">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B48" t="s">
         <v>220</v>
@@ -43537,7 +43824,7 @@
         <f t="shared" si="0"/>
         <v>0.60486187300000005</v>
       </c>
-      <c r="H48" s="61">
+      <c r="H48" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B48, prodcom_data[product], 0))</f>
         <v>0.66130800742337414</v>
       </c>
@@ -43598,9 +43885,9 @@
       <c r="AD48" s="59"/>
       <c r="AE48" s="60"/>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A49" s="64">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
         <v>542</v>
@@ -43622,7 +43909,7 @@
         <f t="shared" si="0"/>
         <v>0.593659673</v>
       </c>
-      <c r="H49" s="61">
+      <c r="H49" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B49, prodcom_data[product], 0))</f>
         <v>0.84223339185782964</v>
       </c>
@@ -43683,9 +43970,9 @@
       <c r="AD49" s="59"/>
       <c r="AE49" s="60"/>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A50" s="64">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B50" t="s">
         <v>117</v>
@@ -43707,7 +43994,7 @@
         <f t="shared" si="0"/>
         <v>0.507331541</v>
       </c>
-      <c r="H50" s="61">
+      <c r="H50" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B50, prodcom_data[product], 0))</f>
         <v>0.78843905350643284</v>
       </c>
@@ -43758,9 +44045,9 @@
       <c r="AD50" s="59"/>
       <c r="AE50" s="60"/>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A51" s="64">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
         <v>284</v>
@@ -43782,7 +44069,7 @@
         <f t="shared" si="0"/>
         <v>0.44373955900000001</v>
       </c>
-      <c r="H51" s="61">
+      <c r="H51" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B51, prodcom_data[product], 0))</f>
         <v>0.9014296604554024</v>
       </c>
@@ -43843,9 +44130,9 @@
       <c r="AD51" s="59"/>
       <c r="AE51" s="60"/>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A52" s="64">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
         <v>186</v>
@@ -43867,7 +44154,7 @@
         <f t="shared" si="0"/>
         <v>0.37760138599999998</v>
       </c>
-      <c r="H52" s="61">
+      <c r="H52" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B52, prodcom_data[product], 0))</f>
         <v>0.11917329138193365</v>
       </c>
@@ -43918,9 +44205,9 @@
       <c r="AD52" s="59"/>
       <c r="AE52" s="60"/>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A53" s="64">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
         <v>581</v>
@@ -43942,7 +44229,7 @@
         <f t="shared" si="0"/>
         <v>0.334412816</v>
       </c>
-      <c r="H53" s="61">
+      <c r="H53" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B53, prodcom_data[product], 0))</f>
         <v>0.59226283959165005</v>
       </c>
@@ -43985,9 +44272,9 @@
       <c r="AD53" s="59"/>
       <c r="AE53" s="60"/>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A54" s="64">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B54" t="s">
         <v>459</v>
@@ -44009,7 +44296,7 @@
         <f t="shared" si="0"/>
         <v>0.32184670100000001</v>
       </c>
-      <c r="H54" s="61">
+      <c r="H54" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B54, prodcom_data[product], 0))</f>
         <v>0.18642415725740188</v>
       </c>
@@ -44070,9 +44357,9 @@
       <c r="AD54" s="59"/>
       <c r="AE54" s="60"/>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A55" s="64">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
         <v>226</v>
@@ -44094,7 +44381,7 @@
         <f t="shared" si="0"/>
         <v>0.32163824499999999</v>
       </c>
-      <c r="H55" s="61">
+      <c r="H55" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B55, prodcom_data[product], 0))</f>
         <v>0.27981747008972768</v>
       </c>
@@ -44155,9 +44442,9 @@
       <c r="AD55" s="59"/>
       <c r="AE55" s="60"/>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A56" s="64">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B56" t="s">
         <v>40</v>
@@ -44179,7 +44466,7 @@
         <f t="shared" si="0"/>
         <v>0.31820840700000003</v>
       </c>
-      <c r="H56" s="61">
+      <c r="H56" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B56, prodcom_data[product], 0))</f>
         <v>0.44804616680036363</v>
       </c>
@@ -44240,238 +44527,216 @@
       <c r="AD56" s="59"/>
       <c r="AE56" s="60"/>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:32" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="64">
-        <v>48</v>
-      </c>
-      <c r="B57" s="65" t="s">
-        <v>345</v>
-      </c>
-      <c r="C57" s="64" t="s">
-        <v>2829</v>
-      </c>
-      <c r="D57" s="52" t="s">
-        <v>3010</v>
+        <v>49</v>
+      </c>
+      <c r="B57" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C57" s="64">
+        <v>290311</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>62</v>
       </c>
       <c r="E57" s="48" t="s">
-        <v>3011</v>
+        <v>3081</v>
       </c>
       <c r="F57" s="56">
-        <f>Calculations!C32*(Calculations!C29/SUM(Calculations!$C$28:$C$29))</f>
-        <v>242141968.15384617</v>
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B57, prodcom_data[product], 0))</f>
+        <v>300894106</v>
       </c>
       <c r="G57" s="54">
         <f t="shared" si="0"/>
-        <v>0.24214196815384617</v>
-      </c>
-      <c r="H57" s="61">
+        <v>0.30089410599999999</v>
+      </c>
+      <c r="H57" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B57, prodcom_data[product], 0))</f>
-        <v>0.88632047658515611</v>
-      </c>
-      <c r="I57" s="48" t="s">
-        <v>3012</v>
+        <v>0.99702850277831634</v>
+      </c>
+      <c r="I57" s="49" t="s">
+        <v>3086</v>
       </c>
       <c r="J57" s="49" t="s">
-        <v>2671</v>
+        <v>3087</v>
       </c>
       <c r="K57" s="79" t="s">
-        <v>3013</v>
+        <v>3088</v>
       </c>
       <c r="L57" s="79">
-        <v>174.16</v>
-      </c>
-      <c r="M57" s="80" t="s">
-        <v>2974</v>
+        <v>50.49</v>
+      </c>
+      <c r="M57" s="98">
+        <v>1</v>
       </c>
       <c r="N57" s="72">
         <f>M57*Calculations!$C$37/L57</f>
-        <v>0.6206878732200275</v>
+        <v>0.23788869082986727</v>
       </c>
       <c r="O57" s="81" t="s">
-        <v>3014</v>
+        <v>3089</v>
       </c>
       <c r="P57" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q57" s="58">
-        <v>0.88</v>
-      </c>
-      <c r="R57" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S57" s="61" cm="1">
-        <f t="array" ref="S57">1-SUM(IF(ISNUMBER(P57:Q57), P57:Q57, 0))</f>
-        <v>0.12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R57" s="59"/>
+      <c r="S57" s="59"/>
       <c r="T57" s="59"/>
       <c r="U57" s="63"/>
       <c r="V57" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="W57" s="58">
-        <v>0.88</v>
-      </c>
-      <c r="X57" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y57" s="61" cm="1">
-        <f t="array" ref="Y57">1-SUM(IF(ISNUMBER(V57:W57), V57:W57, 0))</f>
-        <v>0.12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X57" s="59"/>
+      <c r="Y57" s="59"/>
       <c r="Z57" s="59"/>
       <c r="AA57" s="60"/>
       <c r="AB57" s="59"/>
       <c r="AC57" s="60"/>
       <c r="AD57" s="59"/>
       <c r="AE57" s="60"/>
+      <c r="AF57"/>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:32" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="64">
-        <v>49</v>
-      </c>
-      <c r="B58" s="65" t="s">
-        <v>345</v>
-      </c>
-      <c r="C58" s="64" t="s">
-        <v>2829</v>
-      </c>
-      <c r="D58" s="52" t="s">
-        <v>3015</v>
+        <v>50</v>
+      </c>
+      <c r="B58" s="50" t="s">
+        <v>393</v>
+      </c>
+      <c r="C58" s="64">
+        <v>291219</v>
+      </c>
+      <c r="D58" s="50" t="s">
+        <v>394</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>3016</v>
+        <v>3082</v>
       </c>
       <c r="F58" s="56">
-        <f>Calculations!C32*(Calculations!C28/SUM(Calculations!$C$28:$C$29))</f>
-        <v>807139893.84615386</v>
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B58, prodcom_data[product], 0))</f>
+        <v>300000000</v>
       </c>
       <c r="G58" s="54">
         <f t="shared" si="0"/>
-        <v>0.80713989384615381</v>
-      </c>
-      <c r="H58" s="61">
+        <v>0.3</v>
+      </c>
+      <c r="H58" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B58, prodcom_data[product], 0))</f>
-        <v>0.88632047658515611</v>
-      </c>
-      <c r="I58" s="48" t="s">
-        <v>3017</v>
-      </c>
-      <c r="J58" s="49" t="s">
-        <v>2671</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I58" s="49" t="s">
+        <v>2691</v>
+      </c>
+      <c r="J58" s="49"/>
       <c r="K58" s="79" t="s">
-        <v>3018</v>
+        <v>3094</v>
       </c>
       <c r="L58" s="79">
-        <v>250.25</v>
+        <v>72.11</v>
       </c>
       <c r="M58" s="80" t="s">
-        <v>2959</v>
+        <v>2925</v>
       </c>
       <c r="N58" s="72">
         <f>M58*Calculations!$C$37/L58</f>
-        <v>0.71994005994005994</v>
+        <v>0.66625988073776177</v>
       </c>
       <c r="O58" s="81" t="s">
-        <v>3019</v>
+        <v>3095</v>
       </c>
       <c r="P58" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="Q58" s="58">
-        <v>0.88</v>
-      </c>
-      <c r="R58" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="S58" s="61" cm="1">
-        <f t="array" ref="S58">1-SUM(IF(ISNUMBER(P58:Q58), P58:Q58, 0))</f>
-        <v>0.12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R58" s="59"/>
+      <c r="S58" s="59"/>
       <c r="T58" s="59"/>
       <c r="U58" s="63"/>
       <c r="V58" s="59" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="W58" s="58">
-        <v>0.88</v>
-      </c>
-      <c r="X58" s="59" t="s">
-        <v>3043</v>
-      </c>
-      <c r="Y58" s="61" cm="1">
-        <f t="array" ref="Y58">1-SUM(IF(ISNUMBER(V58:W58), V58:W58, 0))</f>
-        <v>0.12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="X58" s="59"/>
+      <c r="Y58" s="59"/>
       <c r="Z58" s="59"/>
       <c r="AA58" s="60"/>
       <c r="AB58" s="59"/>
       <c r="AC58" s="60"/>
       <c r="AD58" s="59"/>
       <c r="AE58" s="60"/>
+      <c r="AF58"/>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:32" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="64">
-        <v>50</v>
-      </c>
-      <c r="B59" s="65" t="s">
-        <v>634</v>
-      </c>
-      <c r="C59" s="64" t="s">
-        <v>2819</v>
-      </c>
-      <c r="D59" s="52" t="s">
-        <v>3020</v>
+        <v>51</v>
+      </c>
+      <c r="B59" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="64">
+        <v>290723</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>165</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>3021</v>
+        <v>3083</v>
       </c>
       <c r="F59" s="56">
-        <f>Calculations!C6*(Calculations!C24/(Calculations!C15+Calculations!C24))</f>
-        <v>1089108418.3783784</v>
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B59, prodcom_data[product], 0))</f>
+        <v>258032226</v>
       </c>
       <c r="G59" s="54">
         <f t="shared" si="0"/>
-        <v>1.0891084183783784</v>
-      </c>
-      <c r="H59" s="61">
+        <v>0.25803222599999998</v>
+      </c>
+      <c r="H59" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B59, prodcom_data[product], 0))</f>
-        <v>0.87748442629671652</v>
-      </c>
-      <c r="I59" s="48" t="s">
-        <v>3022</v>
-      </c>
-      <c r="J59" s="49" t="s">
-        <v>2661</v>
-      </c>
+        <v>0.77509698342872879</v>
+      </c>
+      <c r="I59" s="49" t="s">
+        <v>3084</v>
+      </c>
+      <c r="J59" s="49"/>
       <c r="K59" s="79" t="s">
-        <v>3023</v>
+        <v>3092</v>
       </c>
       <c r="L59" s="79">
-        <v>224.3</v>
+        <v>228.29</v>
       </c>
       <c r="M59" s="80" t="s">
-        <v>2919</v>
+        <v>2959</v>
       </c>
       <c r="N59" s="72">
         <f>M59*Calculations!$C$37/L59</f>
-        <v>0.64258582255907271</v>
+        <v>0.78919356958254849</v>
       </c>
       <c r="O59" s="81" t="s">
-        <v>3024</v>
+        <v>3093</v>
       </c>
       <c r="P59" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q59" s="58">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="R59" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S59" s="61" cm="1">
         <f t="array" ref="S59">1-SUM(IF(ISNUMBER(P59:Q59), P59:Q59, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="T59" s="59"/>
       <c r="U59" s="63"/>
@@ -44479,14 +44744,14 @@
         <v>3036</v>
       </c>
       <c r="W59" s="58">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="X59" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y59" s="61" cm="1">
         <f t="array" ref="Y59">1-SUM(IF(ISNUMBER(V59:W59), V59:W59, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="Z59" s="59"/>
       <c r="AA59" s="60"/>
@@ -44494,69 +44759,68 @@
       <c r="AC59" s="60"/>
       <c r="AD59" s="59"/>
       <c r="AE59" s="60"/>
+      <c r="AF59"/>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:32" s="50" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="64">
-        <v>51</v>
-      </c>
-      <c r="B60" s="65" t="s">
-        <v>634</v>
-      </c>
-      <c r="C60" s="64" t="s">
-        <v>2819</v>
-      </c>
-      <c r="D60" s="52" t="s">
-        <v>3025</v>
+        <v>52</v>
+      </c>
+      <c r="B60" s="50" t="s">
+        <v>623</v>
+      </c>
+      <c r="C60" s="64">
+        <v>390519</v>
+      </c>
+      <c r="D60" s="50" t="s">
+        <v>624</v>
       </c>
       <c r="E60" s="48" t="s">
-        <v>3026</v>
+        <v>2939</v>
       </c>
       <c r="F60" s="56">
-        <f>Calculations!C6*(Calculations!C15/(Calculations!C15+Calculations!C24))</f>
-        <v>1281304021.6216214</v>
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B60, prodcom_data[product], 0))</f>
+        <v>250743096</v>
       </c>
       <c r="G60" s="54">
         <f t="shared" si="0"/>
-        <v>1.2813040216216214</v>
-      </c>
-      <c r="H60" s="61">
+        <v>0.250743096</v>
+      </c>
+      <c r="H60" s="97">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B60, prodcom_data[product], 0))</f>
-        <v>0.87748442629671652</v>
-      </c>
-      <c r="I60" s="48" t="s">
-        <v>3027</v>
-      </c>
-      <c r="J60" s="49" t="s">
-        <v>2661</v>
-      </c>
+        <v>0.79762913990660789</v>
+      </c>
+      <c r="I60" s="49" t="s">
+        <v>2673</v>
+      </c>
+      <c r="J60" s="49"/>
       <c r="K60" s="79" t="s">
-        <v>3028</v>
+        <v>2940</v>
       </c>
       <c r="L60" s="79">
-        <v>582.79999999999995</v>
+        <v>86.08905</v>
       </c>
       <c r="M60" s="80" t="s">
-        <v>3029</v>
+        <v>2925</v>
       </c>
       <c r="N60" s="72">
         <f>M60*Calculations!$C$37/L60</f>
-        <v>0.61827385037748805</v>
+        <v>0.55807329735895561</v>
       </c>
       <c r="O60" s="81" t="s">
-        <v>3030</v>
+        <v>2941</v>
       </c>
       <c r="P60" s="59" t="s">
         <v>3036</v>
       </c>
       <c r="Q60" s="58">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="R60" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="S60" s="61" cm="1">
         <f t="array" ref="S60">1-SUM(IF(ISNUMBER(P60:Q60), P60:Q60, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.13</v>
       </c>
       <c r="T60" s="59"/>
       <c r="U60" s="63"/>
@@ -44564,14 +44828,14 @@
         <v>3036</v>
       </c>
       <c r="W60" s="58">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="X60" s="59" t="s">
         <v>3043</v>
       </c>
       <c r="Y60" s="61" cm="1">
         <f t="array" ref="Y60">1-SUM(IF(ISNUMBER(V60:W60), V60:W60, 0))</f>
-        <v>8.9999999999999969E-2</v>
+        <v>0.13</v>
       </c>
       <c r="Z60" s="59"/>
       <c r="AA60" s="60"/>
@@ -44579,9 +44843,424 @@
       <c r="AC60" s="60"/>
       <c r="AD60" s="59"/>
       <c r="AE60" s="60"/>
+      <c r="AF60"/>
     </row>
-    <row r="110" spans="32:32" x14ac:dyDescent="0.3">
-      <c r="AF110" t="s">
+    <row r="61" spans="1:32" s="50" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="64">
+        <v>53</v>
+      </c>
+      <c r="B61" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="C61" s="64">
+        <v>291524</v>
+      </c>
+      <c r="D61" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="E61" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="F61" s="56">
+        <f>INDEX(prodcom_data[PRODQNT + IMPQNT - EU27 - 2022], MATCH(B61, prodcom_data[product], 0))</f>
+        <v>215273632</v>
+      </c>
+      <c r="G61" s="54">
+        <f t="shared" si="0"/>
+        <v>0.21527363199999999</v>
+      </c>
+      <c r="H61" s="97">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B61, prodcom_data[product], 0))</f>
+        <v>1.1148601794389756E-2</v>
+      </c>
+      <c r="I61" s="49" t="s">
+        <v>3085</v>
+      </c>
+      <c r="J61" s="49"/>
+      <c r="K61" s="79" t="s">
+        <v>3090</v>
+      </c>
+      <c r="L61" s="79">
+        <v>102.09</v>
+      </c>
+      <c r="M61" s="80" t="s">
+        <v>2925</v>
+      </c>
+      <c r="N61" s="72">
+        <f>M61*Calculations!$C$37/L61</f>
+        <v>0.47060436869428929</v>
+      </c>
+      <c r="O61" s="81" t="s">
+        <v>3091</v>
+      </c>
+      <c r="P61" s="59" t="s">
+        <v>3042</v>
+      </c>
+      <c r="Q61" s="58">
+        <v>1</v>
+      </c>
+      <c r="R61" s="59"/>
+      <c r="S61" s="59"/>
+      <c r="T61" s="59"/>
+      <c r="U61" s="63"/>
+      <c r="V61" s="59" t="s">
+        <v>3042</v>
+      </c>
+      <c r="W61" s="58">
+        <v>1</v>
+      </c>
+      <c r="X61" s="59"/>
+      <c r="Y61" s="59"/>
+      <c r="Z61" s="59"/>
+      <c r="AA61" s="60"/>
+      <c r="AB61" s="59"/>
+      <c r="AC61" s="60"/>
+      <c r="AD61" s="59"/>
+      <c r="AE61" s="60"/>
+      <c r="AF61"/>
+    </row>
+    <row r="62" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A62" s="64">
+        <v>54</v>
+      </c>
+      <c r="B62" s="65" t="s">
+        <v>345</v>
+      </c>
+      <c r="C62" s="64" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D62" s="52" t="s">
+        <v>3010</v>
+      </c>
+      <c r="E62" s="48" t="s">
+        <v>3011</v>
+      </c>
+      <c r="F62" s="56">
+        <f>Calculations!C32*(Calculations!C29/SUM(Calculations!$C$28:$C$29))</f>
+        <v>242141968.15384617</v>
+      </c>
+      <c r="G62" s="54">
+        <f t="shared" si="0"/>
+        <v>0.24214196815384617</v>
+      </c>
+      <c r="H62" s="97">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B62, prodcom_data[product], 0))</f>
+        <v>0.88632047658515611</v>
+      </c>
+      <c r="I62" s="48" t="s">
+        <v>3012</v>
+      </c>
+      <c r="J62" s="49" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K62" s="79" t="s">
+        <v>3013</v>
+      </c>
+      <c r="L62" s="79">
+        <v>174.16</v>
+      </c>
+      <c r="M62" s="80" t="s">
+        <v>2974</v>
+      </c>
+      <c r="N62" s="72">
+        <f>M62*Calculations!$C$37/L62</f>
+        <v>0.6206878732200275</v>
+      </c>
+      <c r="O62" s="81" t="s">
+        <v>3014</v>
+      </c>
+      <c r="P62" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Q62" s="58">
+        <v>0.88</v>
+      </c>
+      <c r="R62" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S62" s="61" cm="1">
+        <f t="array" ref="S62">1-SUM(IF(ISNUMBER(P62:Q62), P62:Q62, 0))</f>
+        <v>0.12</v>
+      </c>
+      <c r="T62" s="59"/>
+      <c r="U62" s="63"/>
+      <c r="V62" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="W62" s="58">
+        <v>0.88</v>
+      </c>
+      <c r="X62" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y62" s="61" cm="1">
+        <f t="array" ref="Y62">1-SUM(IF(ISNUMBER(V62:W62), V62:W62, 0))</f>
+        <v>0.12</v>
+      </c>
+      <c r="Z62" s="59"/>
+      <c r="AA62" s="60"/>
+      <c r="AB62" s="59"/>
+      <c r="AC62" s="60"/>
+      <c r="AD62" s="59"/>
+      <c r="AE62" s="60"/>
+    </row>
+    <row r="63" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A63" s="64">
+        <v>55</v>
+      </c>
+      <c r="B63" s="65" t="s">
+        <v>345</v>
+      </c>
+      <c r="C63" s="64" t="s">
+        <v>2829</v>
+      </c>
+      <c r="D63" s="52" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E63" s="48" t="s">
+        <v>3016</v>
+      </c>
+      <c r="F63" s="56">
+        <f>Calculations!C32*(Calculations!C28/SUM(Calculations!$C$28:$C$29))</f>
+        <v>807139893.84615386</v>
+      </c>
+      <c r="G63" s="54">
+        <f t="shared" si="0"/>
+        <v>0.80713989384615381</v>
+      </c>
+      <c r="H63" s="97">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B63, prodcom_data[product], 0))</f>
+        <v>0.88632047658515611</v>
+      </c>
+      <c r="I63" s="48" t="s">
+        <v>3017</v>
+      </c>
+      <c r="J63" s="49" t="s">
+        <v>2671</v>
+      </c>
+      <c r="K63" s="79" t="s">
+        <v>3018</v>
+      </c>
+      <c r="L63" s="79">
+        <v>250.25</v>
+      </c>
+      <c r="M63" s="80" t="s">
+        <v>2959</v>
+      </c>
+      <c r="N63" s="72">
+        <f>M63*Calculations!$C$37/L63</f>
+        <v>0.71994005994005994</v>
+      </c>
+      <c r="O63" s="81" t="s">
+        <v>3019</v>
+      </c>
+      <c r="P63" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Q63" s="58">
+        <v>0.88</v>
+      </c>
+      <c r="R63" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S63" s="61" cm="1">
+        <f t="array" ref="S63">1-SUM(IF(ISNUMBER(P63:Q63), P63:Q63, 0))</f>
+        <v>0.12</v>
+      </c>
+      <c r="T63" s="59"/>
+      <c r="U63" s="63"/>
+      <c r="V63" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="W63" s="58">
+        <v>0.88</v>
+      </c>
+      <c r="X63" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y63" s="61" cm="1">
+        <f t="array" ref="Y63">1-SUM(IF(ISNUMBER(V63:W63), V63:W63, 0))</f>
+        <v>0.12</v>
+      </c>
+      <c r="Z63" s="59"/>
+      <c r="AA63" s="60"/>
+      <c r="AB63" s="59"/>
+      <c r="AC63" s="60"/>
+      <c r="AD63" s="59"/>
+      <c r="AE63" s="60"/>
+    </row>
+    <row r="64" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A64" s="64">
+        <v>56</v>
+      </c>
+      <c r="B64" s="65" t="s">
+        <v>634</v>
+      </c>
+      <c r="C64" s="64" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D64" s="52" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E64" s="48" t="s">
+        <v>3021</v>
+      </c>
+      <c r="F64" s="56">
+        <f>Calculations!C6*(Calculations!C24/(Calculations!C15+Calculations!C24))</f>
+        <v>1089108418.3783784</v>
+      </c>
+      <c r="G64" s="54">
+        <f t="shared" si="0"/>
+        <v>1.0891084183783784</v>
+      </c>
+      <c r="H64" s="97">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B64, prodcom_data[product], 0))</f>
+        <v>0.87748442629671652</v>
+      </c>
+      <c r="I64" s="48" t="s">
+        <v>3022</v>
+      </c>
+      <c r="J64" s="49" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K64" s="79" t="s">
+        <v>3023</v>
+      </c>
+      <c r="L64" s="79">
+        <v>224.3</v>
+      </c>
+      <c r="M64" s="80" t="s">
+        <v>2919</v>
+      </c>
+      <c r="N64" s="72">
+        <f>M64*Calculations!$C$37/L64</f>
+        <v>0.64258582255907271</v>
+      </c>
+      <c r="O64" s="81" t="s">
+        <v>3024</v>
+      </c>
+      <c r="P64" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Q64" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="R64" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S64" s="61" cm="1">
+        <f t="array" ref="S64">1-SUM(IF(ISNUMBER(P64:Q64), P64:Q64, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="T64" s="59"/>
+      <c r="U64" s="63"/>
+      <c r="V64" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="W64" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="X64" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y64" s="61" cm="1">
+        <f t="array" ref="Y64">1-SUM(IF(ISNUMBER(V64:W64), V64:W64, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="Z64" s="59"/>
+      <c r="AA64" s="60"/>
+      <c r="AB64" s="59"/>
+      <c r="AC64" s="60"/>
+      <c r="AD64" s="59"/>
+      <c r="AE64" s="60"/>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A65" s="64">
+        <v>57</v>
+      </c>
+      <c r="B65" s="65" t="s">
+        <v>634</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D65" s="52" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E65" s="48" t="s">
+        <v>3026</v>
+      </c>
+      <c r="F65" s="56">
+        <f>Calculations!C6*(Calculations!C15/(Calculations!C15+Calculations!C24))</f>
+        <v>1281304021.6216214</v>
+      </c>
+      <c r="G65" s="54">
+        <f t="shared" si="0"/>
+        <v>1.2813040216216214</v>
+      </c>
+      <c r="H65" s="97">
+        <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B65, prodcom_data[product], 0))</f>
+        <v>0.87748442629671652</v>
+      </c>
+      <c r="I65" s="48" t="s">
+        <v>3027</v>
+      </c>
+      <c r="J65" s="49" t="s">
+        <v>2661</v>
+      </c>
+      <c r="K65" s="79" t="s">
+        <v>3028</v>
+      </c>
+      <c r="L65" s="79">
+        <v>582.79999999999995</v>
+      </c>
+      <c r="M65" s="80" t="s">
+        <v>3029</v>
+      </c>
+      <c r="N65" s="72">
+        <f>M65*Calculations!$C$37/L65</f>
+        <v>0.61827385037748805</v>
+      </c>
+      <c r="O65" s="81" t="s">
+        <v>3030</v>
+      </c>
+      <c r="P65" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="Q65" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="R65" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="S65" s="61" cm="1">
+        <f t="array" ref="S65">1-SUM(IF(ISNUMBER(P65:Q65), P65:Q65, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="T65" s="59"/>
+      <c r="U65" s="63"/>
+      <c r="V65" s="59" t="s">
+        <v>3036</v>
+      </c>
+      <c r="W65" s="58">
+        <v>0.91</v>
+      </c>
+      <c r="X65" s="59" t="s">
+        <v>3043</v>
+      </c>
+      <c r="Y65" s="61" cm="1">
+        <f t="array" ref="Y65">1-SUM(IF(ISNUMBER(V65:W65), V65:W65, 0))</f>
+        <v>8.9999999999999969E-2</v>
+      </c>
+      <c r="Z65" s="59"/>
+      <c r="AA65" s="60"/>
+      <c r="AB65" s="59"/>
+      <c r="AC65" s="60"/>
+      <c r="AD65" s="59"/>
+      <c r="AE65" s="60"/>
+    </row>
+    <row r="115" spans="32:32" x14ac:dyDescent="0.3">
+      <c r="AF115" t="s">
         <v>2658</v>
       </c>
     </row>

--- a/Article_data/Step 3 results from Prodcom data manipulations.xlsx
+++ b/Article_data/Step 3 results from Prodcom data manipulations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\nicolas\projects\202604-paper-1-supplementary-code\Article_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A660D838-64B7-4AB0-934B-596014D9CB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{446257C7-A827-451F-A9E9-D43B6D007B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-45" windowWidth="29070" windowHeight="15750" tabRatio="570" activeTab="3" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="570" xr2:uid="{EE4678C9-3BCB-4D41-A2DA-6855614353C7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -54,7 +54,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nicolas Lienart:</t>
         </r>
@@ -63,7 +63,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Saudi Arabia and South Korea</t>
@@ -78,7 +78,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Nicolas Lienart:</t>
         </r>
@@ -87,7 +87,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 United States + Mexico</t>
@@ -9465,7 +9465,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9610,19 +9610,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -10038,14 +10025,14 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -40482,10 +40469,10 @@
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="F7" s="96" t="s">
+      <c r="F7" s="98" t="s">
         <v>705</v>
       </c>
-      <c r="G7" s="96"/>
+      <c r="G7" s="98"/>
       <c r="I7" s="47" t="s">
         <v>3074</v>
       </c>
@@ -40610,7 +40597,7 @@
         <f>F9/1000000000</f>
         <v>11.059816493</v>
       </c>
-      <c r="H9" s="97">
+      <c r="H9" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B9, prodcom_data[product], 0))</f>
         <v>0.86402104863567564</v>
       </c>
@@ -40695,7 +40682,7 @@
         <f t="shared" ref="G10:G65" si="0">F10/1000000000</f>
         <v>10.337493766</v>
       </c>
-      <c r="H10" s="97">
+      <c r="H10" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B10, prodcom_data[product], 0))</f>
         <v>0.87904863332422545</v>
       </c>
@@ -40787,7 +40774,7 @@
         <f t="shared" si="0"/>
         <v>9.0817412019999999</v>
       </c>
-      <c r="H11" s="97">
+      <c r="H11" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B11, prodcom_data[product], 0))</f>
         <v>0.94409418582769256</v>
       </c>
@@ -40880,7 +40867,7 @@
         <f t="shared" si="0"/>
         <v>7.6288794710000003</v>
       </c>
-      <c r="H12" s="97">
+      <c r="H12" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B12, prodcom_data[product], 0))</f>
         <v>0.78369292184089345</v>
       </c>
@@ -40964,7 +40951,7 @@
         <f t="shared" si="0"/>
         <v>6.9047320579999996</v>
       </c>
-      <c r="H13" s="97">
+      <c r="H13" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B13, prodcom_data[product], 0))</f>
         <v>0.14193164800139446</v>
       </c>
@@ -41065,7 +41052,7 @@
         <f t="shared" si="0"/>
         <v>6.2344760670000001</v>
       </c>
-      <c r="H14" s="97">
+      <c r="H14" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B14, prodcom_data[product], 0))</f>
         <v>0.88287081478020857</v>
       </c>
@@ -41150,7 +41137,7 @@
         <f t="shared" si="0"/>
         <v>5.008047468</v>
       </c>
-      <c r="H15" s="97">
+      <c r="H15" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B15, prodcom_data[product], 0))</f>
         <v>0.89272188364169869</v>
       </c>
@@ -41240,7 +41227,7 @@
         <f t="shared" si="0"/>
         <v>4.4742138760000003</v>
       </c>
-      <c r="H16" s="97">
+      <c r="H16" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B16, prodcom_data[product], 0))</f>
         <v>0.7961067883023123</v>
       </c>
@@ -41324,7 +41311,7 @@
         <f t="shared" si="0"/>
         <v>4.2387100530000001</v>
       </c>
-      <c r="H17" s="97">
+      <c r="H17" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B17, prodcom_data[product], 0))</f>
         <v>0.8225375065540016</v>
       </c>
@@ -41399,7 +41386,7 @@
         <f t="shared" si="0"/>
         <v>3.6279763919999999</v>
       </c>
-      <c r="H18" s="97">
+      <c r="H18" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B18, prodcom_data[product], 0))</f>
         <v>0.82690725513409014</v>
       </c>
@@ -41492,7 +41479,7 @@
         <f t="shared" si="0"/>
         <v>3.4912837350000001</v>
       </c>
-      <c r="H19" s="97">
+      <c r="H19" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B19, prodcom_data[product], 0))</f>
         <v>0.80199726304971886</v>
       </c>
@@ -41567,7 +41554,7 @@
         <f t="shared" si="0"/>
         <v>3.34918497</v>
       </c>
-      <c r="H20" s="97">
+      <c r="H20" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B20, prodcom_data[product], 0))</f>
         <v>0.6568762309953875</v>
       </c>
@@ -41642,7 +41629,7 @@
         <f t="shared" si="0"/>
         <v>2.8089402570000002</v>
       </c>
-      <c r="H21" s="97">
+      <c r="H21" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B21, prodcom_data[product], 0))</f>
         <v>0.9968172135460267</v>
       </c>
@@ -41717,7 +41704,7 @@
         <f t="shared" si="0"/>
         <v>2.0000466659999998</v>
       </c>
-      <c r="H22" s="97">
+      <c r="H22" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B22, prodcom_data[product], 0))</f>
         <v>0.99997666754441616</v>
       </c>
@@ -41792,7 +41779,7 @@
         <f t="shared" si="0"/>
         <v>1.8640651770000001</v>
       </c>
-      <c r="H23" s="97">
+      <c r="H23" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B23, prodcom_data[product], 0))</f>
         <v>0.88707249478326589</v>
       </c>
@@ -41872,7 +41859,7 @@
         <f t="shared" si="0"/>
         <v>1.7957479670000001</v>
       </c>
-      <c r="H24" s="97">
+      <c r="H24" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B24, prodcom_data[product], 0))</f>
         <v>0.55687101886052137</v>
       </c>
@@ -41957,7 +41944,7 @@
         <f t="shared" si="0"/>
         <v>1.650938177</v>
       </c>
-      <c r="H25" s="97">
+      <c r="H25" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B25, prodcom_data[product], 0))</f>
         <v>0.98168669522505081</v>
       </c>
@@ -42041,7 +42028,7 @@
         <f t="shared" si="0"/>
         <v>1.592476459</v>
       </c>
-      <c r="H26" s="97">
+      <c r="H26" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B26, prodcom_data[product], 0))</f>
         <v>0.93163807390386044</v>
       </c>
@@ -42116,7 +42103,7 @@
         <f t="shared" si="0"/>
         <v>1.2029393820000001</v>
       </c>
-      <c r="H27" s="97">
+      <c r="H27" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B27, prodcom_data[product], 0))</f>
         <v>0.7564803460728331</v>
       </c>
@@ -42201,7 +42188,7 @@
         <f t="shared" si="0"/>
         <v>1.191905947</v>
       </c>
-      <c r="H28" s="97">
+      <c r="H28" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B28, prodcom_data[product], 0))</f>
         <v>0.46597635861951109</v>
       </c>
@@ -42286,7 +42273,7 @@
         <f t="shared" si="0"/>
         <v>1.1203816150000001</v>
       </c>
-      <c r="H29" s="97">
+      <c r="H29" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B29, prodcom_data[product], 0))</f>
         <v>0.97878773028598831</v>
       </c>
@@ -42361,7 +42348,7 @@
         <f t="shared" si="0"/>
         <v>1.0908528070000001</v>
       </c>
-      <c r="H30" s="97">
+      <c r="H30" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B30, prodcom_data[product], 0))</f>
         <v>0.92846915963429333</v>
       </c>
@@ -42446,7 +42433,7 @@
         <f t="shared" si="0"/>
         <v>0.931200527</v>
       </c>
-      <c r="H31" s="97">
+      <c r="H31" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B31, prodcom_data[product], 0))</f>
         <v>0.97723312392412343</v>
       </c>
@@ -42531,7 +42518,7 @@
         <f t="shared" si="0"/>
         <v>0.91489276799999997</v>
       </c>
-      <c r="H32" s="97">
+      <c r="H32" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B32, prodcom_data[product], 0))</f>
         <v>0.98372184312642852</v>
       </c>
@@ -42616,7 +42603,7 @@
         <f t="shared" si="0"/>
         <v>0.88856497499999998</v>
       </c>
-      <c r="H33" s="97">
+      <c r="H33" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B33, prodcom_data[product], 0))</f>
         <v>0.16881151544376369</v>
       </c>
@@ -42691,7 +42678,7 @@
         <f t="shared" si="0"/>
         <v>0.88675937800000004</v>
       </c>
-      <c r="H34" s="97">
+      <c r="H34" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B34, prodcom_data[product], 0))</f>
         <v>0.9949802605865421</v>
       </c>
@@ -42766,7 +42753,7 @@
         <f t="shared" si="0"/>
         <v>0.88227254300000002</v>
       </c>
-      <c r="H35" s="97">
+      <c r="H35" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B35, prodcom_data[product], 0))</f>
         <v>0.90674928778782138</v>
       </c>
@@ -42855,7 +42842,7 @@
         <f t="shared" si="0"/>
         <v>0.88188415799999997</v>
       </c>
-      <c r="H36" s="97">
+      <c r="H36" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B36, prodcom_data[product], 0))</f>
         <v>0.54958148029233567</v>
       </c>
@@ -42940,7 +42927,7 @@
         <f t="shared" si="0"/>
         <v>0.87233590599999999</v>
       </c>
-      <c r="H37" s="97">
+      <c r="H37" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B37, prodcom_data[product], 0))</f>
         <v>0.50439285712492499</v>
       </c>
@@ -43015,7 +43002,7 @@
         <f t="shared" si="0"/>
         <v>0.84802669900000005</v>
       </c>
-      <c r="H38" s="97">
+      <c r="H38" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B38, prodcom_data[product], 0))</f>
         <v>0.94336652483154892</v>
       </c>
@@ -43100,7 +43087,7 @@
         <f t="shared" si="0"/>
         <v>0.84621718300000004</v>
       </c>
-      <c r="H39" s="97">
+      <c r="H39" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B39, prodcom_data[product], 0))</f>
         <v>0.71535186139088358</v>
       </c>
@@ -43175,7 +43162,7 @@
         <f t="shared" si="0"/>
         <v>0.82143353699999999</v>
       </c>
-      <c r="H40" s="97">
+      <c r="H40" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B40, prodcom_data[product], 0))</f>
         <v>0.97390715616715806</v>
       </c>
@@ -43260,7 +43247,7 @@
         <f t="shared" si="0"/>
         <v>0.79072103000000005</v>
       </c>
-      <c r="H41" s="97">
+      <c r="H41" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B41, prodcom_data[product], 0))</f>
         <v>0.93548794446506622</v>
       </c>
@@ -43345,7 +43332,7 @@
         <f t="shared" si="0"/>
         <v>0.77849552700000002</v>
       </c>
-      <c r="H42" s="97">
+      <c r="H42" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B42, prodcom_data[product], 0))</f>
         <v>0.9345821199560983</v>
       </c>
@@ -43430,7 +43417,7 @@
         <f t="shared" si="0"/>
         <v>0.70506910199999995</v>
       </c>
-      <c r="H43" s="97">
+      <c r="H43" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B43, prodcom_data[product], 0))</f>
         <v>0.85098041922137724</v>
       </c>
@@ -43505,7 +43492,7 @@
         <f t="shared" si="0"/>
         <v>0.683315016</v>
       </c>
-      <c r="H44" s="97">
+      <c r="H44" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B44, prodcom_data[product], 0))</f>
         <v>0.35122892718634474</v>
       </c>
@@ -43580,7 +43567,7 @@
         <f t="shared" si="0"/>
         <v>0.667655569</v>
       </c>
-      <c r="H45" s="97">
+      <c r="H45" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B45, prodcom_data[product], 0))</f>
         <v>0.85514301162071182</v>
       </c>
@@ -43655,7 +43642,7 @@
         <f t="shared" si="0"/>
         <v>0.66734765100000004</v>
       </c>
-      <c r="H46" s="97">
+      <c r="H46" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B46, prodcom_data[product], 0))</f>
         <v>0.80917344833809868</v>
       </c>
@@ -43740,7 +43727,7 @@
         <f t="shared" si="0"/>
         <v>0.64249725999999996</v>
       </c>
-      <c r="H47" s="97">
+      <c r="H47" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B47, prodcom_data[product], 0))</f>
         <v>0.93385612259264728</v>
       </c>
@@ -43824,7 +43811,7 @@
         <f t="shared" si="0"/>
         <v>0.60486187300000005</v>
       </c>
-      <c r="H48" s="97">
+      <c r="H48" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B48, prodcom_data[product], 0))</f>
         <v>0.66130800742337414</v>
       </c>
@@ -43909,7 +43896,7 @@
         <f t="shared" si="0"/>
         <v>0.593659673</v>
       </c>
-      <c r="H49" s="97">
+      <c r="H49" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B49, prodcom_data[product], 0))</f>
         <v>0.84223339185782964</v>
       </c>
@@ -43994,7 +43981,7 @@
         <f t="shared" si="0"/>
         <v>0.507331541</v>
       </c>
-      <c r="H50" s="97">
+      <c r="H50" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B50, prodcom_data[product], 0))</f>
         <v>0.78843905350643284</v>
       </c>
@@ -44069,7 +44056,7 @@
         <f t="shared" si="0"/>
         <v>0.44373955900000001</v>
       </c>
-      <c r="H51" s="97">
+      <c r="H51" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B51, prodcom_data[product], 0))</f>
         <v>0.9014296604554024</v>
       </c>
@@ -44154,7 +44141,7 @@
         <f t="shared" si="0"/>
         <v>0.37760138599999998</v>
       </c>
-      <c r="H52" s="97">
+      <c r="H52" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B52, prodcom_data[product], 0))</f>
         <v>0.11917329138193365</v>
       </c>
@@ -44229,7 +44216,7 @@
         <f t="shared" si="0"/>
         <v>0.334412816</v>
       </c>
-      <c r="H53" s="97">
+      <c r="H53" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B53, prodcom_data[product], 0))</f>
         <v>0.59226283959165005</v>
       </c>
@@ -44296,7 +44283,7 @@
         <f t="shared" si="0"/>
         <v>0.32184670100000001</v>
       </c>
-      <c r="H54" s="97">
+      <c r="H54" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B54, prodcom_data[product], 0))</f>
         <v>0.18642415725740188</v>
       </c>
@@ -44381,7 +44368,7 @@
         <f t="shared" si="0"/>
         <v>0.32163824499999999</v>
       </c>
-      <c r="H55" s="97">
+      <c r="H55" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B55, prodcom_data[product], 0))</f>
         <v>0.27981747008972768</v>
       </c>
@@ -44466,7 +44453,7 @@
         <f t="shared" si="0"/>
         <v>0.31820840700000003</v>
       </c>
-      <c r="H56" s="97">
+      <c r="H56" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B56, prodcom_data[product], 0))</f>
         <v>0.44804616680036363</v>
       </c>
@@ -44551,7 +44538,7 @@
         <f t="shared" si="0"/>
         <v>0.30089410599999999</v>
       </c>
-      <c r="H57" s="97">
+      <c r="H57" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B57, prodcom_data[product], 0))</f>
         <v>0.99702850277831634</v>
       </c>
@@ -44567,7 +44554,7 @@
       <c r="L57" s="79">
         <v>50.49</v>
       </c>
-      <c r="M57" s="98">
+      <c r="M57" s="97">
         <v>1</v>
       </c>
       <c r="N57" s="72">
@@ -44627,7 +44614,7 @@
         <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
-      <c r="H58" s="97">
+      <c r="H58" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B58, prodcom_data[product], 0))</f>
         <v>1</v>
       </c>
@@ -44701,7 +44688,7 @@
         <f t="shared" si="0"/>
         <v>0.25803222599999998</v>
       </c>
-      <c r="H59" s="97">
+      <c r="H59" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B59, prodcom_data[product], 0))</f>
         <v>0.77509698342872879</v>
       </c>
@@ -44785,7 +44772,7 @@
         <f t="shared" si="0"/>
         <v>0.250743096</v>
       </c>
-      <c r="H60" s="97">
+      <c r="H60" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B60, prodcom_data[product], 0))</f>
         <v>0.79762913990660789</v>
       </c>
@@ -44869,7 +44856,7 @@
         <f t="shared" si="0"/>
         <v>0.21527363199999999</v>
       </c>
-      <c r="H61" s="97">
+      <c r="H61" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B61, prodcom_data[product], 0))</f>
         <v>1.1148601794389756E-2</v>
       </c>
@@ -44943,7 +44930,7 @@
         <f t="shared" si="0"/>
         <v>0.24214196815384617</v>
       </c>
-      <c r="H62" s="97">
+      <c r="H62" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B62, prodcom_data[product], 0))</f>
         <v>0.88632047658515611</v>
       </c>
@@ -45028,7 +45015,7 @@
         <f t="shared" si="0"/>
         <v>0.80713989384615381</v>
       </c>
-      <c r="H63" s="97">
+      <c r="H63" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B63, prodcom_data[product], 0))</f>
         <v>0.88632047658515611</v>
       </c>
@@ -45113,7 +45100,7 @@
         <f t="shared" si="0"/>
         <v>1.0891084183783784</v>
       </c>
-      <c r="H64" s="97">
+      <c r="H64" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B64, prodcom_data[product], 0))</f>
         <v>0.87748442629671652</v>
       </c>
@@ -45198,7 +45185,7 @@
         <f t="shared" si="0"/>
         <v>1.2813040216216214</v>
       </c>
-      <c r="H65" s="97">
+      <c r="H65" s="96">
         <f>INDEX(prodcom_data[Local production share of available quantity (PRODQNT + IMPQNT) - EU27 - 2022], MATCH(B65, prodcom_data[product], 0))</f>
         <v>0.87748442629671652</v>
       </c>
